--- a/film.xlsx
+++ b/film.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/cinema_en_classe_localhost 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF26D46-7CF7-4644-9CA5-187889CF5784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2035123-AE60-994F-8046-0FC10EDCDFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
   <si>
     <t>youtube</t>
   </si>
@@ -539,6 +539,17 @@
   </si>
   <si>
     <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_0</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Ceci est un test de questions
+Qestion 1 : Ceci est un test de questions
+Qestion 1 : Ceci est un test de questions
+Qestion 1 : Ceci est un test de questions
+Qestion 1 : Ceci est un test de questions
+Qestion 1 : Ceci est un test de questions</t>
   </si>
 </sst>
 </file>
@@ -589,9 +600,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -932,10 +946,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="61.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>139</v>
       </c>
@@ -966,78 +983,81 @@
       <c r="J1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1442,77 +1462,77 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -1528,8 +1548,11 @@
       <c r="J111" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K111" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>112</v>
       </c>

--- a/film.xlsx
+++ b/film.xlsx
@@ -5,18 +5,19 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Documents/Codex/2026-05-25/files-mentioned-by-the-user-index/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2035123-AE60-994F-8046-0FC10EDCDFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EDBF99-31AF-AA45-965A-0775EF1BA444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning" sheetId="1" r:id="rId1"/>
+    <sheet name="Films" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$B$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$B$144</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="329">
   <si>
     <t>youtube</t>
   </si>
@@ -551,12 +552,735 @@
 Qestion 1 : Ceci est un test de questions
 Qestion 1 : Ceci est un test de questions</t>
   </si>
+  <si>
+    <t>A cloudy lesson</t>
+  </si>
+  <si>
+    <t>titre</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t>Qestion 1 : Qui sont les deux personnages ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+a. Un grand-père et son petit fil 
+b. Un grand-père et sa petite fille 
+c. Un grand-père et son fils
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 2 : Que se passe-t-il lorsque le grand-père souffle dans le cercle ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. Il en sort un génie
+b. Il en sort une énorme bulle
+c. Il en sort un gros nuage
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 3 : Que se passe-t-il lorsque c’est l’autre personnage qui souffle ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. Il ne se passe rien
+b. Le cercle s'envole
+c. Il crache à l'intérieur
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t>Qestion 4 : Que se passe-t-il ensuite ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+a. Il abîme le cercle
+b. Il arrive à utiliser le cercle
+c. Il jette le cercle
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 5 : Que décide-t-il alors ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. De créer de nouvelles formes pour les nuages
+b. De demander au grand-père de lui expliquer encore
+c. De partir très loin
+</t>
+    </r>
+  </si>
+  <si>
+    <t>An Object at Rest</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t>Qestion 1 : C’est l’histoire…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+a. D’une étoile 
+b. D’une rivière 
+c. D’une montagne
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 2 : Que se passe-t-il pendant qu’elle dort ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. Une catastrophe se produit
+b. Le temps passe
+c. Les dinosaures détruisent tout
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 3 : Quand elle se réveille, que s’est-il passé ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. Elle a rétréci
+b. Elle n’existe plus
+c. Elle s’est agrandie
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t>Qestion 4 : A quoi n’est-elle pas utilisée ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+a. A faire un boulet de canon
+b. A faire un moulin à eau
+c. IA faire une table
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve">Qestion 5 : Que décide-t-il alors ?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a. Elle n’existe plus
+b. Elle devient un grain de sable
+c. Elle redevient montagne
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Bertie l'éléphant</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hwt1-j_n1SY?si=OKVoa5rllkueH4N-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Boite à monstre</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iSexOBHpGxE?si=IZ8ZQVLt4VlbPga2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Bottle</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5mVEapKnS1c?si=O4I9bzTrHeTRVcz2</t>
+  </si>
+  <si>
+    <t>Cooped</t>
+  </si>
+  <si>
+    <t>https://youtu.be/p1mAcvSExCw?si=wVRjH62R_Opq46oc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Cours de nature</t>
+  </si>
+  <si>
+    <t>https://youtu.be/T78ruBKK26w?si=IHgt9yh7hzym_iWa</t>
+  </si>
+  <si>
+    <t>Dust Buddies</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mZ6eeAjgSZI?si=qlOIDQNHZrd6sj8O</t>
+  </si>
+  <si>
+    <t>Embarked</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y47-gmGvZhI?si=515qesQpwA7ZKqef</t>
+  </si>
+  <si>
+    <t>For the birds</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WjoDEQqyTig?si=Wj17jimnCSxQgZFh</t>
+  </si>
+  <si>
+    <t>Glace à l'eau</t>
+  </si>
+  <si>
+    <t>https://youtu.be/C7e0CqPTkrI?si=5CTAyu2E1elSJrVw</t>
+  </si>
+  <si>
+    <t>Jamais sans mon dentier</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WyCQE9XHqDA?si=OYKlJEmHIO8lx5pt</t>
+  </si>
+  <si>
+    <t>Jelly</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2qH442rW6F4?si=1X5CseK5uoJUY2CW</t>
+  </si>
+  <si>
+    <t>Jour de pluie</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HQSJa-_Xopo?si=Qdtp2dLUOGIHyCHu</t>
+  </si>
+  <si>
+    <t>Joy et la carpe chanceuse</t>
+  </si>
+  <si>
+    <t>https://youtu.be/h4wFLWJ8MG4?si=9MlqzoT9JqxRq-xT</t>
+  </si>
+  <si>
+    <t>Joy et le Héron</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZQGuVKHtrxc?si=Sn1jDssPd73xh4Hy</t>
+  </si>
+  <si>
+    <t>Knick Knack</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zgwJeG7pS9c</t>
+  </si>
+  <si>
+    <t>La maison en petits cubes</t>
+  </si>
+  <si>
+    <t>https://youtu.be/YUtoiyu80TM</t>
+  </si>
+  <si>
+    <t>La vie en vert</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SfyINYirOoA?si=N4Z5RJOtpVlFvNwZ</t>
+  </si>
+  <si>
+    <t>Le cadeau</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3XA0bB79oGc?si=mJyPELtH8LVtvXZA</t>
+  </si>
+  <si>
+    <t>Le complexe du hérisson</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W0f-ULXGqsE?si=ug7f8kDuS17HSIHX</t>
+  </si>
+  <si>
+    <t>Le plus gros président du monde</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sRWCctUzubE?si=SmgqLvu7KaJljm2r</t>
+  </si>
+  <si>
+    <t>Les chaussures de Louis</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eIWyHjVPas0?si=dbzlzEg46XB72ruC</t>
+  </si>
+  <si>
+    <t>Les lettres qui tombent</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EQ71vgRzCA4?si=5ADvSg5sBy68e8Go</t>
+  </si>
+  <si>
+    <t>Les pyramides d'Egypte</t>
+  </si>
+  <si>
+    <t>https://youtu.be/j6PbonHsqW0?si=NXgNJtYDfaHQgqCF</t>
+  </si>
+  <si>
+    <t>Lily et le bonhomme de neige</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FCF-rNMLVpE?si=4Lhp3tqQ9bsSfd8d</t>
+  </si>
+  <si>
+    <t>Lost Property</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qwMe-Z87OZ0?si=Sua6_509LWN0t7FD</t>
+  </si>
+  <si>
+    <t>Lumière</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hdyAFuHRayQ?si=JFeJtTAKmZItzmgV</t>
+  </si>
+  <si>
+    <t>Lunette</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eviPBToWpP4?si=-m1_uRMYQ-WVE98k</t>
+  </si>
+  <si>
+    <t>Migrants</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ugPJi8kMK8Q?si=a5d3bzrg1ThCGHIS</t>
+  </si>
+  <si>
+    <t>Mon petit frère de la lune</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GfGbfLuBQAY?si=VP7vEv7OmdsC2yBA</t>
+  </si>
+  <si>
+    <t>Monkey Symphony</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9CZmq-RJvoI?si=sIlcxul5NWSTfqXT</t>
+  </si>
+  <si>
+    <t>Mr Hublot</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=j2-DJacGz8Y</t>
+  </si>
+  <si>
+    <t>One man band</t>
+  </si>
+  <si>
+    <t>https://youtu.be/454nNoD6-TI?si=Mymkt5ar5KWb4sWy</t>
+  </si>
+  <si>
+    <t>One upon a blue moon</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rIX2eUvZiro?si=1mVsSAiwN6qUCYrY</t>
+  </si>
+  <si>
+    <t>Pip</t>
+  </si>
+  <si>
+    <t>https://youtu.be/07d2dXHYb94?si=RoPl4avSi4Yx4gVQ</t>
+  </si>
+  <si>
+    <t>Quantum Jump</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FVNJFBI0b-g?si=3sCNCTNuL4qxOO4Z</t>
+  </si>
+  <si>
+    <t>Rituel</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QADYuPXfrxM?si=iuxuvdzCfvsKFzk9</t>
+  </si>
+  <si>
+    <t>Rubato</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1D7D3_HFB3o?si=0_RDZ2Vscdipqs9C</t>
+  </si>
+  <si>
+    <t>Sans Gravité</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vX77zcKiN98?si=AiGeBdNGKCrrtI8q</t>
+  </si>
+  <si>
+    <t>Sapling</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fmLDta7pMs8?si=xTImfs-m_kc2OWcv</t>
+  </si>
+  <si>
+    <t>Snack Attack</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6YSxJnqCr8I</t>
+  </si>
+  <si>
+    <t>Soar</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UUlaseGrkLc?si=HWZHUUNiAlhalk09</t>
+  </si>
+  <si>
+    <t>SpellBound</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TuNdTpjXkJ0?si=bXUMJ-zn86x8h7r0</t>
+  </si>
+  <si>
+    <t>Sweet Cocoon</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yQ1ZcNpbwOA?si=iXUYgh1Kt0nb7gV9</t>
+  </si>
+  <si>
+    <t>The Misguided Monk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mQQ3BdjCc4I?si=HadQCgmFvrogCLCA</t>
+  </si>
+  <si>
+    <t>The monk and the fly</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4cywWIPoqko?si=TDclT7XZ5M3ERr5r</t>
+  </si>
+  <si>
+    <t>The mountain king</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UQsB3W6Eciw?si=2l3hNmwMLJhvq-Yy</t>
+  </si>
+  <si>
+    <t>The song for rain</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pBB1-UVCzPo?si=0-ct6AcKLfo_v0Ai</t>
+  </si>
+  <si>
+    <t>The Wishgranter</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zON0wDD7VJY?si=wMbL-LS5_FEd6Hlz</t>
+  </si>
+  <si>
+    <t>Tuurngait</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XaI-nEN2DRE?si=QDVJDhvNAG6XQPD6</t>
+  </si>
+  <si>
+    <t>Un carré pour la biodiversité</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wGm97ppSM3w?si=pkX65PY3fDJEs_c1</t>
+  </si>
+  <si>
+    <t>Vagabond</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7k7rCTP-sOI?si=8A3CtJF_CLXdQsjM</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CfAWTuE9psE?si=Him0sQMqAkuz2JRW</t>
+  </si>
+  <si>
+    <t>Au coeur de la nuit, un jeune éléphanteau ramène un jouet perdu à sa propriétaire…</t>
+  </si>
+  <si>
+    <t>https://animationland.fr/wp-content/uploads/2017/08/bertie-éléphant-678x381.png</t>
+  </si>
+  <si>
+    <t>Chris Turner &amp; Zak Boxall</t>
+  </si>
+  <si>
+    <t>5 min 20</t>
+  </si>
+  <si>
+    <t>Court, Dramatique, Poétique</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1680060/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3761946/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6852774/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6128252/?ref_=fn_t_1</t>
+  </si>
+  <si>
+    <t>Mikel MUGICA, Adele HAWKINS, Soo Kyung KANG</t>
+  </si>
+  <si>
+    <t>Etats-Unis</t>
+  </si>
+  <si>
+    <t>4 min 23</t>
+  </si>
+  <si>
+    <t>Court métrage Animation Familial</t>
+  </si>
+  <si>
+    <t>Ah les cabanes…quel délicieux souvenir… Et quel déchirement de les quitter lorsqu’on doit déménager. A moins que… mais oui ! Tout n’est pas perdu…</t>
+  </si>
+  <si>
+    <t>https://a.ltrbxd.com/resized/film-poster/7/2/2/1/9/1/722191-embarked-0-2000-0-3000-crop.jpg?v=111200c4cd</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0248808/?ref_=fn_t_1</t>
+  </si>
+  <si>
+    <t>https://medias.unifrance.org/medias/124/107/224124/format_page/glace-a-l-eau.jpg</t>
+  </si>
+  <si>
+    <t>Animation</t>
+  </si>
+  <si>
+    <t>Séparé de sa banquise, un iceberg curieux dérive au gré des courants. Il découvre alors avec crainte et surprise un monde aussi majestueux que tourmenté.</t>
+  </si>
+  <si>
+    <t>6 min</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Damien Desvignes, Victor Hayé, Mathieu Barbe</t>
+  </si>
+  <si>
+    <t>Le combat contre l’oppression d’une bande de quatre retraités loufoques. Quatre résidents d’une maison de retraite veulent regarder leur feuilleton favori mais l’infirmière en chef leur confisque la télécommande.</t>
+  </si>
+  <si>
+    <t>5 min</t>
+  </si>
+  <si>
+    <t>Alice Coutelle, Thomas Dibet, Hugo Favre, Eliette Gibaud, Cerise Grefferat, Guillaume Jarrosson, Thi Bich Pham et Thibault Spieser</t>
+  </si>
+  <si>
+    <t>Animation, Court, Comédie</t>
+  </si>
+  <si>
+    <t>https://sunread26.wordpress.com/wp-content/uploads/2024/09/jamais-sans-mon-dentier-229831.png</t>
+  </si>
+  <si>
+    <t>Un jour de beau temps, comme à son habitude, Milo joue dans la ville avec son ami. Quand soudain, au détour d’une rue, ce dernier disparaît sans laisser de trace. Milo le retrouvera-t-il ?</t>
+  </si>
+  <si>
+    <t>2 min 21</t>
+  </si>
+  <si>
+    <t>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B</t>
+  </si>
+  <si>
+    <t>https://www.esma-3d.ca/wp-content/uploads/2015/12/cloudy-day-affiche-ok.jpg</t>
+  </si>
+  <si>
+    <t>Kamelia CHABANE, Adrien FLANQUART, Emeric MALVAT et Benjamin TUSSIOT</t>
+  </si>
+  <si>
+    <t>7 min 33</t>
+  </si>
+  <si>
+    <t>Dans un monde isolé ou la sècheresse perdure, un petit village survit grâce à une machine qui transforme les nuages en eau potable. Mais lorsque le nuage tant attendu arrive à proximité de la machine, la bêtise d’un villageois et de son brave compagnon effraie la précieuse source d’eau. Les deux fautifs, bien décidés à se racheter auprès des villageois, se lancent alors dans une chasse au nuage frénétique...</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt8016566/</t>
+  </si>
+  <si>
+    <t>3 min 44</t>
+  </si>
+  <si>
+    <t>Le petit chien Joy aide la petite carpe à remonter une cascade en construisant des marches dedans. À la fin, la carpe parvient à franchir la cascade en sautant et devient un dragon.</t>
+  </si>
+  <si>
+    <t>https://cdn.i.haymarketmedia.asia/?n=campaign-china%2fcontent%2fJOY_landing.png&amp;h=570&amp;w=855&amp;q=100&amp;v=20250320&amp;c=1</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0097674/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1361566/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt9784346/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3682556/</t>
+  </si>
+  <si>
+    <t>Julia Robin
+Pauline Brunner
+Paul Chuop
+Chloé Goussé
+Alexandre Monge</t>
+  </si>
+  <si>
+    <t>2 min 36</t>
+  </si>
+  <si>
+    <t>Ce film traite avec humour le thème du repli sur soi en utilisant le hérisson, animal réputé peureux, comme personnage principal.</t>
+  </si>
+  <si>
+    <t>https://www.films-pour-enfants.com/films-pour-enfants/voir-film-enfant-complexe-ecole.jpg</t>
+  </si>
+  <si>
+    <t>Benjamin Renner</t>
+  </si>
+  <si>
+    <t>1 min 17</t>
+  </si>
+  <si>
+    <t>Le plus gros Président du Monde fait tout son possible pour garder la terre propre mais si personne n'y met du sien, c'est mission impossible.</t>
+  </si>
+  <si>
+    <t>https://media.senscritique.com/media/000004411305/0/le_plus_gros_president_du_monde.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -574,6 +1298,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri (Corps)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -600,11 +1339,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -946,14 +1696,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="11" max="11" width="61.5" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="80.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>139</v>
       </c>
       <c r="B1" t="s">
@@ -988,839 +1739,1908 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="A45" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="A46" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="A47" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="A48" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="A50" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="A51" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="A52" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="A53" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="A54" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="A56" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="A57" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="A58" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="A59" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="A60" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="A61" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="A62" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="A64" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="A65" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="A66" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="A67" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="A68" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="A69" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="A70" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="A71" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="A72" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="A73" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="A74" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="A75" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="A76" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="A77" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="A78" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="A79" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="A80" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="A81" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="A82" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="A83" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="A84" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="A85" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="A86" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="A87" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="A88" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="A89" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="A90" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="A91" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="A92" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="A93" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="A94" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="A95" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="A96" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="A97" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="A98" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="A99" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="A100" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="A101" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+      <c r="A102" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="A103" s="6" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="A104" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="A105" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+      <c r="A106" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+      <c r="A107" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+      <c r="A108" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="A109" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+      <c r="A110" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="404" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" s="1"/>
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A112" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A113" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A115" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
         <v>140</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C116" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E116" t="s">
         <v>84</v>
       </c>
-      <c r="J111" t="s">
+      <c r="J116" t="s">
         <v>152</v>
       </c>
-      <c r="K111" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-      <c r="B112" t="s">
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A117" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B117" t="s">
         <v>147</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C117" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" t="s">
-        <v>154</v>
-      </c>
-      <c r="C113" t="s">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A118" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>176</v>
+      </c>
+      <c r="D118" t="s">
+        <v>281</v>
+      </c>
+      <c r="E118" t="s">
+        <v>84</v>
+      </c>
+      <c r="F118">
+        <v>2016</v>
+      </c>
+      <c r="G118" t="s">
+        <v>282</v>
+      </c>
+      <c r="H118" t="s">
+        <v>283</v>
+      </c>
+      <c r="I118" t="s">
+        <v>279</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A119" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>178</v>
+      </c>
+      <c r="C119" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-      <c r="B114" t="s">
-        <v>154</v>
-      </c>
-      <c r="C114" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>115</v>
-      </c>
-      <c r="B115" t="s">
-        <v>154</v>
-      </c>
-      <c r="C115" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>116</v>
-      </c>
-      <c r="B116" t="s">
-        <v>154</v>
-      </c>
-      <c r="C116" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>117</v>
-      </c>
-      <c r="B117" t="s">
-        <v>154</v>
-      </c>
-      <c r="C117" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>118</v>
-      </c>
-      <c r="B118" t="s">
-        <v>154</v>
-      </c>
-      <c r="C118" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A120" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B119" t="s">
-        <v>154</v>
-      </c>
-      <c r="C119" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
+        <v>180</v>
+      </c>
+      <c r="C120" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A121" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B120" t="s">
-        <v>154</v>
-      </c>
-      <c r="C120" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
+        <v>182</v>
+      </c>
+      <c r="C121" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A122" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B122" t="s">
+        <v>184</v>
+      </c>
+      <c r="C122" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A123" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B121" t="s">
-        <v>154</v>
-      </c>
-      <c r="C121" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+      <c r="B123" t="s">
+        <v>186</v>
+      </c>
+      <c r="C123" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A124" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B122" t="s">
-        <v>154</v>
-      </c>
-      <c r="C122" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+      <c r="B124" t="s">
+        <v>188</v>
+      </c>
+      <c r="D124" t="s">
+        <v>288</v>
+      </c>
+      <c r="E124" t="s">
+        <v>289</v>
+      </c>
+      <c r="F124">
+        <v>2014</v>
+      </c>
+      <c r="G124" t="s">
+        <v>290</v>
+      </c>
+      <c r="H124" t="s">
+        <v>291</v>
+      </c>
+      <c r="I124" t="s">
+        <v>292</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A125" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B123" t="s">
-        <v>154</v>
-      </c>
-      <c r="C123" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+      <c r="B125" t="s">
+        <v>190</v>
+      </c>
+      <c r="C125" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A126" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B124" t="s">
-        <v>154</v>
-      </c>
-      <c r="C124" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="B126" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E126" t="s">
+        <v>299</v>
+      </c>
+      <c r="F126">
+        <v>2019</v>
+      </c>
+      <c r="G126" t="s">
+        <v>298</v>
+      </c>
+      <c r="H126" t="s">
+        <v>296</v>
+      </c>
+      <c r="I126" t="s">
+        <v>297</v>
+      </c>
+      <c r="J126" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A127" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B127" t="s">
+        <v>194</v>
+      </c>
+      <c r="D127" t="s">
+        <v>303</v>
+      </c>
+      <c r="E127" t="s">
+        <v>299</v>
+      </c>
+      <c r="F127">
+        <v>2016</v>
+      </c>
+      <c r="G127" t="s">
+        <v>302</v>
+      </c>
+      <c r="H127" t="s">
+        <v>304</v>
+      </c>
+      <c r="I127" t="s">
+        <v>301</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A128" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B125" t="s">
-        <v>154</v>
-      </c>
-      <c r="C125" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+      <c r="B128" t="s">
+        <v>196</v>
+      </c>
+      <c r="E128" t="s">
+        <v>299</v>
+      </c>
+      <c r="F128">
+        <v>2018</v>
+      </c>
+      <c r="G128" t="s">
+        <v>307</v>
+      </c>
+      <c r="I128" t="s">
+        <v>306</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A129" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B126" t="s">
-        <v>154</v>
-      </c>
-      <c r="C126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="B129" t="s">
+        <v>198</v>
+      </c>
+      <c r="D129" t="s">
+        <v>310</v>
+      </c>
+      <c r="E129" t="s">
+        <v>299</v>
+      </c>
+      <c r="F129">
+        <v>2009</v>
+      </c>
+      <c r="G129" t="s">
+        <v>311</v>
+      </c>
+      <c r="I129" t="s">
+        <v>312</v>
+      </c>
+      <c r="J129" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A130" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B127" t="s">
-        <v>154</v>
-      </c>
-      <c r="C127" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="B130" t="s">
+        <v>200</v>
+      </c>
+      <c r="F130">
+        <v>2019</v>
+      </c>
+      <c r="G130" t="s">
+        <v>314</v>
+      </c>
+      <c r="I130" t="s">
+        <v>315</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A131" s="6" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+      <c r="B131" t="s">
+        <v>202</v>
+      </c>
+      <c r="C131" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A132" s="7">
+        <v>46190</v>
+      </c>
+      <c r="B132" t="s">
+        <v>204</v>
+      </c>
+      <c r="C132" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A133" s="6" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+      <c r="B133" t="s">
+        <v>206</v>
+      </c>
+      <c r="C133" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A134" s="6" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+      <c r="B134" t="s">
+        <v>208</v>
+      </c>
+      <c r="C134" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A135" s="6" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="B135" t="s">
+        <v>210</v>
+      </c>
+      <c r="C135" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A136" s="6" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+      <c r="B136" t="s">
+        <v>212</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E136" t="s">
+        <v>299</v>
+      </c>
+      <c r="F136">
+        <v>2013</v>
+      </c>
+      <c r="G136" t="s">
+        <v>322</v>
+      </c>
+      <c r="I136" t="s">
+        <v>323</v>
+      </c>
+      <c r="J136" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A137" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B137" t="s">
+        <v>214</v>
+      </c>
+      <c r="D137" t="s">
+        <v>325</v>
+      </c>
+      <c r="E137" t="s">
+        <v>299</v>
+      </c>
+      <c r="F137">
+        <v>2006</v>
+      </c>
+      <c r="G137" t="s">
+        <v>326</v>
+      </c>
+      <c r="I137" t="s">
+        <v>327</v>
+      </c>
+      <c r="J137" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B133" t="s">
-        <v>140</v>
-      </c>
-      <c r="C133" t="s">
-        <v>145</v>
-      </c>
-      <c r="E133" t="s">
-        <v>84</v>
-      </c>
-      <c r="J133" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A139" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B134" t="s">
-        <v>147</v>
-      </c>
-      <c r="C134" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A141" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A142" s="7">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A143" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A144" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="1"/>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="1"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="1"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B138" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B138">
-      <sortCondition ref="A1:A138"/>
+  <autoFilter ref="A1:B144" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B144">
+      <sortCondition ref="A1:A144"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J128" r:id="rId1" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{9C2E73AE-51D1-2B4A-BA62-E465D8CB2D3A}"/>
+    <hyperlink ref="J127" r:id="rId2" xr:uid="{7C54B1D5-5C31-3844-8D87-78C42AF1B71A}"/>
+    <hyperlink ref="J124" r:id="rId3" xr:uid="{8AD0B3A6-A358-4445-9976-D6A2F5CE179B}"/>
+    <hyperlink ref="C116" r:id="rId4" xr:uid="{69E8C45A-892E-9B43-8A15-017EDB8C8A51}"/>
+    <hyperlink ref="J130" r:id="rId5" xr:uid="{2AB0365A-EC68-944C-B59E-728AAE3E821A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
     <ignoredError sqref="B1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB1CDA6-09BE-5D45-B63F-1135F97788C0}">
+  <dimension ref="A1:K142"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="37.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="11" max="11" width="90.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4">
+        <v>2016</v>
+      </c>
+      <c r="G4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I4" t="s">
+        <v>279</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F10">
+        <v>2014</v>
+      </c>
+      <c r="G10" t="s">
+        <v>290</v>
+      </c>
+      <c r="H10" t="s">
+        <v>291</v>
+      </c>
+      <c r="I10" t="s">
+        <v>292</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F12">
+        <v>2019</v>
+      </c>
+      <c r="G12" t="s">
+        <v>298</v>
+      </c>
+      <c r="H12" t="s">
+        <v>296</v>
+      </c>
+      <c r="I12" t="s">
+        <v>297</v>
+      </c>
+      <c r="J12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13">
+        <v>2016</v>
+      </c>
+      <c r="G13" t="s">
+        <v>302</v>
+      </c>
+      <c r="H13" t="s">
+        <v>304</v>
+      </c>
+      <c r="I13" t="s">
+        <v>301</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" t="s">
+        <v>299</v>
+      </c>
+      <c r="F14">
+        <v>2018</v>
+      </c>
+      <c r="G14" t="s">
+        <v>307</v>
+      </c>
+      <c r="I14" t="s">
+        <v>306</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" t="s">
+        <v>310</v>
+      </c>
+      <c r="E15" t="s">
+        <v>299</v>
+      </c>
+      <c r="F15">
+        <v>2009</v>
+      </c>
+      <c r="G15" t="s">
+        <v>311</v>
+      </c>
+      <c r="I15" t="s">
+        <v>312</v>
+      </c>
+      <c r="J15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F16">
+        <v>2019</v>
+      </c>
+      <c r="G16" t="s">
+        <v>314</v>
+      </c>
+      <c r="I16" t="s">
+        <v>315</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E22" t="s">
+        <v>299</v>
+      </c>
+      <c r="F22">
+        <v>2013</v>
+      </c>
+      <c r="G22" t="s">
+        <v>322</v>
+      </c>
+      <c r="I22" t="s">
+        <v>323</v>
+      </c>
+      <c r="J22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" t="s">
+        <v>325</v>
+      </c>
+      <c r="E23" t="s">
+        <v>299</v>
+      </c>
+      <c r="F23">
+        <v>2006</v>
+      </c>
+      <c r="G23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I23" t="s">
+        <v>327</v>
+      </c>
+      <c r="J23" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B36" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B41" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B43" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B46" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B47" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B48" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B49" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B53" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B54" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B55" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>140</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E111" t="s">
+        <v>84</v>
+      </c>
+      <c r="J111" t="s">
+        <v>152</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>147</v>
+      </c>
+      <c r="C112" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>154</v>
+      </c>
+      <c r="C113" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>154</v>
+      </c>
+      <c r="C114" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B117" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>154</v>
+      </c>
+      <c r="C120" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>154</v>
+      </c>
+      <c r="C121" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B122" t="s">
+        <v>154</v>
+      </c>
+      <c r="C122" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B123" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B125" t="s">
+        <v>154</v>
+      </c>
+      <c r="C125" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B126" t="s">
+        <v>154</v>
+      </c>
+      <c r="C126" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B127" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>140</v>
+      </c>
+      <c r="C133" t="s">
+        <v>145</v>
+      </c>
+      <c r="E133" t="s">
+        <v>84</v>
+      </c>
+      <c r="J133" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B140" s="1"/>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B141" s="1"/>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B142" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C111" r:id="rId1" xr:uid="{EF232C5C-7DEE-DD4F-AC35-CB0C609B2391}"/>
+    <hyperlink ref="J14" r:id="rId2" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{A3508436-8B84-B841-A9AE-76F0AAA56E41}"/>
+    <hyperlink ref="J13" r:id="rId3" xr:uid="{99B30D0E-1247-EF46-A4E0-D9F00B0EF7CE}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{337919EE-DEC5-6546-97F1-E7C147633C5A}"/>
+    <hyperlink ref="C2" r:id="rId5" xr:uid="{8C67ACDC-62EC-AE4D-87F2-B889684A86E0}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{BBE60714-FB11-044B-B3A1-A300C0F3490C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/film.xlsx
+++ b/film.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Documents/Codex/2026-05-25/files-mentioned-by-the-user-index/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EDBF99-31AF-AA45-965A-0775EF1BA444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20864934-3D1A-8B49-B5A1-88B57A170022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Films" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$B$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$C$144</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="329">
   <si>
     <t>youtube</t>
   </si>
@@ -1339,14 +1339,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1696,1069 +1692,1139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="80.5" customWidth="1"/>
+    <col min="1" max="2" width="14.83203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="80.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>143</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>144</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>142</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>149</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>150</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>151</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="6" t="s">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" s="6" t="s">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="6" t="s">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A100" s="6" t="s">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" s="6" t="s">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" s="6" t="s">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="6" t="s">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" s="6" t="s">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106" s="6" t="s">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="6" t="s">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A108" s="6" t="s">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" s="6" t="s">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="6" t="s">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="6" t="s">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="1"/>
-      <c r="K111" s="2"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="6" t="s">
+      <c r="D111" s="1"/>
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K112" s="2"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A113" s="6" t="s">
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A114" s="6" t="s">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A115" s="6" t="s">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A116" s="6" t="s">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116" s="4" t="s">
         <v>116</v>
       </c>
       <c r="B116" t="s">
+        <v>170</v>
+      </c>
+      <c r="C116" t="s">
         <v>140</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>84</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A117" s="7">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117" s="5">
         <v>46169</v>
       </c>
       <c r="B117" t="s">
+        <v>173</v>
+      </c>
+      <c r="C117" t="s">
         <v>147</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A118" s="6" t="s">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>175</v>
+      </c>
+      <c r="C118" t="s">
         <v>176</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>281</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>84</v>
       </c>
-      <c r="F118">
+      <c r="G118">
         <v>2016</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>282</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>283</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>279</v>
       </c>
-      <c r="J118" s="1" t="s">
+      <c r="K118" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A119" s="6" t="s">
+    <row r="119" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A119" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C119" t="s">
         <v>178</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A120" s="6" t="s">
+    <row r="120" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A120" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C120" t="s">
         <v>180</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A121" s="6" t="s">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="4" t="s">
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>181</v>
+      </c>
+      <c r="C121" t="s">
         <v>182</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A122" s="7">
+    <row r="122" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A122" s="5">
         <v>46176</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C122" t="s">
         <v>184</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A123" s="6" t="s">
+    <row r="123" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A123" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C123" t="s">
         <v>186</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A124" s="6" t="s">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C124" t="s">
         <v>188</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>288</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>289</v>
       </c>
-      <c r="F124">
+      <c r="G124">
         <v>2014</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>290</v>
       </c>
-      <c r="H124" t="s">
+      <c r="I124" t="s">
         <v>291</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>292</v>
       </c>
-      <c r="J124" s="1" t="s">
+      <c r="K124" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A125" s="6" t="s">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C125" t="s">
         <v>190</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A126" s="6" t="s">
+    <row r="126" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A126" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C126" t="s">
         <v>192</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="E126" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>299</v>
       </c>
-      <c r="F126">
+      <c r="G126">
         <v>2019</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>298</v>
       </c>
-      <c r="H126" t="s">
+      <c r="I126" t="s">
         <v>296</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>297</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A127" s="7">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="5">
         <v>46183</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C127" t="s">
         <v>194</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>303</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>299</v>
       </c>
-      <c r="F127">
+      <c r="G127">
         <v>2016</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>302</v>
       </c>
-      <c r="H127" t="s">
+      <c r="I127" t="s">
         <v>304</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>301</v>
       </c>
-      <c r="J127" s="1" t="s">
+      <c r="K127" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A128" s="6" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C128" t="s">
         <v>196</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>299</v>
       </c>
-      <c r="F128">
+      <c r="G128">
         <v>2018</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>307</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>306</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="K128" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A129" s="6" t="s">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C129" t="s">
         <v>198</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>310</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>299</v>
       </c>
-      <c r="F129">
+      <c r="G129">
         <v>2009</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>311</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>312</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A130" s="6" t="s">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C130" t="s">
         <v>200</v>
       </c>
-      <c r="F130">
+      <c r="G130">
         <v>2019</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>314</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>315</v>
       </c>
-      <c r="J130" s="1" t="s">
+      <c r="K130" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A131" s="6" t="s">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C131" t="s">
         <v>202</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A132" s="7">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132" s="5">
         <v>46190</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C132" t="s">
         <v>204</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A133" s="6" t="s">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C133" t="s">
         <v>206</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A134" s="6" t="s">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C134" t="s">
         <v>208</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A135" s="6" t="s">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A135" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C135" t="s">
         <v>210</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A136" s="6" t="s">
+    <row r="136" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A136" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C136" t="s">
         <v>212</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="E136" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>299</v>
       </c>
-      <c r="F136">
+      <c r="G136">
         <v>2013</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>322</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>323</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A137" s="7">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A137" s="5">
         <v>46197</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C137" t="s">
         <v>214</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>325</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>299</v>
       </c>
-      <c r="F137">
+      <c r="G137">
         <v>2006</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>326</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>327</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A138" s="6" t="s">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A138" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A139" s="6" t="s">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A139" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A140" s="6" t="s">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A140" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A141" s="6" t="s">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A141" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A142" s="7">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A142" s="5">
         <v>46204</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A143" s="6" t="s">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A143" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A144" s="6" t="s">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B146" s="1"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B147" s="1"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B148" s="1"/>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C148" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B144" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B144">
+  <autoFilter ref="A1:C144" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C144">
       <sortCondition ref="A1:A144"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J128" r:id="rId1" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{9C2E73AE-51D1-2B4A-BA62-E465D8CB2D3A}"/>
-    <hyperlink ref="J127" r:id="rId2" xr:uid="{7C54B1D5-5C31-3844-8D87-78C42AF1B71A}"/>
-    <hyperlink ref="J124" r:id="rId3" xr:uid="{8AD0B3A6-A358-4445-9976-D6A2F5CE179B}"/>
-    <hyperlink ref="C116" r:id="rId4" xr:uid="{69E8C45A-892E-9B43-8A15-017EDB8C8A51}"/>
-    <hyperlink ref="J130" r:id="rId5" xr:uid="{2AB0365A-EC68-944C-B59E-728AAE3E821A}"/>
+    <hyperlink ref="K128" r:id="rId1" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{9C2E73AE-51D1-2B4A-BA62-E465D8CB2D3A}"/>
+    <hyperlink ref="K127" r:id="rId2" xr:uid="{7C54B1D5-5C31-3844-8D87-78C42AF1B71A}"/>
+    <hyperlink ref="K124" r:id="rId3" xr:uid="{8AD0B3A6-A358-4445-9976-D6A2F5CE179B}"/>
+    <hyperlink ref="D116" r:id="rId4" xr:uid="{69E8C45A-892E-9B43-8A15-017EDB8C8A51}"/>
+    <hyperlink ref="K130" r:id="rId5" xr:uid="{2AB0365A-EC68-944C-B59E-728AAE3E821A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="B1" numberStoredAsText="1"/>
+    <ignoredError sqref="C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2768,13 +2834,13 @@
   <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="11" max="11" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" t="s">
         <v>171</v>
       </c>
       <c r="B1" t="s">
@@ -2809,7 +2875,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>170</v>
       </c>
       <c r="B2" t="s">
@@ -2829,7 +2895,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>173</v>
       </c>
       <c r="B3" t="s">
@@ -2843,7 +2909,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>175</v>
       </c>
       <c r="B4" t="s">
@@ -2872,7 +2938,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B5" t="s">
@@ -2883,7 +2949,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B6" t="s">
@@ -2894,7 +2960,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>181</v>
       </c>
       <c r="B7" t="s">
@@ -2905,7 +2971,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>183</v>
       </c>
       <c r="B8" t="s">
@@ -2916,7 +2982,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B9" t="s">
@@ -2927,7 +2993,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B10" t="s">
@@ -2956,7 +3022,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B11" t="s">
@@ -2967,7 +3033,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>191</v>
       </c>
       <c r="B12" t="s">
@@ -2996,7 +3062,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B13" t="s">
@@ -3025,7 +3091,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>195</v>
       </c>
       <c r="B14" t="s">
@@ -3048,7 +3114,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B15" t="s">
@@ -3074,7 +3140,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B16" t="s">
@@ -3094,7 +3160,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B17" t="s">
@@ -3105,7 +3171,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B18" t="s">
@@ -3116,7 +3182,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B19" t="s">
@@ -3127,7 +3193,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B20" t="s">
@@ -3138,7 +3204,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>209</v>
       </c>
       <c r="B21" t="s">
@@ -3149,7 +3215,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B22" t="s">
@@ -3175,7 +3241,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B23" t="s">
@@ -3201,7 +3267,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>215</v>
       </c>
       <c r="B24" t="s">
@@ -3209,7 +3275,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>217</v>
       </c>
       <c r="B25" t="s">
@@ -3217,7 +3283,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B26" t="s">
@@ -3225,7 +3291,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>221</v>
       </c>
       <c r="B27" t="s">
@@ -3233,7 +3299,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B28" t="s">
@@ -3241,7 +3307,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B29" t="s">
@@ -3249,7 +3315,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>227</v>
       </c>
       <c r="B30" t="s">
@@ -3257,7 +3323,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B31" t="s">
@@ -3265,7 +3331,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>231</v>
       </c>
       <c r="B32" t="s">
@@ -3273,7 +3339,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>233</v>
       </c>
       <c r="B33" t="s">
@@ -3281,7 +3347,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B34" t="s">
@@ -3289,7 +3355,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>237</v>
       </c>
       <c r="B35" t="s">
@@ -3297,7 +3363,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>239</v>
       </c>
       <c r="B36" t="s">
@@ -3305,7 +3371,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>241</v>
       </c>
       <c r="B37" t="s">
@@ -3313,7 +3379,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>243</v>
       </c>
       <c r="B38" t="s">
@@ -3321,7 +3387,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>245</v>
       </c>
       <c r="B39" t="s">
@@ -3329,7 +3395,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B40" t="s">
@@ -3337,7 +3403,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>249</v>
       </c>
       <c r="B41" t="s">
@@ -3345,7 +3411,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>251</v>
       </c>
       <c r="B42" t="s">
@@ -3353,7 +3419,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B43" t="s">
@@ -3361,7 +3427,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>255</v>
       </c>
       <c r="B44" t="s">
@@ -3369,7 +3435,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>257</v>
       </c>
       <c r="B45" t="s">
@@ -3377,7 +3443,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>259</v>
       </c>
       <c r="B46" t="s">
@@ -3385,7 +3451,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>261</v>
       </c>
       <c r="B47" t="s">
@@ -3393,7 +3459,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>263</v>
       </c>
       <c r="B48" t="s">
@@ -3401,7 +3467,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B49" t="s">
@@ -3409,7 +3475,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B50" t="s">
@@ -3417,7 +3483,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>269</v>
       </c>
       <c r="B51" t="s">
@@ -3425,7 +3491,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B52" t="s">
@@ -3433,7 +3499,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>273</v>
       </c>
       <c r="B53" t="s">
@@ -3441,7 +3507,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B54" t="s">
@@ -3449,7 +3515,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>277</v>
       </c>
       <c r="B55" t="s">

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20864934-3D1A-8B49-B5A1-88B57A170022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5D6B5D-566E-1145-9C58-15BF78A8E6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="335">
   <si>
     <t>youtube</t>
   </si>
@@ -1274,6 +1274,24 @@
   </si>
   <si>
     <t>https://media.senscritique.com/media/000004411305/0/le_plus_gros_president_du_monde.jpg</t>
+  </si>
+  <si>
+    <t>États-Unis</t>
+  </si>
+  <si>
+    <t>Chine continentale</t>
+  </si>
+  <si>
+    <t>Kyra Buschor</t>
+  </si>
+  <si>
+    <t>Kunio Katō</t>
+  </si>
+  <si>
+    <t>La vie en vert raconte l’histoire d’un monde où la nature a presque disparu. Un petit groupe de personnages tente de redonner une place au vivant et à la végétation dans un univers devenu gris et artificiel. Le film aborde avec poésie les thèmes de l’écologie, de la protection de la nature et de l’espoir.</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYWQ3YmRiMDgtYzM2My00MmI2LTllMDgtOGViMmFhNGU5MzVhXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
   </si>
 </sst>
 </file>
@@ -2417,6 +2435,9 @@
       <c r="D121" t="s">
         <v>285</v>
       </c>
+      <c r="F121" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="122" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
@@ -2445,6 +2466,9 @@
       <c r="D123" t="s">
         <v>287</v>
       </c>
+      <c r="F123" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
@@ -2460,7 +2484,7 @@
         <v>288</v>
       </c>
       <c r="F124" t="s">
-        <v>289</v>
+        <v>329</v>
       </c>
       <c r="G124">
         <v>2014</v>
@@ -2621,6 +2645,12 @@
       <c r="C130" t="s">
         <v>200</v>
       </c>
+      <c r="E130" t="s">
+        <v>331</v>
+      </c>
+      <c r="F130" t="s">
+        <v>330</v>
+      </c>
       <c r="G130">
         <v>2019</v>
       </c>
@@ -2675,6 +2705,9 @@
       <c r="D133" t="s">
         <v>318</v>
       </c>
+      <c r="E133" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
@@ -2688,6 +2721,15 @@
       </c>
       <c r="D134" t="s">
         <v>319</v>
+      </c>
+      <c r="F134" t="s">
+        <v>299</v>
+      </c>
+      <c r="J134" t="s">
+        <v>333</v>
+      </c>
+      <c r="K134" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5D6B5D-566E-1145-9C58-15BF78A8E6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E4FC3A-55B1-CF41-B5F6-DA21CC6A751F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,28 +19,49 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$C$144</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="343">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>titre</t>
+  </si>
   <si>
     <t>youtube</t>
   </si>
   <si>
+    <t>imdb</t>
+  </si>
+  <si>
+    <t>réalisateur</t>
+  </si>
+  <si>
+    <t>pays</t>
+  </si>
+  <si>
+    <t>année</t>
+  </si>
+  <si>
+    <t>durée</t>
+  </si>
+  <si>
+    <t>genres</t>
+  </si>
+  <si>
+    <t>synopsis</t>
+  </si>
+  <si>
+    <t>adresse affiche</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
     <t>01/09/2025</t>
   </si>
   <si>
@@ -290,153 +311,491 @@
     <t>06/03/2026</t>
   </si>
   <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>28/04/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>22/05/2026</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>A cloudy lesson</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=psZmAsH6I3Q&amp;t=1s</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt12954622/</t>
+  </si>
+  <si>
     <t>Angleterre</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>12/03/2026</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>19/03/2026</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>09/04/2026</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>28/04/2026</t>
-  </si>
-  <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>04/05/2026</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>21/05/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
+    <t>Animation, Fantastique</t>
+  </si>
+  <si>
+    <t>https://pics.filmaffinity.com/a_cloudy_lesson-431584893-large.jpg</t>
+  </si>
+  <si>
+    <t>An Object at Rest</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r2kdrUDWjEk</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5062438/?ref_=fn_t_1</t>
+  </si>
+  <si>
+    <t>Animation, Drame</t>
   </si>
   <si>
     <t>28/05/2026</t>
   </si>
   <si>
+    <t>Bertie l'éléphant</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hwt1-j_n1SY?si=OKVoa5rllkueH4N-</t>
+  </si>
+  <si>
+    <t>Chris Turner &amp; Zak Boxall</t>
+  </si>
+  <si>
+    <t>5 min 20</t>
+  </si>
+  <si>
+    <t>Court, Dramatique, Poétique</t>
+  </si>
+  <si>
+    <t>Au coeur de la nuit, un jeune éléphanteau ramène un jouet perdu à sa propriétaire…</t>
+  </si>
+  <si>
+    <t>https://animationland.fr/wp-content/uploads/2017/08/bertie-éléphant-678x381.png</t>
+  </si>
+  <si>
     <t>29/05/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">
+Boite à monstre</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iSexOBHpGxE?si=IZ8ZQVLt4VlbPga2</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_1</t>
+  </si>
+  <si>
     <t>01/06/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">
+Bottle</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5mVEapKnS1c?si=O4I9bzTrHeTRVcz2</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1680060/</t>
+  </si>
+  <si>
+    <t>Animation, Romance</t>
+  </si>
+  <si>
     <t>02/06/2026</t>
   </si>
   <si>
+    <t>Cooped</t>
+  </si>
+  <si>
+    <t>https://youtu.be/p1mAcvSExCw?si=wVRjH62R_Opq46oc</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3761946/</t>
+  </si>
+  <si>
+    <t>États-Unis</t>
+  </si>
+  <si>
+    <t>Animation, Comédie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Cours de nature</t>
+  </si>
+  <si>
+    <t>https://youtu.be/T78ruBKK26w?si=IHgt9yh7hzym_iWa</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6852774/</t>
+  </si>
+  <si>
     <t>04/06/2026</t>
   </si>
   <si>
+    <t>Dust Buddies</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mZ6eeAjgSZI?si=qlOIDQNHZrd6sj8O</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6128252/?ref_=fn_t_1</t>
+  </si>
+  <si>
     <t>05/06/2026</t>
   </si>
   <si>
+    <t>Embarked</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y47-gmGvZhI?si=515qesQpwA7ZKqef</t>
+  </si>
+  <si>
+    <t>Mikel MUGICA, Adele HAWKINS, Soo Kyung KANG</t>
+  </si>
+  <si>
+    <t>4 min 23</t>
+  </si>
+  <si>
+    <t>Court métrage Animation Familial</t>
+  </si>
+  <si>
+    <t>Ah les cabanes…quel délicieux souvenir… Et quel déchirement de les quitter lorsqu’on doit déménager. A moins que… mais oui ! Tout n’est pas perdu…</t>
+  </si>
+  <si>
+    <t>https://a.ltrbxd.com/resized/film-poster/7/2/2/1/9/1/722191-embarked-0-2000-0-3000-crop.jpg?v=111200c4cd</t>
+  </si>
+  <si>
     <t>08/06/2026</t>
   </si>
   <si>
+    <t>For the birds</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WjoDEQqyTig?si=Wj17jimnCSxQgZFh</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0248808/?ref_=fn_t_1</t>
+  </si>
+  <si>
     <t>09/06/2026</t>
   </si>
   <si>
+    <t>Glace à l'eau</t>
+  </si>
+  <si>
+    <t>https://youtu.be/C7e0CqPTkrI?si=5CTAyu2E1elSJrVw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Damien Desvignes, Victor Hayé, Mathieu Barbe</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>6 min</t>
+  </si>
+  <si>
+    <t>Animation</t>
+  </si>
+  <si>
+    <t>Séparé de sa banquise, un iceberg curieux dérive au gré des courants. Il découvre alors avec crainte et surprise un monde aussi majestueux que tourmenté.</t>
+  </si>
+  <si>
+    <t>https://medias.unifrance.org/medias/124/107/224124/format_page/glace-a-l-eau.jpg</t>
+  </si>
+  <si>
+    <t>Jamais sans mon dentier</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WyCQE9XHqDA?si=OYKlJEmHIO8lx5pt</t>
+  </si>
+  <si>
+    <t>Alice Coutelle, Thomas Dibet, Hugo Favre, Eliette Gibaud, Cerise Grefferat, Guillaume Jarrosson, Thi Bich Pham et Thibault Spieser</t>
+  </si>
+  <si>
+    <t>5 min</t>
+  </si>
+  <si>
+    <t>Animation, Court, Comédie</t>
+  </si>
+  <si>
+    <t>Le combat contre l’oppression d’une bande de quatre retraités loufoques. Quatre résidents d’une maison de retraite veulent regarder leur feuilleton favori mais l’infirmière en chef leur confisque la télécommande.</t>
+  </si>
+  <si>
+    <t>https://sunread26.wordpress.com/wp-content/uploads/2024/09/jamais-sans-mon-dentier-229831.png</t>
+  </si>
+  <si>
     <t>11/06/2026</t>
   </si>
   <si>
+    <t>Jelly</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2qH442rW6F4?si=1X5CseK5uoJUY2CW</t>
+  </si>
+  <si>
+    <t>2 min 21</t>
+  </si>
+  <si>
+    <t>Un jour de beau temps, comme à son habitude, Milo joue dans la ville avec son ami. Quand soudain, au détour d’une rue, ce dernier disparaît sans laisser de trace. Milo le retrouvera-t-il ?</t>
+  </si>
+  <si>
+    <t>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B</t>
+  </si>
+  <si>
     <t>12/06/2026</t>
   </si>
   <si>
+    <t>Jour de pluie</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HQSJa-_Xopo?si=Qdtp2dLUOGIHyCHu</t>
+  </si>
+  <si>
+    <t>Kamelia CHABANE, Adrien FLANQUART, Emeric MALVAT et Benjamin TUSSIOT</t>
+  </si>
+  <si>
+    <t>7 min 33</t>
+  </si>
+  <si>
+    <t>Animation, Poétique</t>
+  </si>
+  <si>
+    <t>Dans un monde isolé ou la sècheresse perdure, un petit village survit grâce à une machine qui transforme les nuages en eau potable. Mais lorsque le nuage tant attendu arrive à proximité de la machine, la bêtise d’un villageois et de son brave compagnon effraie la précieuse source d’eau. Les deux fautifs, bien décidés à se racheter auprès des villageois, se lancent alors dans une chasse au nuage frénétique...</t>
+  </si>
+  <si>
+    <t>https://www.esma-3d.ca/wp-content/uploads/2015/12/cloudy-day-affiche-ok.jpg</t>
+  </si>
+  <si>
     <t>15/06/2026</t>
   </si>
   <si>
+    <t>Joy et la carpe chanceuse</t>
+  </si>
+  <si>
+    <t>https://youtu.be/h4wFLWJ8MG4?si=9MlqzoT9JqxRq-xT</t>
+  </si>
+  <si>
+    <t>Kyra Buschor</t>
+  </si>
+  <si>
+    <t>Chine continentale</t>
+  </si>
+  <si>
+    <t>3 min 44</t>
+  </si>
+  <si>
+    <t>Le petit chien Joy aide la petite carpe à remonter une cascade en construisant des marches dedans. À la fin, la carpe parvient à franchir la cascade en sautant et devient un dragon.</t>
+  </si>
+  <si>
+    <t>https://cdn.i.haymarketmedia.asia/?n=campaign-china%2fcontent%2fJOY_landing.png&amp;h=570&amp;w=855&amp;q=100&amp;v=20250320&amp;c=1</t>
+  </si>
+  <si>
     <t>16/06/2026</t>
   </si>
   <si>
+    <t>Joy et le Héron</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZQGuVKHtrxc?si=Sn1jDssPd73xh4Hy</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt8016566/</t>
+  </si>
+  <si>
+    <t>Knick Knack</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zgwJeG7pS9c</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0097674/</t>
+  </si>
+  <si>
     <t>18/06/2026</t>
   </si>
   <si>
+    <t>La maison en petits cubes</t>
+  </si>
+  <si>
+    <t>https://youtu.be/YUtoiyu80TM</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1361566/</t>
+  </si>
+  <si>
+    <t>Kunio Katō</t>
+  </si>
+  <si>
     <t>19/06/2026</t>
   </si>
   <si>
+    <t>La vie en vert</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SfyINYirOoA?si=N4Z5RJOtpVlFvNwZ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt9784346/</t>
+  </si>
+  <si>
+    <t>Animation, Écologie</t>
+  </si>
+  <si>
+    <t>La vie en vert raconte l’histoire d’un monde où la nature a presque disparu. Un petit groupe de personnages tente de redonner une place au vivant et à la végétation dans un univers devenu gris et artificiel. Le film aborde avec poésie les thèmes de l’écologie, de la protection de la nature et de l’espoir.</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYWQ3YmRiMDgtYzM2My00MmI2LTllMDgtOGViMmFhNGU5MzVhXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
     <t>22/06/2026</t>
   </si>
   <si>
+    <t>Le cadeau</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3XA0bB79oGc?si=mJyPELtH8LVtvXZA</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3682556/</t>
+  </si>
+  <si>
     <t>23/06/2026</t>
   </si>
   <si>
+    <t>Le complexe du hérisson</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W0f-ULXGqsE?si=ug7f8kDuS17HSIHX</t>
+  </si>
+  <si>
+    <t>Julia Robin
+Pauline Brunner
+Paul Chuop
+Chloé Goussé
+Alexandre Monge</t>
+  </si>
+  <si>
+    <t>2 min 36</t>
+  </si>
+  <si>
+    <t>Ce film traite avec humour le thème du repli sur soi en utilisant le hérisson, animal réputé peureux, comme personnage principal.</t>
+  </si>
+  <si>
+    <t>https://www.films-pour-enfants.com/films-pour-enfants/voir-film-enfant-complexe-ecole.jpg</t>
+  </si>
+  <si>
+    <t>Le plus gros président du monde</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sRWCctUzubE?si=SmgqLvu7KaJljm2r</t>
+  </si>
+  <si>
+    <t>Benjamin Renner</t>
+  </si>
+  <si>
+    <t>1 min 17</t>
+  </si>
+  <si>
+    <t>Animation, Satire</t>
+  </si>
+  <si>
+    <t>Le plus gros Président du Monde fait tout son possible pour garder la terre propre mais si personne n'y met du sien, c'est mission impossible.</t>
+  </si>
+  <si>
+    <t>https://media.senscritique.com/media/000004411305/0/le_plus_gros_president_du_monde.jpg</t>
+  </si>
+  <si>
     <t>25/06/2026</t>
   </si>
   <si>
@@ -455,94 +814,245 @@
     <t>03/07/2026</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=psZmAsH6I3Q&amp;t=1s</t>
-  </si>
-  <si>
-    <t>réalisateur</t>
-  </si>
-  <si>
-    <t>durée</t>
-  </si>
-  <si>
-    <t>imdb</t>
-  </si>
-  <si>
-    <t>pays</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt12954622/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt5062438/?ref_=fn_t_1</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=r2kdrUDWjEk</t>
-  </si>
-  <si>
-    <t>année</t>
-  </si>
-  <si>
-    <t>genres</t>
-  </si>
-  <si>
-    <t>synopsis</t>
-  </si>
-  <si>
-    <t>adresse affiche</t>
-  </si>
-  <si>
-    <t>https://pics.filmaffinity.com/a_cloudy_lesson-431584893-large.jpg</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iSexOBHpGxE?si=V5QOjq-1kCJu6_Ab</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_2</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_3</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_4</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_5</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_6</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_7</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_8</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_9</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_10</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_11</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_12</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_13</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_0</t>
-  </si>
-  <si>
-    <t>questions</t>
+    <t xml:space="preserve">Qestion 1 : Qui sont les deux personnages ?
+a. Un grand-père et son petit fil 
+b. Un grand-père et sa petite fille 
+c. Un grand-père et son fils
+Qestion 2 : Que se passe-t-il lorsque le grand-père souffle dans le cercle ?
+a. Il en sort un génie
+b. Il en sort une énorme bulle
+c. Il en sort un gros nuage
+Qestion 3 : Que se passe-t-il lorsque c’est l’autre personnage qui souffle ?
+a. Il ne se passe rien
+b. Le cercle s'envole
+c. Il crache à l'intérieur
+Qestion 4 : Que se passe-t-il ensuite ?
+a. Il abîme le cercle
+b. Il arrive à utiliser le cercle
+c. Il jette le cercle
+Qestion 5 : Que décide-t-il alors ?
+a. De créer de nouvelles formes pour les nuages
+b. De demander au grand-père de lui expliquer encore
+c. De partir très loin
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qestion 1 : C’est l’histoire…
+a. D’une étoile 
+b. D’une rivière 
+c. D’une montagne
+Qestion 2 : Que se passe-t-il pendant qu’elle dort ?
+a. Une catastrophe se produit
+b. Le temps passe
+c. Les dinosaures détruisent tout
+Qestion 3 : Quand elle se réveille, que s’est-il passé ?
+a. Elle a rétréci
+b. Elle n’existe plus
+c. Elle s’est agrandie
+Qestion 4 : A quoi n’est-elle pas utilisée ?
+a. A faire un boulet de canon
+b. A faire un moulin à eau
+c. IA faire une table
+Qestion 5 : Que décide-t-il alors ?
+a. Elle n’existe plus
+b. Elle devient un grain de sable
+c. Elle redevient montagne
+</t>
+  </si>
+  <si>
+    <t>Etats-Unis</t>
+  </si>
+  <si>
+    <t>Les chaussures de Louis</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eIWyHjVPas0?si=dbzlzEg46XB72ruC</t>
+  </si>
+  <si>
+    <t>Les lettres qui tombent</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EQ71vgRzCA4?si=5ADvSg5sBy68e8Go</t>
+  </si>
+  <si>
+    <t>Les pyramides d'Egypte</t>
+  </si>
+  <si>
+    <t>https://youtu.be/j6PbonHsqW0?si=NXgNJtYDfaHQgqCF</t>
+  </si>
+  <si>
+    <t>Lily et le bonhomme de neige</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FCF-rNMLVpE?si=4Lhp3tqQ9bsSfd8d</t>
+  </si>
+  <si>
+    <t>Lost Property</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qwMe-Z87OZ0?si=Sua6_509LWN0t7FD</t>
+  </si>
+  <si>
+    <t>Lumière</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hdyAFuHRayQ?si=JFeJtTAKmZItzmgV</t>
+  </si>
+  <si>
+    <t>Lunette</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eviPBToWpP4?si=-m1_uRMYQ-WVE98k</t>
+  </si>
+  <si>
+    <t>Migrants</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ugPJi8kMK8Q?si=a5d3bzrg1ThCGHIS</t>
+  </si>
+  <si>
+    <t>Mon petit frère de la lune</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GfGbfLuBQAY?si=VP7vEv7OmdsC2yBA</t>
+  </si>
+  <si>
+    <t>Monkey Symphony</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9CZmq-RJvoI?si=sIlcxul5NWSTfqXT</t>
+  </si>
+  <si>
+    <t>Mr Hublot</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=j2-DJacGz8Y</t>
+  </si>
+  <si>
+    <t>One man band</t>
+  </si>
+  <si>
+    <t>https://youtu.be/454nNoD6-TI?si=Mymkt5ar5KWb4sWy</t>
+  </si>
+  <si>
+    <t>One upon a blue moon</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rIX2eUvZiro?si=1mVsSAiwN6qUCYrY</t>
+  </si>
+  <si>
+    <t>Pip</t>
+  </si>
+  <si>
+    <t>https://youtu.be/07d2dXHYb94?si=RoPl4avSi4Yx4gVQ</t>
+  </si>
+  <si>
+    <t>Quantum Jump</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FVNJFBI0b-g?si=3sCNCTNuL4qxOO4Z</t>
+  </si>
+  <si>
+    <t>Rituel</t>
+  </si>
+  <si>
+    <t>https://youtu.be/QADYuPXfrxM?si=iuxuvdzCfvsKFzk9</t>
+  </si>
+  <si>
+    <t>Rubato</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1D7D3_HFB3o?si=0_RDZ2Vscdipqs9C</t>
+  </si>
+  <si>
+    <t>Sans Gravité</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vX77zcKiN98?si=AiGeBdNGKCrrtI8q</t>
+  </si>
+  <si>
+    <t>Sapling</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fmLDta7pMs8?si=xTImfs-m_kc2OWcv</t>
+  </si>
+  <si>
+    <t>Snack Attack</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6YSxJnqCr8I</t>
+  </si>
+  <si>
+    <t>Soar</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UUlaseGrkLc?si=HWZHUUNiAlhalk09</t>
+  </si>
+  <si>
+    <t>SpellBound</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TuNdTpjXkJ0?si=bXUMJ-zn86x8h7r0</t>
+  </si>
+  <si>
+    <t>Sweet Cocoon</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yQ1ZcNpbwOA?si=iXUYgh1Kt0nb7gV9</t>
+  </si>
+  <si>
+    <t>The Misguided Monk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mQQ3BdjCc4I?si=HadQCgmFvrogCLCA</t>
+  </si>
+  <si>
+    <t>The monk and the fly</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4cywWIPoqko?si=TDclT7XZ5M3ERr5r</t>
+  </si>
+  <si>
+    <t>The mountain king</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UQsB3W6Eciw?si=2l3hNmwMLJhvq-Yy</t>
+  </si>
+  <si>
+    <t>The song for rain</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pBB1-UVCzPo?si=0-ct6AcKLfo_v0Ai</t>
+  </si>
+  <si>
+    <t>The Wishgranter</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zON0wDD7VJY?si=wMbL-LS5_FEd6Hlz</t>
+  </si>
+  <si>
+    <t>Tuurngait</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XaI-nEN2DRE?si=QDVJDhvNAG6XQPD6</t>
+  </si>
+  <si>
+    <t>Un carré pour la biodiversité</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wGm97ppSM3w?si=pkX65PY3fDJEs_c1</t>
+  </si>
+  <si>
+    <t>Vagabond</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7k7rCTP-sOI?si=8A3CtJF_CLXdQsjM</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CfAWTuE9psE?si=Him0sQMqAkuz2JRW</t>
   </si>
   <si>
     <t>Qestion 1 : Ceci est un test de questions
@@ -553,752 +1063,56 @@
 Qestion 1 : Ceci est un test de questions</t>
   </si>
   <si>
-    <t>A cloudy lesson</t>
-  </si>
-  <si>
-    <t>titre</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t>Qestion 1 : Qui sont les deux personnages ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-a. Un grand-père et son petit fil 
-b. Un grand-père et sa petite fille 
-c. Un grand-père et son fils
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 2 : Que se passe-t-il lorsque le grand-père souffle dans le cercle ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. Il en sort un génie
-b. Il en sort une énorme bulle
-c. Il en sort un gros nuage
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 3 : Que se passe-t-il lorsque c’est l’autre personnage qui souffle ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. Il ne se passe rien
-b. Le cercle s'envole
-c. Il crache à l'intérieur
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t>Qestion 4 : Que se passe-t-il ensuite ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-a. Il abîme le cercle
-b. Il arrive à utiliser le cercle
-c. Il jette le cercle
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 5 : Que décide-t-il alors ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. De créer de nouvelles formes pour les nuages
-b. De demander au grand-père de lui expliquer encore
-c. De partir très loin
-</t>
-    </r>
-  </si>
-  <si>
-    <t>An Object at Rest</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t>Qestion 1 : C’est l’histoire…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-a. D’une étoile 
-b. D’une rivière 
-c. D’une montagne
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 2 : Que se passe-t-il pendant qu’elle dort ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. Une catastrophe se produit
-b. Le temps passe
-c. Les dinosaures détruisent tout
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 3 : Quand elle se réveille, que s’est-il passé ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. Elle a rétréci
-b. Elle n’existe plus
-c. Elle s’est agrandie
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t>Qestion 4 : A quoi n’est-elle pas utilisée ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-a. A faire un boulet de canon
-b. A faire un moulin à eau
-c. IA faire une table
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Corps)"/>
-      </rPr>
-      <t xml:space="preserve">Qestion 5 : Que décide-t-il alors ?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a. Elle n’existe plus
-b. Elle devient un grain de sable
-c. Elle redevient montagne
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Bertie l'éléphant</t>
-  </si>
-  <si>
-    <t>https://youtu.be/hwt1-j_n1SY?si=OKVoa5rllkueH4N-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Boite à monstre</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iSexOBHpGxE?si=IZ8ZQVLt4VlbPga2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Bottle</t>
-  </si>
-  <si>
-    <t>https://youtu.be/5mVEapKnS1c?si=O4I9bzTrHeTRVcz2</t>
-  </si>
-  <si>
-    <t>Cooped</t>
-  </si>
-  <si>
-    <t>https://youtu.be/p1mAcvSExCw?si=wVRjH62R_Opq46oc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Cours de nature</t>
-  </si>
-  <si>
-    <t>https://youtu.be/T78ruBKK26w?si=IHgt9yh7hzym_iWa</t>
-  </si>
-  <si>
-    <t>Dust Buddies</t>
-  </si>
-  <si>
-    <t>https://youtu.be/mZ6eeAjgSZI?si=qlOIDQNHZrd6sj8O</t>
-  </si>
-  <si>
-    <t>Embarked</t>
-  </si>
-  <si>
-    <t>https://youtu.be/y47-gmGvZhI?si=515qesQpwA7ZKqef</t>
-  </si>
-  <si>
-    <t>For the birds</t>
-  </si>
-  <si>
-    <t>https://youtu.be/WjoDEQqyTig?si=Wj17jimnCSxQgZFh</t>
-  </si>
-  <si>
-    <t>Glace à l'eau</t>
-  </si>
-  <si>
-    <t>https://youtu.be/C7e0CqPTkrI?si=5CTAyu2E1elSJrVw</t>
-  </si>
-  <si>
-    <t>Jamais sans mon dentier</t>
-  </si>
-  <si>
-    <t>https://youtu.be/WyCQE9XHqDA?si=OYKlJEmHIO8lx5pt</t>
-  </si>
-  <si>
-    <t>Jelly</t>
-  </si>
-  <si>
-    <t>https://youtu.be/2qH442rW6F4?si=1X5CseK5uoJUY2CW</t>
-  </si>
-  <si>
-    <t>Jour de pluie</t>
-  </si>
-  <si>
-    <t>https://youtu.be/HQSJa-_Xopo?si=Qdtp2dLUOGIHyCHu</t>
-  </si>
-  <si>
-    <t>Joy et la carpe chanceuse</t>
-  </si>
-  <si>
-    <t>https://youtu.be/h4wFLWJ8MG4?si=9MlqzoT9JqxRq-xT</t>
-  </si>
-  <si>
-    <t>Joy et le Héron</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ZQGuVKHtrxc?si=Sn1jDssPd73xh4Hy</t>
-  </si>
-  <si>
-    <t>Knick Knack</t>
-  </si>
-  <si>
-    <t>https://youtu.be/zgwJeG7pS9c</t>
-  </si>
-  <si>
-    <t>La maison en petits cubes</t>
-  </si>
-  <si>
-    <t>https://youtu.be/YUtoiyu80TM</t>
-  </si>
-  <si>
-    <t>La vie en vert</t>
-  </si>
-  <si>
-    <t>https://youtu.be/SfyINYirOoA?si=N4Z5RJOtpVlFvNwZ</t>
-  </si>
-  <si>
-    <t>Le cadeau</t>
-  </si>
-  <si>
-    <t>https://youtu.be/3XA0bB79oGc?si=mJyPELtH8LVtvXZA</t>
-  </si>
-  <si>
-    <t>Le complexe du hérisson</t>
-  </si>
-  <si>
-    <t>https://youtu.be/W0f-ULXGqsE?si=ug7f8kDuS17HSIHX</t>
-  </si>
-  <si>
-    <t>Le plus gros président du monde</t>
-  </si>
-  <si>
-    <t>https://youtu.be/sRWCctUzubE?si=SmgqLvu7KaJljm2r</t>
-  </si>
-  <si>
-    <t>Les chaussures de Louis</t>
-  </si>
-  <si>
-    <t>https://youtu.be/eIWyHjVPas0?si=dbzlzEg46XB72ruC</t>
-  </si>
-  <si>
-    <t>Les lettres qui tombent</t>
-  </si>
-  <si>
-    <t>https://youtu.be/EQ71vgRzCA4?si=5ADvSg5sBy68e8Go</t>
-  </si>
-  <si>
-    <t>Les pyramides d'Egypte</t>
-  </si>
-  <si>
-    <t>https://youtu.be/j6PbonHsqW0?si=NXgNJtYDfaHQgqCF</t>
-  </si>
-  <si>
-    <t>Lily et le bonhomme de neige</t>
-  </si>
-  <si>
-    <t>https://youtu.be/FCF-rNMLVpE?si=4Lhp3tqQ9bsSfd8d</t>
-  </si>
-  <si>
-    <t>Lost Property</t>
-  </si>
-  <si>
-    <t>https://youtu.be/qwMe-Z87OZ0?si=Sua6_509LWN0t7FD</t>
-  </si>
-  <si>
-    <t>Lumière</t>
-  </si>
-  <si>
-    <t>https://youtu.be/hdyAFuHRayQ?si=JFeJtTAKmZItzmgV</t>
-  </si>
-  <si>
-    <t>Lunette</t>
-  </si>
-  <si>
-    <t>https://youtu.be/eviPBToWpP4?si=-m1_uRMYQ-WVE98k</t>
-  </si>
-  <si>
-    <t>Migrants</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ugPJi8kMK8Q?si=a5d3bzrg1ThCGHIS</t>
-  </si>
-  <si>
-    <t>Mon petit frère de la lune</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GfGbfLuBQAY?si=VP7vEv7OmdsC2yBA</t>
-  </si>
-  <si>
-    <t>Monkey Symphony</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9CZmq-RJvoI?si=sIlcxul5NWSTfqXT</t>
-  </si>
-  <si>
-    <t>Mr Hublot</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=j2-DJacGz8Y</t>
-  </si>
-  <si>
-    <t>One man band</t>
-  </si>
-  <si>
-    <t>https://youtu.be/454nNoD6-TI?si=Mymkt5ar5KWb4sWy</t>
-  </si>
-  <si>
-    <t>One upon a blue moon</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rIX2eUvZiro?si=1mVsSAiwN6qUCYrY</t>
-  </si>
-  <si>
-    <t>Pip</t>
-  </si>
-  <si>
-    <t>https://youtu.be/07d2dXHYb94?si=RoPl4avSi4Yx4gVQ</t>
-  </si>
-  <si>
-    <t>Quantum Jump</t>
-  </si>
-  <si>
-    <t>https://youtu.be/FVNJFBI0b-g?si=3sCNCTNuL4qxOO4Z</t>
-  </si>
-  <si>
-    <t>Rituel</t>
-  </si>
-  <si>
-    <t>https://youtu.be/QADYuPXfrxM?si=iuxuvdzCfvsKFzk9</t>
-  </si>
-  <si>
-    <t>Rubato</t>
-  </si>
-  <si>
-    <t>https://youtu.be/1D7D3_HFB3o?si=0_RDZ2Vscdipqs9C</t>
-  </si>
-  <si>
-    <t>Sans Gravité</t>
-  </si>
-  <si>
-    <t>https://youtu.be/vX77zcKiN98?si=AiGeBdNGKCrrtI8q</t>
-  </si>
-  <si>
-    <t>Sapling</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fmLDta7pMs8?si=xTImfs-m_kc2OWcv</t>
-  </si>
-  <si>
-    <t>Snack Attack</t>
-  </si>
-  <si>
-    <t>https://youtu.be/6YSxJnqCr8I</t>
-  </si>
-  <si>
-    <t>Soar</t>
-  </si>
-  <si>
-    <t>https://youtu.be/UUlaseGrkLc?si=HWZHUUNiAlhalk09</t>
-  </si>
-  <si>
-    <t>SpellBound</t>
-  </si>
-  <si>
-    <t>https://youtu.be/TuNdTpjXkJ0?si=bXUMJ-zn86x8h7r0</t>
-  </si>
-  <si>
-    <t>Sweet Cocoon</t>
-  </si>
-  <si>
-    <t>https://youtu.be/yQ1ZcNpbwOA?si=iXUYgh1Kt0nb7gV9</t>
-  </si>
-  <si>
-    <t>The Misguided Monk</t>
-  </si>
-  <si>
-    <t>https://youtu.be/mQQ3BdjCc4I?si=HadQCgmFvrogCLCA</t>
-  </si>
-  <si>
-    <t>The monk and the fly</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4cywWIPoqko?si=TDclT7XZ5M3ERr5r</t>
-  </si>
-  <si>
-    <t>The mountain king</t>
-  </si>
-  <si>
-    <t>https://youtu.be/UQsB3W6Eciw?si=2l3hNmwMLJhvq-Yy</t>
-  </si>
-  <si>
-    <t>The song for rain</t>
-  </si>
-  <si>
-    <t>https://youtu.be/pBB1-UVCzPo?si=0-ct6AcKLfo_v0Ai</t>
-  </si>
-  <si>
-    <t>The Wishgranter</t>
-  </si>
-  <si>
-    <t>https://youtu.be/zON0wDD7VJY?si=wMbL-LS5_FEd6Hlz</t>
-  </si>
-  <si>
-    <t>Tuurngait</t>
-  </si>
-  <si>
-    <t>https://youtu.be/XaI-nEN2DRE?si=QDVJDhvNAG6XQPD6</t>
-  </si>
-  <si>
-    <t>Un carré pour la biodiversité</t>
-  </si>
-  <si>
-    <t>https://youtu.be/wGm97ppSM3w?si=pkX65PY3fDJEs_c1</t>
-  </si>
-  <si>
-    <t>Vagabond</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7k7rCTP-sOI?si=8A3CtJF_CLXdQsjM</t>
-  </si>
-  <si>
-    <t>Wild</t>
-  </si>
-  <si>
-    <t>https://youtu.be/CfAWTuE9psE?si=Him0sQMqAkuz2JRW</t>
-  </si>
-  <si>
-    <t>Au coeur de la nuit, un jeune éléphanteau ramène un jouet perdu à sa propriétaire…</t>
-  </si>
-  <si>
-    <t>https://animationland.fr/wp-content/uploads/2017/08/bertie-éléphant-678x381.png</t>
-  </si>
-  <si>
-    <t>Chris Turner &amp; Zak Boxall</t>
-  </si>
-  <si>
-    <t>5 min 20</t>
-  </si>
-  <si>
-    <t>Court, Dramatique, Poétique</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt1680060/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt3761946/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt6852774/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt6128252/?ref_=fn_t_1</t>
-  </si>
-  <si>
-    <t>Mikel MUGICA, Adele HAWKINS, Soo Kyung KANG</t>
-  </si>
-  <si>
-    <t>Etats-Unis</t>
-  </si>
-  <si>
-    <t>4 min 23</t>
-  </si>
-  <si>
-    <t>Court métrage Animation Familial</t>
-  </si>
-  <si>
-    <t>Ah les cabanes…quel délicieux souvenir… Et quel déchirement de les quitter lorsqu’on doit déménager. A moins que… mais oui ! Tout n’est pas perdu…</t>
-  </si>
-  <si>
-    <t>https://a.ltrbxd.com/resized/film-poster/7/2/2/1/9/1/722191-embarked-0-2000-0-3000-crop.jpg?v=111200c4cd</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt0248808/?ref_=fn_t_1</t>
-  </si>
-  <si>
-    <t>https://medias.unifrance.org/medias/124/107/224124/format_page/glace-a-l-eau.jpg</t>
-  </si>
-  <si>
-    <t>Animation</t>
-  </si>
-  <si>
-    <t>Séparé de sa banquise, un iceberg curieux dérive au gré des courants. Il découvre alors avec crainte et surprise un monde aussi majestueux que tourmenté.</t>
-  </si>
-  <si>
-    <t>6 min</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Damien Desvignes, Victor Hayé, Mathieu Barbe</t>
-  </si>
-  <si>
-    <t>Le combat contre l’oppression d’une bande de quatre retraités loufoques. Quatre résidents d’une maison de retraite veulent regarder leur feuilleton favori mais l’infirmière en chef leur confisque la télécommande.</t>
-  </si>
-  <si>
-    <t>5 min</t>
-  </si>
-  <si>
-    <t>Alice Coutelle, Thomas Dibet, Hugo Favre, Eliette Gibaud, Cerise Grefferat, Guillaume Jarrosson, Thi Bich Pham et Thibault Spieser</t>
-  </si>
-  <si>
-    <t>Animation, Court, Comédie</t>
-  </si>
-  <si>
-    <t>https://sunread26.wordpress.com/wp-content/uploads/2024/09/jamais-sans-mon-dentier-229831.png</t>
-  </si>
-  <si>
-    <t>Un jour de beau temps, comme à son habitude, Milo joue dans la ville avec son ami. Quand soudain, au détour d’une rue, ce dernier disparaît sans laisser de trace. Milo le retrouvera-t-il ?</t>
-  </si>
-  <si>
-    <t>2 min 21</t>
-  </si>
-  <si>
-    <t>https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B</t>
-  </si>
-  <si>
-    <t>https://www.esma-3d.ca/wp-content/uploads/2015/12/cloudy-day-affiche-ok.jpg</t>
-  </si>
-  <si>
-    <t>Kamelia CHABANE, Adrien FLANQUART, Emeric MALVAT et Benjamin TUSSIOT</t>
-  </si>
-  <si>
-    <t>7 min 33</t>
-  </si>
-  <si>
-    <t>Dans un monde isolé ou la sècheresse perdure, un petit village survit grâce à une machine qui transforme les nuages en eau potable. Mais lorsque le nuage tant attendu arrive à proximité de la machine, la bêtise d’un villageois et de son brave compagnon effraie la précieuse source d’eau. Les deux fautifs, bien décidés à se racheter auprès des villageois, se lancent alors dans une chasse au nuage frénétique...</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt8016566/</t>
-  </si>
-  <si>
-    <t>3 min 44</t>
-  </si>
-  <si>
-    <t>Le petit chien Joy aide la petite carpe à remonter une cascade en construisant des marches dedans. À la fin, la carpe parvient à franchir la cascade en sautant et devient un dragon.</t>
-  </si>
-  <si>
-    <t>https://cdn.i.haymarketmedia.asia/?n=campaign-china%2fcontent%2fJOY_landing.png&amp;h=570&amp;w=855&amp;q=100&amp;v=20250320&amp;c=1</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt0097674/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt1361566/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt9784346/</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt3682556/</t>
-  </si>
-  <si>
-    <t>Julia Robin
-Pauline Brunner
-Paul Chuop
-Chloé Goussé
-Alexandre Monge</t>
-  </si>
-  <si>
-    <t>2 min 36</t>
-  </si>
-  <si>
-    <t>Ce film traite avec humour le thème du repli sur soi en utilisant le hérisson, animal réputé peureux, comme personnage principal.</t>
-  </si>
-  <si>
-    <t>https://www.films-pour-enfants.com/films-pour-enfants/voir-film-enfant-complexe-ecole.jpg</t>
-  </si>
-  <si>
-    <t>Benjamin Renner</t>
-  </si>
-  <si>
-    <t>1 min 17</t>
-  </si>
-  <si>
-    <t>Le plus gros Président du Monde fait tout son possible pour garder la terre propre mais si personne n'y met du sien, c'est mission impossible.</t>
-  </si>
-  <si>
-    <t>https://media.senscritique.com/media/000004411305/0/le_plus_gros_president_du_monde.jpg</t>
-  </si>
-  <si>
-    <t>États-Unis</t>
-  </si>
-  <si>
-    <t>Chine continentale</t>
-  </si>
-  <si>
-    <t>Kyra Buschor</t>
-  </si>
-  <si>
-    <t>Kunio Katō</t>
-  </si>
-  <si>
-    <t>La vie en vert raconte l’histoire d’un monde où la nature a presque disparu. Un petit groupe de personnages tente de redonner une place au vivant et à la végétation dans un univers devenu gris et artificiel. Le film aborde avec poésie les thèmes de l’écologie, de la protection de la nature et de l’espoir.</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/M/MV5BYWQ3YmRiMDgtYzM2My00MmI2LTllMDgtOGViMmFhNGU5MzVhXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+    <t>https://youtu.be/iSexOBHpGxE?si=V5QOjq-1kCJu6_Ab</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_0</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_2</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_3</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_4</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_5</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_6</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_7</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_8</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_9</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_10</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_11</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_12</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_13</t>
+  </si>
+  <si>
+    <t>Court, Animation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1313,19 +1127,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri (Corps)"/>
     </font>
     <font>
       <b/>
@@ -1355,7 +1156,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1363,7 +1164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1714,638 +1515,642 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14.83203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
     <col min="12" max="12" width="80.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>150</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D111" s="1"/>
       <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L112" s="2"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="F116" t="s">
-        <v>84</v>
+        <v>130</v>
+      </c>
+      <c r="I116" t="s">
+        <v>131</v>
       </c>
       <c r="K116" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -2353,199 +2158,220 @@
         <v>46169</v>
       </c>
       <c r="B117" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>135</v>
+      </c>
+      <c r="I117" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="C118" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="E118" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="F118" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="G118">
         <v>2016</v>
       </c>
       <c r="H118" t="s">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="I118" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="J118" t="s">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C119" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="D119" t="s">
+        <v>148</v>
+      </c>
+      <c r="I119" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C120" t="s">
+        <v>151</v>
+      </c>
+      <c r="D120" t="s">
+        <v>152</v>
+      </c>
+      <c r="I120" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C120" t="s">
-        <v>180</v>
-      </c>
-      <c r="D120" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="B121" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
-        <v>285</v>
+        <v>157</v>
       </c>
       <c r="F121" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="I121" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>46176</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C122" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="D122" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+      <c r="I122" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D123" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
       <c r="F123" t="s">
-        <v>329</v>
+        <v>158</v>
+      </c>
+      <c r="I123" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C124" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E124" t="s">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="F124" t="s">
-        <v>329</v>
+        <v>158</v>
       </c>
       <c r="G124">
         <v>2014</v>
       </c>
       <c r="H124" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="I124" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="J124" t="s">
-        <v>292</v>
+        <v>173</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>293</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C125" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D125" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="I125" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C126" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="F126" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G126">
         <v>2019</v>
       </c>
       <c r="H126" t="s">
-        <v>298</v>
+        <v>184</v>
       </c>
       <c r="I126" t="s">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="J126" t="s">
-        <v>297</v>
+        <v>186</v>
       </c>
       <c r="K126" t="s">
-        <v>295</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -2553,129 +2379,141 @@
         <v>46183</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C127" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E127" t="s">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G127">
         <v>2016</v>
       </c>
       <c r="H127" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="I127" t="s">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="J127" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>305</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F128" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G128">
         <v>2018</v>
       </c>
       <c r="H128" t="s">
-        <v>307</v>
+        <v>198</v>
+      </c>
+      <c r="I128" t="s">
+        <v>131</v>
       </c>
       <c r="J128" t="s">
-        <v>306</v>
+        <v>199</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C129" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E129" t="s">
-        <v>310</v>
+        <v>204</v>
       </c>
       <c r="F129" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G129">
         <v>2009</v>
       </c>
       <c r="H129" t="s">
-        <v>311</v>
+        <v>205</v>
+      </c>
+      <c r="I129" t="s">
+        <v>206</v>
       </c>
       <c r="J129" t="s">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="K129" t="s">
-        <v>309</v>
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C130" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E130" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="F130" t="s">
-        <v>330</v>
+        <v>213</v>
       </c>
       <c r="G130">
         <v>2019</v>
       </c>
       <c r="H130" t="s">
-        <v>314</v>
+        <v>214</v>
+      </c>
+      <c r="I130" t="s">
+        <v>131</v>
       </c>
       <c r="J130" t="s">
-        <v>315</v>
+        <v>215</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C131" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D131" t="s">
-        <v>313</v>
+        <v>220</v>
+      </c>
+      <c r="I131" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
@@ -2683,96 +2521,111 @@
         <v>46190</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C132" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D132" t="s">
-        <v>317</v>
+        <v>223</v>
+      </c>
+      <c r="I132" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C133" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="D133" t="s">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="E133" t="s">
-        <v>332</v>
+        <v>228</v>
+      </c>
+      <c r="I133" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C134" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="D134" t="s">
-        <v>319</v>
+        <v>232</v>
       </c>
       <c r="F134" t="s">
-        <v>299</v>
+        <v>183</v>
+      </c>
+      <c r="I134" t="s">
+        <v>233</v>
       </c>
       <c r="J134" t="s">
-        <v>333</v>
+        <v>234</v>
       </c>
       <c r="K134" t="s">
-        <v>334</v>
+        <v>235</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C135" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="D135" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+      <c r="I135" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="C136" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="F136" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G136">
         <v>2013</v>
       </c>
       <c r="H136" t="s">
-        <v>322</v>
+        <v>244</v>
+      </c>
+      <c r="I136" t="s">
+        <v>159</v>
       </c>
       <c r="J136" t="s">
-        <v>323</v>
+        <v>245</v>
       </c>
       <c r="K136" t="s">
-        <v>324</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
@@ -2780,48 +2633,51 @@
         <v>46197</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="C137" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="E137" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="F137" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="G137">
         <v>2006</v>
       </c>
       <c r="H137" t="s">
-        <v>326</v>
+        <v>250</v>
+      </c>
+      <c r="I137" t="s">
+        <v>251</v>
       </c>
       <c r="J137" t="s">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="K137" t="s">
-        <v>328</v>
+        <v>253</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>135</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>136</v>
+        <v>257</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -2832,12 +2688,12 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>137</v>
+        <v>258</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.2">
@@ -2850,29 +2706,25 @@
       <c r="C148" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C144" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:C144" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C144">
       <sortCondition ref="A1:A144"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K128" r:id="rId1" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{9C2E73AE-51D1-2B4A-BA62-E465D8CB2D3A}"/>
-    <hyperlink ref="K127" r:id="rId2" xr:uid="{7C54B1D5-5C31-3844-8D87-78C42AF1B71A}"/>
-    <hyperlink ref="K124" r:id="rId3" xr:uid="{8AD0B3A6-A358-4445-9976-D6A2F5CE179B}"/>
-    <hyperlink ref="D116" r:id="rId4" xr:uid="{69E8C45A-892E-9B43-8A15-017EDB8C8A51}"/>
-    <hyperlink ref="K130" r:id="rId5" xr:uid="{2AB0365A-EC68-944C-B59E-728AAE3E821A}"/>
+    <hyperlink ref="D116" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K124" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K127" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K128" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K130" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <ignoredErrors>
-    <ignoredError sqref="C1" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB1CDA6-09BE-5D45-B63F-1135F97788C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2883,852 +2735,852 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="J2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>2016</v>
       </c>
       <c r="G4" t="s">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="H4" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="F10">
         <v>2014</v>
       </c>
       <c r="G10" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>292</v>
+        <v>173</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>293</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="E12" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F12">
         <v>2019</v>
       </c>
       <c r="G12" t="s">
-        <v>298</v>
+        <v>184</v>
       </c>
       <c r="H12" t="s">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="I12" t="s">
-        <v>297</v>
+        <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>295</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F13">
         <v>2016</v>
       </c>
       <c r="G13" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="H13" t="s">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="I13" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>305</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E14" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F14">
         <v>2018</v>
       </c>
       <c r="G14" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="I14" t="s">
-        <v>306</v>
+        <v>199</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>204</v>
       </c>
       <c r="E15" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F15">
         <v>2009</v>
       </c>
       <c r="G15" t="s">
-        <v>311</v>
+        <v>205</v>
       </c>
       <c r="I15" t="s">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="J15" t="s">
-        <v>309</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F16">
         <v>2019</v>
       </c>
       <c r="G16" t="s">
-        <v>314</v>
+        <v>214</v>
       </c>
       <c r="I16" t="s">
-        <v>315</v>
+        <v>215</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C19" t="s">
-        <v>318</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C20" t="s">
-        <v>319</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F22">
         <v>2013</v>
       </c>
       <c r="G22" t="s">
-        <v>322</v>
+        <v>244</v>
       </c>
       <c r="I22" t="s">
-        <v>323</v>
+        <v>245</v>
       </c>
       <c r="J22" t="s">
-        <v>324</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="D23" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="E23" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="F23">
         <v>2006</v>
       </c>
       <c r="G23" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="I23" t="s">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="J23" t="s">
-        <v>328</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s">
-        <v>230</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>231</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s">
-        <v>244</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>251</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s">
-        <v>252</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="B47" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="B55" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E111" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="J111" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>169</v>
+        <v>327</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C113" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C114" t="s">
-        <v>167</v>
+        <v>329</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C115" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C116" t="s">
-        <v>155</v>
+        <v>330</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C117" t="s">
-        <v>156</v>
+        <v>331</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C118" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C119" t="s">
-        <v>158</v>
+        <v>333</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C120" t="s">
-        <v>159</v>
+        <v>334</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C121" t="s">
-        <v>160</v>
+        <v>335</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C122" t="s">
-        <v>161</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C123" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C125" t="s">
-        <v>164</v>
+        <v>339</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C126" t="s">
-        <v>165</v>
+        <v>340</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="C127" t="s">
-        <v>166</v>
+        <v>341</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E133" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="J133" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
@@ -3742,12 +3594,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C111" r:id="rId1" xr:uid="{EF232C5C-7DEE-DD4F-AC35-CB0C609B2391}"/>
-    <hyperlink ref="J14" r:id="rId2" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{A3508436-8B84-B841-A9AE-76F0AAA56E41}"/>
-    <hyperlink ref="J13" r:id="rId3" xr:uid="{99B30D0E-1247-EF46-A4E0-D9F00B0EF7CE}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{337919EE-DEC5-6546-97F1-E7C147633C5A}"/>
-    <hyperlink ref="C2" r:id="rId5" xr:uid="{8C67ACDC-62EC-AE4D-87F2-B889684A86E0}"/>
-    <hyperlink ref="J16" r:id="rId6" xr:uid="{BBE60714-FB11-044B-B3A1-A300C0F3490C}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="J10" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="J13" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="J14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="J16" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="C111" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E4FC3A-55B1-CF41-B5F6-DA21CC6A751F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD388747-A123-1048-B04E-8EF27DFED198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$C$144</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="362">
   <si>
     <t>date</t>
   </si>
@@ -1107,12 +1120,69 @@
   <si>
     <t>Court, Animation</t>
   </si>
+  <si>
+    <t>https://youtu.be/eIWyHjVPas0?si=wRqiC6W9YYxWuW9s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EQ71vgRzCA4?si=cizNMfHpgyhWK1Cu</t>
+  </si>
+  <si>
+    <t>https://youtu.be/j6PbonHsqW0?si=5Zan8upFUJo2GEww</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FCF-rNMLVpE?si=3injAi32eTl8juFB</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qwMe-Z87OZ0?si=b5FawhF6lSAEnrmv</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hdyAFuHRayQ?si=a0YtPd-CF2n0ssqX</t>
+  </si>
+  <si>
+    <t>https://youtu.be/eviPBToWpP4?si=EskY_2YtYWNz-r0l</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt16287242/?ref_=nv_sr_srsg_0_tt_8_nm_0_in_0_q_Les%20chaussures%20de%20Louis</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3711876/?ref_=nv_sr_srsg_0_tt_1_nm_0_in_0_q_Bokstavsbarn</t>
+  </si>
+  <si>
+    <t>https://media.senscritique.com/media/000018433232/0/falling_letters.jpg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt4800364/?ref_=nv_sr_srsg_0_tt_3_nm_0_in_0_q_Les%20pyramides%20d%27Egypte</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6057856/?ref_=nv_sr_srsg_0_tt_5_nm_3_in_0_q_%20Lily%20and%20The%20Snowman</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3689006/?ref_=nv_sr_srsg_3_tt_8_nm_0_in_0_q_Lost%20Property</t>
+  </si>
+  <si>
+    <t>The Light Team</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>3 min 23</t>
+  </si>
+  <si>
+    <t>Dans un monde plongé dans l’obscurité, une petite créature découvre une mystérieuse source de lumière. Fasciné par cette découverte, il cherche à partager cette lumière avec les autres, mais devra faire face à la peur, à la curiosité et aux réactions du monde qui l’entoure. Ce court métrage aborde avec poésie les thèmes du progrès, du partage et de l’espoir.</t>
+  </si>
+  <si>
+    <t>Animation, Science-fiction, Fantastique</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6970856/?ref_=nm_ov_bio_lk</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1130,6 +1200,13 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
@@ -1158,7 +1235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1171,6 +1248,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2297,7 +2375,7 @@
       <c r="A124" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="6" t="s">
         <v>168</v>
       </c>
       <c r="C124" t="s">
@@ -2329,7 +2407,7 @@
       <c r="A125" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="6" t="s">
         <v>176</v>
       </c>
       <c r="C125" t="s">
@@ -2346,7 +2424,7 @@
       <c r="A126" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C126" t="s">
@@ -2378,7 +2456,7 @@
       <c r="A127" s="5">
         <v>46183</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="6" t="s">
         <v>188</v>
       </c>
       <c r="C127" t="s">
@@ -2410,7 +2488,7 @@
       <c r="A128" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="6" t="s">
         <v>196</v>
       </c>
       <c r="C128" t="s">
@@ -2439,7 +2517,7 @@
       <c r="A129" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="6" t="s">
         <v>202</v>
       </c>
       <c r="C129" t="s">
@@ -2471,7 +2549,7 @@
       <c r="A130" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="6" t="s">
         <v>210</v>
       </c>
       <c r="C130" t="s">
@@ -2503,7 +2581,7 @@
       <c r="A131" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="6" t="s">
         <v>218</v>
       </c>
       <c r="C131" t="s">
@@ -2520,7 +2598,7 @@
       <c r="A132" s="5">
         <v>46190</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C132" t="s">
@@ -2537,7 +2615,7 @@
       <c r="A133" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="6" t="s">
         <v>225</v>
       </c>
       <c r="C133" t="s">
@@ -2557,7 +2635,7 @@
       <c r="A134" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C134" t="s">
@@ -2583,7 +2661,7 @@
       <c r="A135" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="6" t="s">
         <v>237</v>
       </c>
       <c r="C135" t="s">
@@ -2600,7 +2678,7 @@
       <c r="A136" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="6" t="s">
         <v>241</v>
       </c>
       <c r="C136" t="s">
@@ -2632,7 +2710,7 @@
       <c r="A137" s="5">
         <v>46197</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="6" t="s">
         <v>247</v>
       </c>
       <c r="C137" t="s">
@@ -2664,36 +2742,116 @@
       <c r="A138" s="4" t="s">
         <v>254</v>
       </c>
+      <c r="B138" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C138" t="s">
+        <v>343</v>
+      </c>
+      <c r="D138" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>255</v>
       </c>
+      <c r="B139" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C139" t="s">
+        <v>344</v>
+      </c>
+      <c r="D139" t="s">
+        <v>351</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>256</v>
       </c>
+      <c r="B140" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C140" t="s">
+        <v>345</v>
+      </c>
+      <c r="D140" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>257</v>
       </c>
+      <c r="B141" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C141" t="s">
+        <v>346</v>
+      </c>
+      <c r="D141" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>46204</v>
       </c>
-      <c r="B142" s="5"/>
+      <c r="B142" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C142" t="s">
+        <v>347</v>
+      </c>
+      <c r="D142" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>258</v>
       </c>
+      <c r="B143" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C143" t="s">
+        <v>348</v>
+      </c>
+      <c r="E143" t="s">
+        <v>356</v>
+      </c>
+      <c r="F143" t="s">
+        <v>357</v>
+      </c>
+      <c r="G143">
+        <v>2018</v>
+      </c>
+      <c r="H143" t="s">
+        <v>358</v>
+      </c>
+      <c r="I143" t="s">
+        <v>360</v>
+      </c>
+      <c r="J143" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>259</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C144" t="s">
+        <v>349</v>
+      </c>
+      <c r="D144" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.2">
@@ -2717,6 +2875,7 @@
     <hyperlink ref="K127" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="K128" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="K130" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K139" r:id="rId6" xr:uid="{66BBCC3E-C4CA-8040-86BD-5AD2C72A2FB3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD388747-A123-1048-B04E-8EF27DFED198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC824DE-1E10-A243-B21E-A2D5DB839811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Films" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$C$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planning!$A$1:$C$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="263">
   <si>
     <t>date</t>
   </si>
@@ -73,348 +73,6 @@
   </si>
   <si>
     <t>questions</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>02/09/2025</t>
-  </si>
-  <si>
-    <t>04/09/2025</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>08/09/2025</t>
-  </si>
-  <si>
-    <t>09/09/2025</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>12/09/2025</t>
-  </si>
-  <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
-    <t>18/09/2025</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>22/09/2025</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>26/09/2025</t>
-  </si>
-  <si>
-    <t>29/09/2025</t>
-  </si>
-  <si>
-    <t>30/09/2025</t>
-  </si>
-  <si>
-    <t>02/10/2025</t>
-  </si>
-  <si>
-    <t>03/10/2025</t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
-    <t>10/10/2025</t>
-  </si>
-  <si>
-    <t>13/10/2025</t>
-  </si>
-  <si>
-    <t>14/10/2025</t>
-  </si>
-  <si>
-    <t>16/10/2025</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-  <si>
-    <t>13/11/2025</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>17/11/2025</t>
-  </si>
-  <si>
-    <t>18/11/2025</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>21/11/2025</t>
-  </si>
-  <si>
-    <t>24/11/2025</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>27/11/2025</t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>02/12/2025</t>
-  </si>
-  <si>
-    <t>04/12/2025</t>
-  </si>
-  <si>
-    <t>05/12/2025</t>
-  </si>
-  <si>
-    <t>08/12/2025</t>
-  </si>
-  <si>
-    <t>09/12/2025</t>
-  </si>
-  <si>
-    <t>11/12/2025</t>
-  </si>
-  <si>
-    <t>12/12/2025</t>
-  </si>
-  <si>
-    <t>15/12/2025</t>
-  </si>
-  <si>
-    <t>16/12/2025</t>
-  </si>
-  <si>
-    <t>18/12/2025</t>
-  </si>
-  <si>
-    <t>19/12/2025</t>
-  </si>
-  <si>
-    <t>05/01/2026</t>
-  </si>
-  <si>
-    <t>06/01/2026</t>
-  </si>
-  <si>
-    <t>08/01/2026</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>12/01/2026</t>
-  </si>
-  <si>
-    <t>13/01/2026</t>
-  </si>
-  <si>
-    <t>15/01/2026</t>
-  </si>
-  <si>
-    <t>16/01/2026</t>
-  </si>
-  <si>
-    <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>20/01/2026</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>27/01/2026</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>03/02/2026</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>12/02/2026</t>
-  </si>
-  <si>
-    <t>13/02/2026</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>12/03/2026</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>19/03/2026</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>09/04/2026</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>28/04/2026</t>
-  </si>
-  <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>04/05/2026</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>21/05/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
   </si>
   <si>
     <t>26/05/2026</t>
@@ -1176,6 +834,51 @@
   </si>
   <si>
     <t>https://www.imdb.com/fr/title/tt6970856/?ref_=nm_ov_bio_lk</t>
+  </si>
+  <si>
+    <t>2 min 20</t>
+  </si>
+  <si>
+    <t>5 min 27</t>
+  </si>
+  <si>
+    <t>7 min</t>
+  </si>
+  <si>
+    <t>6 min 40</t>
+  </si>
+  <si>
+    <t>5 min 30</t>
+  </si>
+  <si>
+    <t>4 min 30</t>
+  </si>
+  <si>
+    <t>12 min</t>
+  </si>
+  <si>
+    <t>4 min</t>
+  </si>
+  <si>
+    <t>3 min 37</t>
+  </si>
+  <si>
+    <t>Animation, Famille</t>
+  </si>
+  <si>
+    <t>1 min 30</t>
+  </si>
+  <si>
+    <t>Animation, Historique</t>
+  </si>
+  <si>
+    <t>6 min 30</t>
+  </si>
+  <si>
+    <t>https://festivalfilmeduc.net/wp-content/uploads/2019/10/36398-lunette-_phoebe-warries.jpg</t>
+  </si>
+  <si>
+    <t>https://media.senscritique.com/media/000019646216/600/light.jpg</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14.83203125" style="4" customWidth="1"/>
@@ -1639,1243 +1342,742 @@
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
+      <c r="A3" s="5">
+        <v>46169</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>249</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>2016</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>251</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>46176</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10">
+        <v>2014</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>228</v>
+      </c>
+      <c r="J10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
+        <v>244</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>65</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12">
+        <v>2019</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
+      <c r="A13" s="5">
+        <v>46183</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13">
+        <v>2016</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>24</v>
+        <v>81</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14">
+        <v>2018</v>
+      </c>
+      <c r="H14" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>25</v>
+        <v>87</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15">
+        <v>2009</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16">
+        <v>2019</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22">
+        <v>2013</v>
+      </c>
+      <c r="H22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23">
+        <v>2006</v>
+      </c>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" t="s">
+        <v>236</v>
+      </c>
+      <c r="H24" t="s">
+        <v>252</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="H25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I25" t="s">
+        <v>257</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" t="s">
+        <v>240</v>
+      </c>
+      <c r="H27" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" t="s">
+        <v>242</v>
+      </c>
+      <c r="F29" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29">
+        <v>2018</v>
+      </c>
+      <c r="H29" t="s">
+        <v>244</v>
+      </c>
+      <c r="I29" t="s">
+        <v>246</v>
+      </c>
+      <c r="J29" t="s">
+        <v>245</v>
+      </c>
+      <c r="K29" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D30" t="s">
+        <v>247</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A98" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A100" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A101" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A102" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A109" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D111" s="1"/>
-      <c r="L111" s="2"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L112" s="2"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A115" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B116" t="s">
-        <v>127</v>
-      </c>
-      <c r="C116" t="s">
-        <v>128</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F116" t="s">
-        <v>130</v>
-      </c>
-      <c r="I116" t="s">
-        <v>131</v>
-      </c>
-      <c r="K116" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A117" s="5">
-        <v>46169</v>
-      </c>
-      <c r="B117" t="s">
-        <v>133</v>
-      </c>
-      <c r="C117" t="s">
-        <v>134</v>
-      </c>
-      <c r="D117" t="s">
-        <v>135</v>
-      </c>
-      <c r="I117" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A118" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B118" t="s">
-        <v>138</v>
-      </c>
-      <c r="C118" t="s">
-        <v>139</v>
-      </c>
-      <c r="E118" t="s">
-        <v>140</v>
-      </c>
-      <c r="F118" t="s">
-        <v>130</v>
-      </c>
-      <c r="G118">
-        <v>2016</v>
-      </c>
-      <c r="H118" t="s">
-        <v>141</v>
-      </c>
-      <c r="I118" t="s">
-        <v>142</v>
-      </c>
-      <c r="J118" t="s">
-        <v>143</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C119" t="s">
-        <v>147</v>
-      </c>
-      <c r="D119" t="s">
-        <v>148</v>
-      </c>
-      <c r="I119" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C120" t="s">
-        <v>151</v>
-      </c>
-      <c r="D120" t="s">
-        <v>152</v>
-      </c>
-      <c r="I120" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A121" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B121" t="s">
-        <v>155</v>
-      </c>
-      <c r="C121" t="s">
-        <v>156</v>
-      </c>
-      <c r="D121" t="s">
-        <v>157</v>
-      </c>
-      <c r="F121" t="s">
-        <v>158</v>
-      </c>
-      <c r="I121" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="5">
-        <v>46176</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C122" t="s">
-        <v>161</v>
-      </c>
-      <c r="D122" t="s">
-        <v>162</v>
-      </c>
-      <c r="I122" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C123" t="s">
-        <v>165</v>
-      </c>
-      <c r="D123" t="s">
-        <v>166</v>
-      </c>
-      <c r="F123" t="s">
-        <v>158</v>
-      </c>
-      <c r="I123" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C124" t="s">
-        <v>169</v>
-      </c>
-      <c r="E124" t="s">
-        <v>170</v>
-      </c>
-      <c r="F124" t="s">
-        <v>158</v>
-      </c>
-      <c r="G124">
-        <v>2014</v>
-      </c>
-      <c r="H124" t="s">
-        <v>171</v>
-      </c>
-      <c r="I124" t="s">
-        <v>342</v>
-      </c>
-      <c r="J124" t="s">
-        <v>173</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C125" t="s">
-        <v>177</v>
-      </c>
-      <c r="D125" t="s">
-        <v>178</v>
-      </c>
-      <c r="I125" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="119" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C126" t="s">
-        <v>181</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F126" t="s">
-        <v>183</v>
-      </c>
-      <c r="G126">
-        <v>2019</v>
-      </c>
-      <c r="H126" t="s">
-        <v>184</v>
-      </c>
-      <c r="I126" t="s">
-        <v>185</v>
-      </c>
-      <c r="J126" t="s">
-        <v>186</v>
-      </c>
-      <c r="K126" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A127" s="5">
-        <v>46183</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C127" t="s">
-        <v>189</v>
-      </c>
-      <c r="E127" t="s">
-        <v>190</v>
-      </c>
-      <c r="F127" t="s">
-        <v>183</v>
-      </c>
-      <c r="G127">
-        <v>2016</v>
-      </c>
-      <c r="H127" t="s">
-        <v>191</v>
-      </c>
-      <c r="I127" t="s">
-        <v>192</v>
-      </c>
-      <c r="J127" t="s">
-        <v>193</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A128" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C128" t="s">
-        <v>197</v>
-      </c>
-      <c r="F128" t="s">
-        <v>183</v>
-      </c>
-      <c r="G128">
-        <v>2018</v>
-      </c>
-      <c r="H128" t="s">
-        <v>198</v>
-      </c>
-      <c r="I128" t="s">
-        <v>131</v>
-      </c>
-      <c r="J128" t="s">
-        <v>199</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C129" t="s">
-        <v>203</v>
-      </c>
-      <c r="E129" t="s">
-        <v>204</v>
-      </c>
-      <c r="F129" t="s">
-        <v>183</v>
-      </c>
-      <c r="G129">
-        <v>2009</v>
-      </c>
-      <c r="H129" t="s">
-        <v>205</v>
-      </c>
-      <c r="I129" t="s">
-        <v>206</v>
-      </c>
-      <c r="J129" t="s">
-        <v>207</v>
-      </c>
-      <c r="K129" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A130" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C130" t="s">
-        <v>211</v>
-      </c>
-      <c r="E130" t="s">
-        <v>212</v>
-      </c>
-      <c r="F130" t="s">
-        <v>213</v>
-      </c>
-      <c r="G130">
-        <v>2019</v>
-      </c>
-      <c r="H130" t="s">
-        <v>214</v>
-      </c>
-      <c r="I130" t="s">
-        <v>131</v>
-      </c>
-      <c r="J130" t="s">
-        <v>215</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C131" t="s">
-        <v>219</v>
-      </c>
-      <c r="D131" t="s">
-        <v>220</v>
-      </c>
-      <c r="I131" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132" s="5">
-        <v>46190</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C132" t="s">
-        <v>222</v>
-      </c>
-      <c r="D132" t="s">
-        <v>223</v>
-      </c>
-      <c r="I132" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C133" t="s">
-        <v>226</v>
-      </c>
-      <c r="D133" t="s">
-        <v>227</v>
-      </c>
-      <c r="E133" t="s">
-        <v>228</v>
-      </c>
-      <c r="I133" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C134" t="s">
-        <v>231</v>
-      </c>
-      <c r="D134" t="s">
-        <v>232</v>
-      </c>
-      <c r="F134" t="s">
-        <v>183</v>
-      </c>
-      <c r="I134" t="s">
-        <v>233</v>
-      </c>
-      <c r="J134" t="s">
-        <v>234</v>
-      </c>
-      <c r="K134" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C135" t="s">
-        <v>238</v>
-      </c>
-      <c r="D135" t="s">
-        <v>239</v>
-      </c>
-      <c r="I135" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C136" t="s">
-        <v>242</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F136" t="s">
-        <v>183</v>
-      </c>
-      <c r="G136">
-        <v>2013</v>
-      </c>
-      <c r="H136" t="s">
-        <v>244</v>
-      </c>
-      <c r="I136" t="s">
-        <v>159</v>
-      </c>
-      <c r="J136" t="s">
-        <v>245</v>
-      </c>
-      <c r="K136" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="5">
-        <v>46197</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C137" t="s">
-        <v>248</v>
-      </c>
-      <c r="E137" t="s">
-        <v>249</v>
-      </c>
-      <c r="F137" t="s">
-        <v>183</v>
-      </c>
-      <c r="G137">
-        <v>2006</v>
-      </c>
-      <c r="H137" t="s">
-        <v>250</v>
-      </c>
-      <c r="I137" t="s">
-        <v>251</v>
-      </c>
-      <c r="J137" t="s">
-        <v>252</v>
-      </c>
-      <c r="K137" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A138" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C138" t="s">
-        <v>343</v>
-      </c>
-      <c r="D138" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A139" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="C139" t="s">
-        <v>344</v>
-      </c>
-      <c r="D139" t="s">
-        <v>351</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A140" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C140" t="s">
-        <v>345</v>
-      </c>
-      <c r="D140" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A141" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C141" t="s">
-        <v>346</v>
-      </c>
-      <c r="D141" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A142" s="5">
-        <v>46204</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C142" t="s">
-        <v>347</v>
-      </c>
-      <c r="D142" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A143" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C143" t="s">
-        <v>348</v>
-      </c>
-      <c r="E143" t="s">
-        <v>356</v>
-      </c>
-      <c r="F143" t="s">
-        <v>357</v>
-      </c>
-      <c r="G143">
-        <v>2018</v>
-      </c>
-      <c r="H143" t="s">
-        <v>358</v>
-      </c>
-      <c r="I143" t="s">
-        <v>360</v>
-      </c>
-      <c r="J143" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C144" t="s">
-        <v>349</v>
-      </c>
-      <c r="D144" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C146" s="1"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C147" s="1"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C148" s="1"/>
+      <c r="K30" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C144" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C144">
-      <sortCondition ref="A1:A144"/>
+  <autoFilter ref="A1:C30" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C30">
+      <sortCondition ref="A1:A30"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="D116" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="K124" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K127" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K128" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K130" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K139" r:id="rId6" xr:uid="{66BBCC3E-C4CA-8040-86BD-5AD2C72A2FB3}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K25" r:id="rId6" xr:uid="{66BBCC3E-C4CA-8040-86BD-5AD2C72A2FB3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2929,817 +2131,817 @@
     </row>
     <row r="2" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>260</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>261</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>2016</v>
       </c>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>2014</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>2019</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F13">
         <v>2016</v>
       </c>
       <c r="G13" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <v>2018</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>200</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F15">
         <v>2009</v>
       </c>
       <c r="G15" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>207</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s">
-        <v>208</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="F16">
         <v>2019</v>
       </c>
       <c r="G16" t="s">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="I16" t="s">
-        <v>215</v>
+        <v>101</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>222</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>225</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>237</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>239</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>241</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F22">
         <v>2013</v>
       </c>
       <c r="G22" t="s">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="I22" t="s">
-        <v>245</v>
+        <v>131</v>
       </c>
       <c r="J22" t="s">
-        <v>246</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>247</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>249</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="F23">
         <v>2006</v>
       </c>
       <c r="G23" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="J23" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>263</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>270</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>271</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>272</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s">
-        <v>274</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>275</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>276</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>284</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>287</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>289</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
-        <v>290</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>293</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>294</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>296</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>297</v>
+        <v>183</v>
       </c>
       <c r="B41" t="s">
-        <v>298</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>299</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>300</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>301</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>302</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>303</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s">
-        <v>304</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>305</v>
+        <v>191</v>
       </c>
       <c r="B45" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>307</v>
+        <v>193</v>
       </c>
       <c r="B46" t="s">
-        <v>308</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>310</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>312</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>313</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>314</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="B50" t="s">
-        <v>316</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>317</v>
+        <v>203</v>
       </c>
       <c r="B51" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>319</v>
+        <v>205</v>
       </c>
       <c r="B52" t="s">
-        <v>320</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>321</v>
+        <v>207</v>
       </c>
       <c r="B53" t="s">
-        <v>322</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>323</v>
+        <v>209</v>
       </c>
       <c r="B54" t="s">
-        <v>324</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="E111" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="J111" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>327</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C114" t="s">
-        <v>329</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C116" t="s">
-        <v>330</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C117" t="s">
-        <v>331</v>
+        <v>217</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C118" t="s">
-        <v>332</v>
+        <v>218</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C119" t="s">
-        <v>333</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C120" t="s">
-        <v>334</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C121" t="s">
-        <v>335</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C122" t="s">
-        <v>336</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C123" t="s">
-        <v>337</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C124" t="s">
-        <v>338</v>
+        <v>224</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C125" t="s">
-        <v>339</v>
+        <v>225</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C126" t="s">
-        <v>340</v>
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>328</v>
+        <v>214</v>
       </c>
       <c r="C127" t="s">
-        <v>341</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="J133" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="C134" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC824DE-1E10-A243-B21E-A2D5DB839811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA615F1-E0DE-A44D-9BDE-150A7F7F63D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="261">
   <si>
     <t>date</t>
   </si>
@@ -114,13 +114,7 @@
     <t>Bertie l'éléphant</t>
   </si>
   <si>
-    <t>https://youtu.be/hwt1-j_n1SY?si=OKVoa5rllkueH4N-</t>
-  </si>
-  <si>
     <t>Chris Turner &amp; Zak Boxall</t>
-  </si>
-  <si>
-    <t>5 min 20</t>
   </si>
   <si>
     <t>Court, Dramatique, Poétique</t>
@@ -216,9 +210,6 @@
     <t>4 min 23</t>
   </si>
   <si>
-    <t>Court métrage Animation Familial</t>
-  </si>
-  <si>
     <t>Ah les cabanes…quel délicieux souvenir… Et quel déchirement de les quitter lorsqu’on doit déménager. A moins que… mais oui ! Tout n’est pas perdu…</t>
   </si>
   <si>
@@ -253,9 +244,6 @@
     <t>France</t>
   </si>
   <si>
-    <t>6 min</t>
-  </si>
-  <si>
     <t>Animation</t>
   </si>
   <si>
@@ -272,9 +260,6 @@
   </si>
   <si>
     <t>Alice Coutelle, Thomas Dibet, Hugo Favre, Eliette Gibaud, Cerise Grefferat, Guillaume Jarrosson, Thi Bich Pham et Thibault Spieser</t>
-  </si>
-  <si>
-    <t>5 min</t>
   </si>
   <si>
     <t>Animation, Court, Comédie</t>
@@ -531,49 +516,25 @@
 </t>
   </si>
   <si>
-    <t>Etats-Unis</t>
-  </si>
-  <si>
     <t>Les chaussures de Louis</t>
   </si>
   <si>
-    <t>https://youtu.be/eIWyHjVPas0?si=dbzlzEg46XB72ruC</t>
-  </si>
-  <si>
     <t>Les lettres qui tombent</t>
   </si>
   <si>
-    <t>https://youtu.be/EQ71vgRzCA4?si=5ADvSg5sBy68e8Go</t>
-  </si>
-  <si>
     <t>Les pyramides d'Egypte</t>
   </si>
   <si>
-    <t>https://youtu.be/j6PbonHsqW0?si=NXgNJtYDfaHQgqCF</t>
-  </si>
-  <si>
     <t>Lily et le bonhomme de neige</t>
   </si>
   <si>
-    <t>https://youtu.be/FCF-rNMLVpE?si=4Lhp3tqQ9bsSfd8d</t>
-  </si>
-  <si>
     <t>Lost Property</t>
   </si>
   <si>
-    <t>https://youtu.be/qwMe-Z87OZ0?si=Sua6_509LWN0t7FD</t>
-  </si>
-  <si>
     <t>Lumière</t>
   </si>
   <si>
-    <t>https://youtu.be/hdyAFuHRayQ?si=JFeJtTAKmZItzmgV</t>
-  </si>
-  <si>
     <t>Lunette</t>
-  </si>
-  <si>
-    <t>https://youtu.be/eviPBToWpP4?si=-m1_uRMYQ-WVE98k</t>
   </si>
   <si>
     <t>Migrants</t>
@@ -836,49 +797,82 @@
     <t>https://www.imdb.com/fr/title/tt6970856/?ref_=nm_ov_bio_lk</t>
   </si>
   <si>
-    <t>2 min 20</t>
-  </si>
-  <si>
-    <t>5 min 27</t>
-  </si>
-  <si>
-    <t>7 min</t>
-  </si>
-  <si>
-    <t>6 min 40</t>
-  </si>
-  <si>
-    <t>5 min 30</t>
-  </si>
-  <si>
-    <t>4 min 30</t>
-  </si>
-  <si>
-    <t>12 min</t>
-  </si>
-  <si>
-    <t>4 min</t>
-  </si>
-  <si>
-    <t>3 min 37</t>
-  </si>
-  <si>
     <t>Animation, Famille</t>
   </si>
   <si>
-    <t>1 min 30</t>
-  </si>
-  <si>
     <t>Animation, Historique</t>
   </si>
   <si>
-    <t>6 min 30</t>
-  </si>
-  <si>
     <t>https://festivalfilmeduc.net/wp-content/uploads/2019/10/36398-lunette-_phoebe-warries.jpg</t>
   </si>
   <si>
     <t>https://media.senscritique.com/media/000019646216/600/light.jpg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XRMTOCBmSNQ</t>
+  </si>
+  <si>
+    <t>2 min 50</t>
+  </si>
+  <si>
+    <t>7 min 39</t>
+  </si>
+  <si>
+    <t>5 min 25</t>
+  </si>
+  <si>
+    <t>3 min 14</t>
+  </si>
+  <si>
+    <t>4 min 05</t>
+  </si>
+  <si>
+    <t>6 min 35</t>
+  </si>
+  <si>
+    <t>5 min 12</t>
+  </si>
+  <si>
+    <t>2 min 54</t>
+  </si>
+  <si>
+    <t>12 min 07</t>
+  </si>
+  <si>
+    <t>5 min 46</t>
+  </si>
+  <si>
+    <t>4 min 18</t>
+  </si>
+  <si>
+    <t>4 min 15</t>
+  </si>
+  <si>
+    <t>3 min 32</t>
+  </si>
+  <si>
+    <t>6 min 14</t>
+  </si>
+  <si>
+    <t>2 min 03</t>
+  </si>
+  <si>
+    <t>3 min 35</t>
+  </si>
+  <si>
+    <t>5 min 17</t>
+  </si>
+  <si>
+    <t>3 min 26</t>
+  </si>
+  <si>
+    <t>9 min 01</t>
+  </si>
+  <si>
+    <t>5 min 51</t>
+  </si>
+  <si>
+    <t>1 min 58</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1349,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -1378,7 +1372,7 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -1392,10 +1386,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1404,33 +1398,33 @@
         <v>2016</v>
       </c>
       <c r="H4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
       <c r="H5" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -1438,45 +1432,45 @@
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I6" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
+      <c r="H7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>251</v>
-      </c>
-      <c r="I7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -1484,126 +1478,126 @@
         <v>46176</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
       <c r="H8" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
-      </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10">
         <v>2014</v>
       </c>
       <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I10" t="s">
-        <v>228</v>
-      </c>
-      <c r="J10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="F12" t="s">
         <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
       </c>
       <c r="G12">
         <v>2019</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1611,138 +1605,141 @@
         <v>46183</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>2016</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>2018</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>2009</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G16">
         <v>2019</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="H17" t="s">
+        <v>251</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1753,36 +1750,39 @@
         <v>46190</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>104</v>
+      </c>
+      <c r="H18" t="s">
+        <v>247</v>
       </c>
       <c r="I18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H19" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1790,45 +1790,48 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>249</v>
+      </c>
+      <c r="I20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="K20" t="s">
         <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20" t="s">
-        <v>120</v>
-      </c>
-      <c r="K20" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1836,34 +1839,34 @@
     </row>
     <row r="22" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>2013</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -1871,48 +1874,48 @@
         <v>46197</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G23">
         <v>2006</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="H24" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -1920,65 +1923,65 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="H25" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I25" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="H26" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I26" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D27" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="H27" t="s">
-        <v>84</v>
+        <v>254</v>
       </c>
       <c r="I27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1986,16 +1989,16 @@
         <v>46204</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D28" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="H28" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2003,57 +2006,57 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E29" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="F29" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="G29">
         <v>2018</v>
       </c>
       <c r="H29" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="I29" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J29" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="K29" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="D30" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="I30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2142,11 +2145,17 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
+      <c r="G2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2159,8 +2168,14 @@
       <c r="C3" t="s">
         <v>21</v>
       </c>
+      <c r="G3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
       <c r="K3" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2168,10 +2183,10 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" t="s">
         <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -2180,601 +2195,787 @@
         <v>2016</v>
       </c>
       <c r="G4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
+      <c r="G5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
+      <c r="G8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>2014</v>
       </c>
       <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="B11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
         <v>66</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>69</v>
       </c>
       <c r="F12">
         <v>2019</v>
       </c>
       <c r="G12" t="s">
+        <v>245</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H12" t="s">
+      <c r="B13" t="s">
         <v>71</v>
       </c>
-      <c r="I12" t="s">
+      <c r="D13" t="s">
         <v>72</v>
       </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F13">
         <v>2016</v>
       </c>
       <c r="G13" t="s">
+        <v>246</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H13" t="s">
+      <c r="B14" t="s">
         <v>78</v>
       </c>
-      <c r="I13" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F14">
         <v>2018</v>
       </c>
       <c r="G14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
         <v>84</v>
       </c>
-      <c r="I14" t="s">
+      <c r="D15" t="s">
         <v>85</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <v>2009</v>
       </c>
       <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I15" t="s">
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-      <c r="J15" t="s">
+      <c r="E16" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" t="s">
-        <v>97</v>
       </c>
       <c r="F16">
         <v>2019</v>
       </c>
       <c r="G16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
         <v>100</v>
       </c>
-      <c r="I16" t="s">
+      <c r="C17" t="s">
         <v>101</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="G17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="G18" t="s">
+        <v>247</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="B19" t="s">
         <v>107</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C19" t="s">
         <v>108</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D19" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="G19" t="s">
+        <v>248</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>112</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" t="s">
+        <v>249</v>
+      </c>
+      <c r="H20" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" t="s">
         <v>116</v>
       </c>
-      <c r="B20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>250</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
         <v>123</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F22">
         <v>2013</v>
       </c>
       <c r="G22" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" t="s">
+        <v>126</v>
+      </c>
+      <c r="J22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
         <v>130</v>
       </c>
-      <c r="I22" t="s">
-        <v>131</v>
-      </c>
-      <c r="J22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F23">
         <v>2006</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>131</v>
+      </c>
+      <c r="H23" t="s">
+        <v>132</v>
       </c>
       <c r="I23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" t="s">
+        <v>256</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" t="s">
+        <v>251</v>
+      </c>
+      <c r="H25" t="s">
+        <v>235</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>226</v>
+      </c>
+      <c r="G26" t="s">
+        <v>255</v>
+      </c>
+      <c r="H26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" t="s">
+        <v>227</v>
+      </c>
+      <c r="G27" t="s">
+        <v>254</v>
+      </c>
+      <c r="H27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" t="s">
+        <v>228</v>
+      </c>
+      <c r="G28" t="s">
+        <v>253</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" t="s">
+        <v>230</v>
+      </c>
+      <c r="F29">
+        <v>2018</v>
+      </c>
+      <c r="G29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H29" t="s">
+        <v>233</v>
+      </c>
+      <c r="I29" t="s">
+        <v>232</v>
+      </c>
+      <c r="J29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>222</v>
+      </c>
+      <c r="C30" t="s">
+        <v>234</v>
+      </c>
+      <c r="G30" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B49" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B51" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B52" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B54" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2791,7 +2992,7 @@
         <v>18</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.2">
@@ -2804,122 +3005,122 @@
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C113" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C114" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C116" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C117" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C118" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C119" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C121" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C122" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C123" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C124" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C125" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C126" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
+        <v>201</v>
+      </c>
+      <c r="C127" t="s">
         <v>214</v>
-      </c>
-      <c r="C127" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.2">
@@ -2955,12 +3156,13 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="J10" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="J13" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="J14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="J16" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="C111" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="C111" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{186B1FBA-DF95-C24D-BFB9-D23FD31DA947}"/>
+    <hyperlink ref="J10" r:id="rId3" xr:uid="{DE481A92-C3EB-1B4F-893B-F8F76042E06E}"/>
+    <hyperlink ref="J13" r:id="rId4" xr:uid="{DA0B6117-DA00-3344-A87C-4E92D413588C}"/>
+    <hyperlink ref="J14" r:id="rId5" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{F665BED2-DA27-0A4D-B108-E2AEFF2279EA}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{65420500-9579-7443-915D-A91EBE5B0664}"/>
+    <hyperlink ref="J25" r:id="rId7" xr:uid="{CF8BD6DB-94B1-9141-932F-245AD7AC80AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/film.xlsx
+++ b/film.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA615F1-E0DE-A44D-9BDE-150A7F7F63D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3C1BD5-1CE3-1F44-9485-4C2944B72B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="322">
   <si>
     <t>date</t>
   </si>
@@ -585,12 +585,6 @@
     <t>https://youtu.be/FVNJFBI0b-g?si=3sCNCTNuL4qxOO4Z</t>
   </si>
   <si>
-    <t>Rituel</t>
-  </si>
-  <si>
-    <t>https://youtu.be/QADYuPXfrxM?si=iuxuvdzCfvsKFzk9</t>
-  </si>
-  <si>
     <t>Rubato</t>
   </si>
   <si>
@@ -601,12 +595,6 @@
   </si>
   <si>
     <t>https://youtu.be/vX77zcKiN98?si=AiGeBdNGKCrrtI8q</t>
-  </si>
-  <si>
-    <t>Sapling</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fmLDta7pMs8?si=xTImfs-m_kc2OWcv</t>
   </si>
   <si>
     <t>Snack Attack</t>
@@ -873,6 +861,201 @@
   </si>
   <si>
     <t>1 min 58</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt14182404/</t>
+  </si>
+  <si>
+    <t>8 min 23</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6606990/?ref_=fn_t_1</t>
+  </si>
+  <si>
+    <t>5 min 56</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5568140/?ref_=fn_t_1</t>
+  </si>
+  <si>
+    <t>2 min 04</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3043542/</t>
+  </si>
+  <si>
+    <t>4 min 33</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0479113/</t>
+  </si>
+  <si>
+    <t>3 min 29</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt4776846/</t>
+  </si>
+  <si>
+    <t>Steve Boot</t>
+  </si>
+  <si>
+    <t>https://www.stashmedia.tv/wp-content/uploads/Steve-Boot-ONce-Upon-a-Blue-Moon-STASH-MAGAZINE1.png</t>
+  </si>
+  <si>
+    <t>La rencontre entre un extra-terrestre et un robot dont la mission va être fortement compromise…</t>
+  </si>
+  <si>
+    <t>Animation, Court, Amitié, Humour</t>
+  </si>
+  <si>
+    <t>Royaume Uni</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt9257672/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’histoire d’un jeune moine qui rêve de maîtriser tous les principes de la méditation. </t>
+  </si>
+  <si>
+    <t>7 min 01</t>
+  </si>
+  <si>
+    <t>Animation, Court, Humour, Comédie</t>
+  </si>
+  <si>
+    <t>Hayk Sahakyants</t>
+  </si>
+  <si>
+    <t>Arménie</t>
+  </si>
+  <si>
+    <t>https://sahakyants.com/wp-content/uploads/2024/10/a1d70d26-2675-4f15-b5c3-db3beaafe9e1.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt7423182/</t>
+  </si>
+  <si>
+    <t>7 min 38</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt11150986/</t>
+  </si>
+  <si>
+    <t>7 min 56</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2893110/</t>
+  </si>
+  <si>
+    <t>3 min 58</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt3686088/</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6588384/</t>
+  </si>
+  <si>
+    <t>3 min 05</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt4428412/</t>
+  </si>
+  <si>
+    <t>5 min 57</t>
+  </si>
+  <si>
+    <t>3 min 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un moine qui préfère être seul voit sa vie bouleversée par l’arrivée d’un petit chien. Cette rencontre lui apprend une leçon importante sur l’amitié et le bonheur.  </t>
+  </si>
+  <si>
+    <t>Animation, Comédie, Conte philosophique, Amitié</t>
+  </si>
+  <si>
+    <t>https://goldenbuddha.org/wp-content/uploads/2017/10/misguided-monk3.png</t>
+  </si>
+  <si>
+    <t>Tom Long</t>
+  </si>
+  <si>
+    <t>3 min 25</t>
+  </si>
+  <si>
+    <t>Un moine cherche à méditer en paix, mais une petite mouche ne cesse de l’embêter. Cette rencontre donne lieu à une série de situations drôles qui montrent qu’il n’est pas toujours facile de rester calme.</t>
+  </si>
+  <si>
+    <t>Animation, Comédie, Fable</t>
+  </si>
+  <si>
+    <t>Irlande</t>
+  </si>
+  <si>
+    <t>https://festivalcinemabudista.cat/wp-content/uploads/2022/09/fcbc_monk_and_fly_portada.jpg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt31073796/</t>
+  </si>
+  <si>
+    <t>5 min 45</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt4047720/</t>
+  </si>
+  <si>
+    <t>8 min 08</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6192248/</t>
+  </si>
+  <si>
+    <t>4 min 48</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2217995/</t>
+  </si>
+  <si>
+    <t>6 min 29</t>
+  </si>
+  <si>
+    <t>Une petite fille découvre tous les animaux et plantes qui vivent dans son jardin. Quand cet environnement est menacé, elle trouve une solution pour protéger la nature.</t>
+  </si>
+  <si>
+    <t>Animation, écologie, sensibilisation à l’environnement</t>
+  </si>
+  <si>
+    <t>Morgane Boullier</t>
+  </si>
+  <si>
+    <t>https://animationland.fr/wp-content/uploads/2017/09/carré-pour-la-biodiversité-678x381.png</t>
+  </si>
+  <si>
+    <t>7 min 25</t>
+  </si>
+  <si>
+    <t>Danemark</t>
+  </si>
+  <si>
+    <t>Pedro Ivo Carvalho</t>
+  </si>
+  <si>
+    <t>3 min 24</t>
+  </si>
+  <si>
+    <t>Animation 3D, aventure, famille, émotion. </t>
+  </si>
+  <si>
+    <t>À la suite du crash d’un avion, un jeune gecko se retrouve seul au cœur de la jungle. Perdu et sans famille, il part à la recherche d’un nouveau foyer et va faire des rencontres qui changeront sa vie.</t>
+  </si>
+  <si>
+    <t>Camille Hubert, Laura Jamorski, Arnaud Pezere et Melissa Aureyre</t>
+  </si>
+  <si>
+    <t>https://www.ecv.fr/app/uploads/2021/04/wild-ecv-animation.jpg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5159538/</t>
   </si>
 </sst>
 </file>
@@ -896,7 +1079,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
@@ -904,8 +1086,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF404040"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -932,20 +1113,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1286,19 +1466,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.83203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="1" max="2" width="14.83203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="33.5" customWidth="1"/>
     <col min="12" max="12" width="80.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1333,7 +1513,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
@@ -1349,7 +1529,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -1359,7 +1539,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46169</v>
       </c>
       <c r="B3" t="s">
@@ -1372,21 +1552,21 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
@@ -1398,7 +1578,7 @@
         <v>2016</v>
       </c>
       <c r="H4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1411,7 +1591,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1424,14 +1604,14 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1444,14 +1624,14 @@
         <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B7" t="s">
@@ -1467,14 +1647,14 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46176</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1487,14 +1667,14 @@
         <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1510,17 +1690,17 @@
         <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C10" t="s">
@@ -1539,7 +1719,7 @@
         <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J10" t="s">
         <v>56</v>
@@ -1549,10 +1729,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C11" t="s">
@@ -1562,17 +1742,17 @@
         <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="119" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C12" t="s">
@@ -1588,7 +1768,7 @@
         <v>2019</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
@@ -1601,10 +1781,10 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46183</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C13" t="s">
@@ -1620,7 +1800,7 @@
         <v>2016</v>
       </c>
       <c r="H13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I13" t="s">
         <v>73</v>
@@ -1633,10 +1813,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C14" t="s">
@@ -1662,10 +1842,10 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
@@ -1694,10 +1874,10 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C16" t="s">
@@ -1726,10 +1906,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C17" t="s">
@@ -1739,17 +1919,17 @@
         <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46190</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>102</v>
       </c>
       <c r="C18" t="s">
@@ -1759,17 +1939,17 @@
         <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C19" t="s">
@@ -1782,17 +1962,17 @@
         <v>109</v>
       </c>
       <c r="H19" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C20" t="s">
@@ -1805,7 +1985,7 @@
         <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I20" t="s">
         <v>114</v>
@@ -1818,10 +1998,10 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C21" t="s">
@@ -1831,17 +2011,17 @@
         <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="136" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C22" t="s">
@@ -1870,10 +2050,10 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46197</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C23" t="s">
@@ -1902,171 +2082,675 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H24" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
+        <v>220</v>
+      </c>
+      <c r="H25" t="s">
+        <v>247</v>
+      </c>
+      <c r="I25" t="s">
+        <v>231</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" t="s">
+        <v>222</v>
+      </c>
+      <c r="H26" t="s">
+        <v>251</v>
+      </c>
+      <c r="I26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" t="s">
+        <v>223</v>
+      </c>
+      <c r="H27" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" t="s">
         <v>224</v>
       </c>
-      <c r="H25" t="s">
-        <v>251</v>
-      </c>
-      <c r="I25" t="s">
-        <v>235</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" t="s">
-        <v>218</v>
-      </c>
-      <c r="D26" t="s">
-        <v>226</v>
-      </c>
-      <c r="H26" t="s">
-        <v>255</v>
-      </c>
-      <c r="I26" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" t="s">
-        <v>219</v>
-      </c>
-      <c r="D27" t="s">
-        <v>227</v>
-      </c>
-      <c r="H27" t="s">
-        <v>254</v>
-      </c>
-      <c r="I27" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="5">
-        <v>46204</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" t="s">
-        <v>220</v>
-      </c>
-      <c r="D28" t="s">
-        <v>228</v>
-      </c>
       <c r="H28" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E29" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F29" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G29">
         <v>2018</v>
       </c>
       <c r="H29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J29" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D30" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H30" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I30" t="s">
         <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>237</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <f>WORKDAY(A30,1)</f>
+        <v>46209</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" t="s">
+        <v>257</v>
+      </c>
+      <c r="H31" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C34" s="1"/>
+      <c r="A32" s="4">
+        <f t="shared" ref="A32:A53" si="0">WORKDAY(A31,1)</f>
+        <v>46210</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" t="s">
+        <v>259</v>
+      </c>
+      <c r="H32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" t="s">
+        <v>261</v>
+      </c>
+      <c r="H33" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>263</v>
+      </c>
+      <c r="H34" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" t="s">
+        <v>265</v>
+      </c>
+      <c r="H35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <f t="shared" si="0"/>
+        <v>46216</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" t="s">
+        <v>268</v>
+      </c>
+      <c r="F36" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36">
+        <v>2016</v>
+      </c>
+      <c r="H36" t="s">
+        <v>266</v>
+      </c>
+      <c r="I36" t="s">
+        <v>271</v>
+      </c>
+      <c r="J36" t="s">
+        <v>270</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <f t="shared" si="0"/>
+        <v>46217</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" t="s">
+        <v>273</v>
+      </c>
+      <c r="H37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <f t="shared" si="0"/>
+        <v>46218</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" t="s">
+        <v>278</v>
+      </c>
+      <c r="G38">
+        <v>2016</v>
+      </c>
+      <c r="H38" t="s">
+        <v>275</v>
+      </c>
+      <c r="I38" t="s">
+        <v>276</v>
+      </c>
+      <c r="J38" t="s">
+        <v>274</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <f t="shared" si="0"/>
+        <v>46219</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" t="s">
+        <v>280</v>
+      </c>
+      <c r="H39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <f t="shared" si="0"/>
+        <v>46220</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C40" t="s">
+        <v>169</v>
+      </c>
+      <c r="D40" t="s">
+        <v>282</v>
+      </c>
+      <c r="H40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <f t="shared" si="0"/>
+        <v>46223</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" t="s">
+        <v>284</v>
+      </c>
+      <c r="H41" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
+        <f t="shared" si="0"/>
+        <v>46224</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" t="s">
+        <v>286</v>
+      </c>
+      <c r="H42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
+        <f t="shared" si="0"/>
+        <v>46225</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" t="s">
+        <v>287</v>
+      </c>
+      <c r="H43" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
+        <f t="shared" si="0"/>
+        <v>46226</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" t="s">
+        <v>289</v>
+      </c>
+      <c r="H44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
+        <f t="shared" si="0"/>
+        <v>46227</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E45" t="s">
+        <v>295</v>
+      </c>
+      <c r="F45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G45">
+        <v>2014</v>
+      </c>
+      <c r="H45" t="s">
+        <v>291</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J45" t="s">
+        <v>292</v>
+      </c>
+      <c r="K45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
+        <f t="shared" si="0"/>
+        <v>46230</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" t="s">
+        <v>181</v>
+      </c>
+      <c r="F46" t="s">
+        <v>299</v>
+      </c>
+      <c r="G46">
+        <v>2010</v>
+      </c>
+      <c r="H46" t="s">
+        <v>296</v>
+      </c>
+      <c r="I46" t="s">
+        <v>298</v>
+      </c>
+      <c r="J46" t="s">
+        <v>297</v>
+      </c>
+      <c r="K46" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
+        <f t="shared" si="0"/>
+        <v>46231</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" t="s">
+        <v>183</v>
+      </c>
+      <c r="D47" t="s">
+        <v>301</v>
+      </c>
+      <c r="H47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
+        <f t="shared" si="0"/>
+        <v>46232</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" t="s">
+        <v>303</v>
+      </c>
+      <c r="H48" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
+        <f t="shared" si="0"/>
+        <v>46233</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" t="s">
+        <v>305</v>
+      </c>
+      <c r="H49" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
+        <f t="shared" si="0"/>
+        <v>46234</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" t="s">
+        <v>307</v>
+      </c>
+      <c r="H50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="4">
+        <f t="shared" si="0"/>
+        <v>46237</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" t="s">
+        <v>311</v>
+      </c>
+      <c r="F51" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51">
+        <v>2015</v>
+      </c>
+      <c r="H51" t="s">
+        <v>302</v>
+      </c>
+      <c r="I51" t="s">
+        <v>310</v>
+      </c>
+      <c r="J51" t="s">
+        <v>309</v>
+      </c>
+      <c r="K51" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="4">
+        <f t="shared" si="0"/>
+        <v>46238</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" t="s">
+        <v>193</v>
+      </c>
+      <c r="D52" t="s">
+        <v>321</v>
+      </c>
+      <c r="E52" t="s">
+        <v>315</v>
+      </c>
+      <c r="F52" t="s">
+        <v>314</v>
+      </c>
+      <c r="G52">
+        <v>2015</v>
+      </c>
+      <c r="H52" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="4">
+        <f t="shared" si="0"/>
+        <v>46239</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" t="s">
+        <v>195</v>
+      </c>
+      <c r="E53" t="s">
+        <v>319</v>
+      </c>
+      <c r="F53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53">
+        <v>2020</v>
+      </c>
+      <c r="H53" t="s">
+        <v>316</v>
+      </c>
+      <c r="I53" t="s">
+        <v>317</v>
+      </c>
+      <c r="J53" t="s">
+        <v>318</v>
+      </c>
+      <c r="K53" t="s">
+        <v>320</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C30" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -2074,6 +2758,7 @@
       <sortCondition ref="A1:A30"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -2081,6 +2766,8 @@
     <hyperlink ref="K14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="K16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="K25" r:id="rId6" xr:uid="{66BBCC3E-C4CA-8040-86BD-5AD2C72A2FB3}"/>
+    <hyperlink ref="K36" r:id="rId7" xr:uid="{43E0665D-98BD-8A45-9566-CB982DEB8884}"/>
+    <hyperlink ref="K38" r:id="rId8" xr:uid="{A2A4E428-F265-9E48-917E-4F7835CEDB03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2089,11 +2776,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
     <col min="11" max="11" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2146,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -2169,7 +2858,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -2183,7 +2872,7 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -2195,7 +2884,7 @@
         <v>2016</v>
       </c>
       <c r="G4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H4" t="s">
         <v>26</v>
@@ -2218,7 +2907,7 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -2235,7 +2924,7 @@
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H6" t="s">
         <v>37</v>
@@ -2255,7 +2944,7 @@
         <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H7" t="s">
         <v>43</v>
@@ -2272,7 +2961,7 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H8" t="s">
         <v>43</v>
@@ -2292,14 +2981,14 @@
         <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B10" t="s">
@@ -2318,7 +3007,7 @@
         <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I10" t="s">
         <v>56</v>
@@ -2328,7 +3017,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B11" t="s">
@@ -2338,14 +3027,14 @@
         <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B12" t="s">
@@ -2361,7 +3050,7 @@
         <v>2019</v>
       </c>
       <c r="G12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H12" t="s">
         <v>67</v>
@@ -2374,7 +3063,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B13" t="s">
@@ -2390,7 +3079,7 @@
         <v>2016</v>
       </c>
       <c r="G13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
@@ -2403,7 +3092,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B14" t="s">
@@ -2429,7 +3118,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B15" t="s">
@@ -2458,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B16" t="s">
@@ -2487,7 +3176,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B17" t="s">
@@ -2497,14 +3186,14 @@
         <v>101</v>
       </c>
       <c r="G17" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -2514,14 +3203,14 @@
         <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B19" t="s">
@@ -2534,14 +3223,14 @@
         <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B20" t="s">
@@ -2554,7 +3243,7 @@
         <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H20" t="s">
         <v>114</v>
@@ -2567,7 +3256,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>118</v>
       </c>
       <c r="B21" t="s">
@@ -2577,14 +3266,14 @@
         <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>122</v>
       </c>
       <c r="B22" t="s">
@@ -2613,7 +3302,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B23" t="s">
@@ -2642,370 +3331,607 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G24" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G25" t="s">
+        <v>247</v>
+      </c>
+      <c r="H25" t="s">
+        <v>231</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" t="s">
+        <v>222</v>
+      </c>
+      <c r="G26" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s">
+        <v>223</v>
+      </c>
+      <c r="G27" t="s">
+        <v>250</v>
+      </c>
+      <c r="H27" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" t="s">
         <v>224</v>
       </c>
-      <c r="G25" t="s">
-        <v>251</v>
-      </c>
-      <c r="H25" t="s">
-        <v>235</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C26" t="s">
-        <v>226</v>
-      </c>
-      <c r="G26" t="s">
-        <v>255</v>
-      </c>
-      <c r="H26" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C27" t="s">
-        <v>227</v>
-      </c>
-      <c r="G27" t="s">
-        <v>254</v>
-      </c>
-      <c r="H27" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B28" t="s">
-        <v>220</v>
-      </c>
-      <c r="C28" t="s">
-        <v>228</v>
-      </c>
       <c r="G28" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E29" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F29">
         <v>2018</v>
       </c>
       <c r="G29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I29" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C30" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G30" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H30" t="s">
         <v>43</v>
       </c>
       <c r="J30" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>150</v>
       </c>
       <c r="B31" t="s">
         <v>151</v>
       </c>
+      <c r="C31" t="s">
+        <v>257</v>
+      </c>
+      <c r="G31" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>152</v>
       </c>
       <c r="B32" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="C32" t="s">
+        <v>259</v>
+      </c>
+      <c r="G32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B33" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="C33" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>156</v>
       </c>
       <c r="B34" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="C34" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B35" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="C35" t="s">
+        <v>265</v>
+      </c>
+      <c r="G35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B36" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="C36" t="s">
+        <v>267</v>
+      </c>
+      <c r="D36" t="s">
+        <v>268</v>
+      </c>
+      <c r="E36" t="s">
+        <v>272</v>
+      </c>
+      <c r="F36">
+        <v>2016</v>
+      </c>
+      <c r="G36" t="s">
+        <v>266</v>
+      </c>
+      <c r="H36" t="s">
+        <v>271</v>
+      </c>
+      <c r="I36" t="s">
+        <v>270</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B37" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="C37" t="s">
+        <v>273</v>
+      </c>
+      <c r="G37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B38" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="D38" t="s">
+        <v>277</v>
+      </c>
+      <c r="E38" t="s">
+        <v>278</v>
+      </c>
+      <c r="F38">
+        <v>2016</v>
+      </c>
+      <c r="G38" t="s">
+        <v>275</v>
+      </c>
+      <c r="H38" t="s">
+        <v>276</v>
+      </c>
+      <c r="I38" t="s">
+        <v>274</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B39" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="C39" t="s">
+        <v>280</v>
+      </c>
+      <c r="G39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B40" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="C40" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B41" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="C41" t="s">
+        <v>284</v>
+      </c>
+      <c r="G41" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
         <v>172</v>
       </c>
       <c r="B42" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="C42" t="s">
+        <v>286</v>
+      </c>
+      <c r="G42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>174</v>
       </c>
       <c r="B43" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="C43" t="s">
+        <v>287</v>
+      </c>
+      <c r="G43" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B44" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="C44" t="s">
+        <v>289</v>
+      </c>
+      <c r="G44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B45" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+      <c r="D45" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45">
+        <v>2014</v>
+      </c>
+      <c r="G45" t="s">
+        <v>291</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I45" t="s">
+        <v>292</v>
+      </c>
+      <c r="J45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
         <v>180</v>
       </c>
       <c r="B46" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="E46" t="s">
+        <v>299</v>
+      </c>
+      <c r="F46">
+        <v>2010</v>
+      </c>
+      <c r="G46" t="s">
+        <v>296</v>
+      </c>
+      <c r="H46" t="s">
+        <v>298</v>
+      </c>
+      <c r="I46" t="s">
+        <v>297</v>
+      </c>
+      <c r="J46" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B47" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="C47" t="s">
+        <v>301</v>
+      </c>
+      <c r="G47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
         <v>184</v>
       </c>
       <c r="B48" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="C48" t="s">
+        <v>303</v>
+      </c>
+      <c r="G48" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B49" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="C49" t="s">
+        <v>305</v>
+      </c>
+      <c r="G49" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
         <v>188</v>
       </c>
       <c r="B50" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="C50" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
         <v>190</v>
       </c>
       <c r="B51" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51">
+        <v>2015</v>
+      </c>
+      <c r="G51" t="s">
+        <v>302</v>
+      </c>
+      <c r="H51" t="s">
+        <v>310</v>
+      </c>
+      <c r="I51" t="s">
+        <v>309</v>
+      </c>
+      <c r="J51" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
         <v>192</v>
       </c>
       <c r="B52" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="C52" t="s">
+        <v>321</v>
+      </c>
+      <c r="D52" t="s">
+        <v>315</v>
+      </c>
+      <c r="E52" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52">
+        <v>2015</v>
+      </c>
+      <c r="G52" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
         <v>194</v>
       </c>
       <c r="B53" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
+      <c r="D53" t="s">
+        <v>319</v>
+      </c>
+      <c r="E53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53">
+        <v>2020</v>
+      </c>
+      <c r="G53" t="s">
+        <v>316</v>
+      </c>
+      <c r="H53" t="s">
+        <v>317</v>
+      </c>
+      <c r="I53" t="s">
+        <v>318</v>
+      </c>
+      <c r="J53" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B55" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" t="s">
-        <v>14</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E111" t="s">
-        <v>16</v>
-      </c>
-      <c r="J111" t="s">
-        <v>18</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>200</v>
+      <c r="C111" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C113" t="s">
         <v>32</v>
@@ -3013,156 +3939,142 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C114" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C115" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
+        <v>197</v>
+      </c>
+      <c r="C116" t="s">
         <v>201</v>
-      </c>
-      <c r="C116" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C118" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C119" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C121" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C123" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C124" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C125" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B126" t="s">
-        <v>201</v>
-      </c>
-      <c r="C126" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B127" t="s">
-        <v>201</v>
-      </c>
-      <c r="C127" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B133" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
         <v>14</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C131" t="s">
         <v>15</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E131" t="s">
         <v>16</v>
       </c>
-      <c r="J133" t="s">
+      <c r="J131" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B134" t="s">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
         <v>20</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C132" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B138" s="1"/>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B139" s="1"/>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B140" s="1"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C111" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="C109" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{186B1FBA-DF95-C24D-BFB9-D23FD31DA947}"/>
     <hyperlink ref="J10" r:id="rId3" xr:uid="{DE481A92-C3EB-1B4F-893B-F8F76042E06E}"/>
     <hyperlink ref="J13" r:id="rId4" xr:uid="{DA0B6117-DA00-3344-A87C-4E92D413588C}"/>
     <hyperlink ref="J14" r:id="rId5" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{F665BED2-DA27-0A4D-B108-E2AEFF2279EA}"/>
     <hyperlink ref="J16" r:id="rId6" xr:uid="{65420500-9579-7443-915D-A91EBE5B0664}"/>
     <hyperlink ref="J25" r:id="rId7" xr:uid="{CF8BD6DB-94B1-9141-932F-245AD7AC80AB}"/>
+    <hyperlink ref="J36" r:id="rId8" xr:uid="{2811E055-8240-DD4C-8D14-FEA41F368BA5}"/>
+    <hyperlink ref="J38" r:id="rId9" xr:uid="{EAEB4FD9-29D8-AB4C-9E46-753E9EF7FD53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3C1BD5-1CE3-1F44-9485-4C2944B72B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD6870D-7946-AE4A-9D02-464672399C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="326">
   <si>
     <t>date</t>
   </si>
@@ -1056,6 +1056,18 @@
   </si>
   <si>
     <t>https://www.imdb.com/fr/title/tt5159538/</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYTFmMzhhZGYtZjJlYS00NjdmLWFiY2EtZWUzOTdmY2RmMDljXkEyXkFqcGc@._V1_QL75_UY281_CR11,0,190,281_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BNTUyM2MwMDMtOGU1Mi00YWMxLTlhYmEtYWM4NmU1YTc0OWFkXkEyXkFqcGc@._V1_QL75_UY281_CR27,0,190,281_.jpg</t>
+  </si>
+  <si>
+    <t>https://cdna.artstation.com/p/assets/images/images/045/828/370/large/paul-emile-boucher-tuurngait-poster.jpg?1643647059</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BMTFiOTI4YmYtMDczMy00ZjAyLTg1ZTUtYzdkOWI0ZmJlNjBkXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
   </si>
 </sst>
 </file>
@@ -2451,6 +2463,9 @@
       <c r="H40" t="s">
         <v>283</v>
       </c>
+      <c r="K40" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
@@ -2604,6 +2619,9 @@
       <c r="H47" t="s">
         <v>302</v>
       </c>
+      <c r="K47" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
@@ -2658,6 +2676,9 @@
       <c r="H50" t="s">
         <v>308</v>
       </c>
+      <c r="K50" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
@@ -2717,6 +2738,9 @@
       </c>
       <c r="H52" t="s">
         <v>313</v>
+      </c>
+      <c r="K52" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">

--- a/film.xlsx
+++ b/film.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD6870D-7946-AE4A-9D02-464672399C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0286E9DF-3E51-D64C-AFA0-543AB25329D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="327">
   <si>
     <t>date</t>
   </si>
@@ -1068,6 +1068,9 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/M/MV5BMTFiOTI4YmYtMDczMy00ZjAyLTg1ZTUtYzdkOWI0ZmJlNjBkXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9uWmQIUkdIo</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2317,7 @@
         <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>326</v>
       </c>
       <c r="D34" t="s">
         <v>263</v>

--- a/film.xlsx
+++ b/film.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0286E9DF-3E51-D64C-AFA0-543AB25329D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D8891A-1B60-824C-AD0B-F681BA7EA3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="402">
   <si>
     <t>date</t>
   </si>
@@ -675,56 +675,6 @@
     <t>https://youtu.be/CfAWTuE9psE?si=Him0sQMqAkuz2JRW</t>
   </si>
   <si>
-    <t>Qestion 1 : Ceci est un test de questions
-Qestion 1 : Ceci est un test de questions
-Qestion 1 : Ceci est un test de questions
-Qestion 1 : Ceci est un test de questions
-Qestion 1 : Ceci est un test de questions
-Qestion 1 : Ceci est un test de questions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iSexOBHpGxE?si=V5QOjq-1kCJu6_Ab</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_0</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_2</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_3</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_4</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_5</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_6</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_7</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_8</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_9</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_10</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_11</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_12</t>
-  </si>
-  <si>
-    <t>https://www.imdb.com/fr/title/tt2476810/?ref_=fn_t_13</t>
-  </si>
-  <si>
     <t>Court, Animation</t>
   </si>
   <si>
@@ -1058,19 +1008,536 @@
     <t>https://www.imdb.com/fr/title/tt5159538/</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/M/MV5BYTFmMzhhZGYtZjJlYS00NjdmLWFiY2EtZWUzOTdmY2RmMDljXkEyXkFqcGc@._V1_QL75_UY281_CR11,0,190,281_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/M/MV5BNTUyM2MwMDMtOGU1Mi00YWMxLTlhYmEtYWM4NmU1YTc0OWFkXkEyXkFqcGc@._V1_QL75_UY281_CR27,0,190,281_.jpg</t>
-  </si>
-  <si>
-    <t>https://cdna.artstation.com/p/assets/images/images/045/828/370/large/paul-emile-boucher-tuurngait-poster.jpg?1643647059</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/M/MV5BMTFiOTI4YmYtMDczMy00ZjAyLTg1ZTUtYzdkOWI0ZmJlNjBkXkEyXkFqcGc@._V1_FMjpg_UX1000_.jpg</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=9uWmQIUkdIo</t>
+    <t>Piper</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=11p9Eg5d6gs</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5613056/</t>
+  </si>
+  <si>
+    <t>Alan Barillaro</t>
+  </si>
+  <si>
+    <t>6 min 00</t>
+  </si>
+  <si>
+    <t>Un jeune bécasseau affamé quitte pour la première fois son nid afin de trouver de la nourriture sur la plage. Mais les coquillages sont enfouis dans le sable, là où les vagues viennent s'écraser. Grâce à un petit bernard-l'hermite, elle apprend à surmonter sa peur de l'eau. Oscar du meilleur court métrage d'animation en 2017.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui est le personnage principal ?
+a. Un jeune bécasseau (petit oiseau)
+b. Un crabe
+c. Une mouette adulte
+Qestion 2 : Pourquoi Piper a-t-elle peur au début du film ?
+a. Elle a peur du bruit
+b. Elle a été surprise par une vague
+c. Elle a peur des autres oiseaux
+Qestion 3 : Qui aide Piper à comprendre comment se protéger des vagues ?
+a. Sa mère
+b. Un petit bernard-l'hermite
+c. Un poisson
+Qestion 4 : Que fait le bernard-l'hermite quand une vague arrive ?
+a. Il s'enfouit dans le sable
+b. Il s'enfuit en courant
+c. Il grimpe sur un rocher
+Qestion 5 : Comment se termine le film ?
+a. Piper a toujours peur des vagues
+b. Piper n'ose plus jamais retourner à la plage
+c. Piper n'a plus peur et joue dans les vagues</t>
+  </si>
+  <si>
+    <t>Alike</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kQjtK32mGJQ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5293824/</t>
+  </si>
+  <si>
+    <t>Daniel Martínez Lara, Rafa Cano Méndez</t>
+  </si>
+  <si>
+    <t>8 min 00</t>
+  </si>
+  <si>
+    <t>Animation, Fiction</t>
+  </si>
+  <si>
+    <t>Dans une ville grise où tout est réglé comme du papier à musique, Copi, un père très occupé, tente d'enseigner à son fils Paste la « bonne » façon de faire les choses. Mais Paste préfère dessiner et rêver plutôt que suivre les règles. Le film interroge avec poésie la place de la créativité et de la spontanéité face à la routine du quotidien.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui sont les deux personnages principaux ?
+a. Deux frères
+b. Un père (Copi) et son fils (Paste)
+c. Un maître et son élève
+Qestion 2 : Que fait Paste à l'école au lieu d'apprendre comme les autres enfants ?
+a. Il dort
+b. Il dessine et laisse parler son imagination
+c. Il joue avec ses camarades
+Qestion 3 : Qui, dans la ville grise, attire l'attention de Paste chaque matin ?
+a. Un violoniste dans la rue
+b. Un vendeur de journaux
+c. Un policier
+Qestion 4 : Que devient Copi au fil du film, à force de travailler sans relâche ?
+a. Il devient de plus en plus gris et fatigué
+b. Il devient de plus en plus coloré
+c. Il quitte son travail
+Qestion 5 : Comment Copi retrouve-t-il de la couleur et de la joie à la fin ?
+a. En prenant des vacances
+b. En imitant le violoniste pour son fils
+c. En achetant un cadeau à Paste</t>
+  </si>
+  <si>
+    <t>Kitbull</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-hOYcTfEbGs</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt9536832/</t>
+  </si>
+  <si>
+    <t>Rosana Sullivan</t>
+  </si>
+  <si>
+    <t>9 min 00</t>
+  </si>
+  <si>
+    <t>Animation, Court, Drame, Famille</t>
+  </si>
+  <si>
+    <t>Un chaton errant, farouchement indépendant, et un pitbull maltraité par son propriétaire se croisent dans une ruelle. Malgré leurs différences, une amitié improbable naît entre eux, jusqu'à ce que le chat aide le chien à échapper à son maître. Court métrage Pixar du programme SparkShorts, entièrement dessiné à la main.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui sont les deux animaux principaux de l'histoire ?
+a. Un chaton errant et un pitbull
+b. Un chien et un oiseau
+c. Deux chatons
+Qestion 2 : Comment le pitbull est-il traité au début du film ?
+a. Il est choyé par son maître
+b. Il est maltraité et enchaîné
+c. Il vit en liberté dans la rue
+Qestion 3 : Comment naît l'amitié entre le chaton et le pitbull ?
+a. Ils se battent d'abord puis apprennent à se faire confiance
+b. Ils sont amis dès leur première rencontre
+c. Ils sont réunis par un humain
+Qestion 4 : Qu'est-ce que le chaton aide le pitbull à faire ?
+a. À trouver de la nourriture
+b. À s'échapper de son enclos
+c. À apprendre à miauler
+Qestion 5 : Comment se termine le film ?
+a. Les deux animaux sont adoptés et vivent heureux ensemble
+b. Ils se perdent de vue
+c. Le chaton part seul</t>
+  </si>
+  <si>
+    <t>Day &amp; Night (Jour et Nuit)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wmk9uFGRCRw</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1620446/</t>
+  </si>
+  <si>
+    <t>Teddy Newton</t>
+  </si>
+  <si>
+    <t>Deux personnages opposés, Jour et Nuit, se rencontrent et se méfient d'abord l'un de l'autre. Chacun porte en lui un monde différent (scènes de jour ou de nuit) qu'ils découvrent peu à peu chez l'autre, jusqu'à devenir amis. Nommé aux Oscars 2011.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui sont les deux personnages principaux ?
+a. Jour et Nuit
+b. Deux nuages
+c. Le soleil et la lune
+Qestion 2 : Comment réagissent Jour et Nuit lorsqu'ils se rencontrent ?
+a. Ils sont amis immédiatement
+b. Ils se méfient l'un de l'autre
+c. Ils se battent violemment
+Qestion 3 : Que voit-on à l'intérieur du corps de chaque personnage ?
+a. Des scènes de la vie de jour ou de nuit
+b. Des étoiles uniquement
+c. Rien du tout
+Qestion 4 : Comment évolue leur relation au fil du film ?
+a. Ils restent ennemis
+b. Ils deviennent amis en découvrant leurs qualités
+c. Ils se séparent définitivement
+Qestion 5 : Quelle leçon peut-on tirer de ce film ?
+a. Il faut se méfier de ce qui est différent
+b. Les différences peuvent être une richesse
+c. Il vaut mieux rester seul</t>
+  </si>
+  <si>
+    <t>Le Joueur d'échecs (Geri's Game)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9IYRC7g2ICg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt0131409/</t>
+  </si>
+  <si>
+    <t>Jan Pinkava</t>
+  </si>
+  <si>
+    <t>5 min 00</t>
+  </si>
+  <si>
+    <t>Un vieil homme, Geri, joue une partie d'échecs en solitaire dans un parc, incarnant tour à tour les deux joueurs. Quand son « adversaire » prend l'avantage, il utilise une ruse astucieuse pour renverser la partie. Oscar du meilleur court métrage d'animation en 1998.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Où se déroule la scène ?
+a. Dans un parc
+b. Dans une maison
+c. Dans un café
+Qestion 2 : Contre qui Geri joue-t-il aux échecs ?
+a. Contre un autre vieil homme
+b. Contre lui-même
+c. Contre un enfant
+Qestion 3 : Comment Geri change-t-il de personnage entre les deux joueurs ?
+a. Il change de vêtements
+b. Il change de place et met ou enlève ses lunettes
+c. Il ferme les yeux
+Qestion 4 : Que fait Geri quand il semble sur le point de perdre ?
+a. Il abandonne la partie
+b. Il fait semblant d'avoir un malaise
+c. Il renverse l'échiquier
+Qestion 5 : Comment se termine la partie ?
+a. Geri perd
+b. Geri gagne grâce à sa ruse
+c. La partie n'est jamais terminée</t>
+  </si>
+  <si>
+    <t>Fresh Guacamole</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dNJdJIwCF_Y</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2309977/</t>
+  </si>
+  <si>
+    <t>PES</t>
+  </si>
+  <si>
+    <t>1 min 40</t>
+  </si>
+  <si>
+    <t>Animation, Stop motion</t>
+  </si>
+  <si>
+    <t>Sans aucune parole, une paire de mains prépare du guacamole en utilisant des objets du quotidien à la place des vrais ingrédients : une grenade en guise d'avocat, des dés à la place de l'oignon coupé, des jetons de poker en guise de chips. Le plus court film jamais nommé aux Oscars.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Quelle technique d'animation est utilisée dans ce film ?
+a. Le dessin animé classique
+b. Le stop motion (image par image)
+c. L'animation 3D par ordinateur
+Qestion 2 : Quel objet remplace l'avocat ?
+a. Un ballon
+b. Une grenade
+c. Une balle de tennis
+Qestion 3 : Que deviennent les objets une fois « coupés » ?
+a. Ils disparaissent
+b. Ils se transforment en dés
+c. Ils explosent
+Qestion 4 : Qu'est-ce qui remplace les chips à la fin ?
+a. Des jetons de poker
+b. Des pièces de monnaie
+c. Des cartes à jouer
+Qestion 5 : Quelle est la particularité de ce court métrage dans l'histoire des Oscars ?
+a. C'est le plus long film jamais nommé
+b. C'est le plus court film jamais nommé aux Oscars
+c. C'est le premier film en couleur</t>
+  </si>
+  <si>
+    <t>Western Spaghetti</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qBjLW5_dGAM</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1352849/</t>
+  </si>
+  <si>
+    <t>1 min 42</t>
+  </si>
+  <si>
+    <t>Toujours sans parole et en stop-motion, PES prépare un plat de spaghettis en détournant des objets du quotidien : des élastiques pour les pâtes, un Rubik's Cube pour l'ail, du papier bulle pour l'eau bouillante. Le tout premier film de la série « cuisine » de PES.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Quel plat est préparé dans ce film ?
+a. Une pizza
+b. Des spaghettis
+c. Une salade
+Qestion 2 : Que remplacent les élastiques colorés ?
+a. Les spaghettis
+b. Les tomates
+c. Le fromage
+Qestion 3 : Quel objet est utilisé pour représenter l'ail coupé ?
+a. Un Rubik's Cube
+b. Une balle de golf
+c. Un dé à coudre
+Qestion 4 : Comment le film raconte-t-il son histoire ?
+a. Avec beaucoup de dialogues
+b. Sans aucune parole
+c. Avec une voix off
+Qestion 5 : Quel autre court métrage du même réalisateur est la suite de celui-ci ?
+a. Fresh Guacamole
+b. Kitbull
+c. Piper</t>
+  </si>
+  <si>
+    <t>Maestro</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/359281775</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt10651548/</t>
+  </si>
+  <si>
+    <t>Illogic (Florian Babikian, Victor Caire, Théophile Dufresne, Gabriel Grapperon, Lucas Navarro)</t>
+  </si>
+  <si>
+    <t>2 min 00</t>
+  </si>
+  <si>
+    <t>Animation 3D</t>
+  </si>
+  <si>
+    <t>Au cœur d'une forêt, en pleine nuit, un écureuil chef d'orchestre réunit tous les animaux (oiseaux, hérissons, grenouilles, tortues, poissons, un cerf...) pour un concert d'opéra improvisé, sur une musique classique flamboyante.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui dirige le concert dans la forêt ?
+a. Un cerf
+b. Un écureuil
+c. Un oiseau
+Qestion 2 : Quand se déroule la scène ?
+a. En plein jour
+b. La nuit
+c. Au lever du soleil
+Qestion 3 : Quels types d'animaux participent au concert ?
+a. Seulement des oiseaux
+b. Une grande variété d'animaux de la forêt
+c. Seulement des poissons
+Qestion 4 : Comment les animaux communiquent-ils leur musique ?
+a. En parlant
+b. En chantant et en jouant sans aucun dialogue
+c. Avec des instruments électroniques
+Qestion 5 : Quel est le style musical du film ?
+a. Du rock
+b. De l'opéra classique
+c. De la musique électronique</t>
+  </si>
+  <si>
+    <t>Oktapodi</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uhQu4HqT7y8</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1323941/</t>
+  </si>
+  <si>
+    <t>Julien Bocabeille, François-Xavier Chanioux, Olivier Delabarre, Thierry Marchand, Quentin Marmier, Emud Mokhberi</t>
+  </si>
+  <si>
+    <t>2 min 26</t>
+  </si>
+  <si>
+    <t>Deux poulpes amoureux vivent tranquillement dans un aquarium jusqu'au jour où l'un d'eux est enlevé par un cuisinier. L'autre poulpe se lance dans une course-poursuite effrénée à travers un village grec pour le sauver. Film de fin d'études des Gobelins, nommé aux Oscars 2009.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Où vivent les deux poulpes au début du film ?
+a. Dans la mer
+b. Dans un aquarium
+c. Dans une piscine
+Qestion 2 : Qui enlève l'un des deux poulpes ?
+a. Un pêcheur
+b. Un cuisinier
+c. Un enfant
+Qestion 3 : Où se déroule la course-poursuite ?
+a. Dans un village grec
+b. Dans une grande ville
+c. Sous l'eau
+Qestion 4 : Ce court métrage a été réalisé par :
+a. Des étudiants de l'école Gobelins
+b. Les studios Pixar
+c. Un réalisateur japonais
+Qestion 5 : Comment se termine l'histoire ?
+a. Les deux poulpes sont séparés pour toujours
+b. Les deux poulpes se retrouvent et restent ensemble
+c. Le cuisinier attrape les deux poulpes</t>
+  </si>
+  <si>
+    <t>Hair Love</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VV2wroJE5v4</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt7129636/</t>
+  </si>
+  <si>
+    <t>Matthew A. Cherry, Everett Downing Jr., Bruce W. Smith</t>
+  </si>
+  <si>
+    <t>Animation, Comédie, Famille</t>
+  </si>
+  <si>
+    <t>Zuri, une petite fille aux cheveux bouclés, tente pour la première fois de se coiffer seule. Face à la difficulté, son papa vient l'aider et, ensemble, ils y arrivent, avant d'aller rendre visite à la maman de Zuri, hospitalisée. Oscar du meilleur court métrage d'animation en 2020. Note : le film évoque la maladie d'un parent (la maman hospitalisée a perdu ses cheveux) — sujet sensible à connaître avant diffusion en classe.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Que tente de faire Zuri au début du film ?
+a. Coiffer ses cheveux toute seule
+b. Faire du vélo
+c. Cuisiner un gâteau
+Qestion 2 : Qui vient l'aider quand elle n'y arrive pas ?
+a. Son grand frère
+b. Son papa
+c. Sa maîtresse
+Qestion 3 : Comment le papa apprend-il à coiffer sa fille ?
+a. Il devine tout seul
+b. Il regarde une vidéo tuto enregistrée par la maman
+c. Il demande à une amie
+Qestion 4 : Où se rendent Zuri et son papa à la fin du film ?
+a. À l'école
+b. À l'hôpital pour voir la maman
+c. Au parc
+Qestion 5 : Ce court métrage a reçu quelle récompense ?
+a. Le prix du public à Cannes
+b. L'Oscar du meilleur court métrage d'animation
+c. Aucune récompense</t>
+  </si>
+  <si>
+    <t>Paperman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jo_pJkWuUyQ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt2388725/</t>
+  </si>
+  <si>
+    <t>John Kahrs</t>
+  </si>
+  <si>
+    <t>6 min 33</t>
+  </si>
+  <si>
+    <t>Animation, Comédie romantique</t>
+  </si>
+  <si>
+    <t>Dans le New York des années 1940, un jeune employé de bureau croise le regard d'une jeune femme sur un quai de gare. Pour tenter de la retrouver, il utilise une flotte d'avions en papier lancés depuis la fenêtre de son bureau. Film en noir et blanc, sans aucun dialogue. Oscar du meilleur court métrage d'animation en 2013.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Où et quand se déroule l'histoire ?
+a. À Paris, de nos jours
+b. À New York, dans les années 1940
+c. À Londres, dans le futur
+Qestion 2 : Comment le jeune homme et la jeune femme se rencontrent-ils la première fois ?
+a. Dans un café
+b. Sur un quai de gare, à cause du vent
+c. Au cinéma
+Qestion 3 : Que jette le jeune homme depuis la fenêtre de son bureau ?
+a. Des fleurs
+b. Des avions en papier
+c. Des ballons
+Qestion 4 : Dans quel style le film est-il réalisé ?
+a. En couleur et en 3D
+b. En noir et blanc
+c. En dessin animé classique coloré
+Qestion 5 : Quelle récompense ce court métrage a-t-il reçue ?
+a. Aucune
+b. L'Oscar du meilleur court métrage d'animation
+c. Le prix du public à Annecy seulement</t>
+  </si>
+  <si>
+    <t>Changeover</t>
+  </si>
+  <si>
+    <t>https://vimeo.com/220937184</t>
+  </si>
+  <si>
+    <t>Mehdi Alibeygi</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>Animation 2D, Comédie</t>
+  </si>
+  <si>
+    <t>Un petit oiseau séducteur survole un terrain de badminton et tombe sous le charme d'un volant resté coincé dans un coin du terrain, le prenant pour une compagne. Il déploie tout son numéro de séduction... jusqu'à un dénouement inattendu et comique.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Que fait l'oiseau au-dessus du terrain de badminton ?
+a. Il cherche à manger
+b. Il tombe amoureux d'un volant de badminton
+c. Il construit un nid
+Qestion 2 : Pourquoi l'oiseau est-il attiré par le volant ?
+a. Il le prend pour un autre oiseau
+b. Il veut le manger
+c. Il veut jouer au badminton
+Qestion 3 : Que fait l'oiseau pour séduire le volant ?
+a. Il chante et parade autour de lui
+b. Il l'ignore complètement
+c. Il s'envole loin
+Qestion 4 : Dans quel pays le réalisateur de ce film est-il né ?
+a. En France
+b. En Iran
+c. Au Japon
+Qestion 5 : Comment se termine le film, de façon comique ?
+a. L'oiseau part avec le volant
+b. Une raquette de badminton interrompt la scène
+c. Le volant se transforme en oiseau</t>
+  </si>
+  <si>
+    <t>Twin Islands</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fdr5fthfCOw</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt12612778/</t>
+  </si>
+  <si>
+    <t>Manon Sailly, Lara Cochetel, Raphaël Huot, Christine Jaudoin, Charlotte Sarfati, Fanny Teisson</t>
+  </si>
+  <si>
+    <t>10 min 00</t>
+  </si>
+  <si>
+    <t>Animation 3D, Fantastique</t>
+  </si>
+  <si>
+    <t>Deux frères jumeaux, sauvés de la noyade par des dieux, reçoivent chacun une île identique à gouverner selon une seule règle : tout doit y être symétrique et en double. Mais le jour où la reine de l'une des îles ne met au monde qu'un seul enfant, l'équilibre du royaume est menacé.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Qui gouverne les deux îles jumelles ?
+a. Deux reines
+b. Deux frères rois
+c. Un seul roi
+Qestion 2 : Quelle règle les habitants des îles doivent-ils respecter ?
+a. Ne jamais se parler
+b. Que tout soit symétrique et en double
+c. Vivre séparés
+Qestion 3 : Quel événement vient bouleverser cet équilibre ?
+a. Une tempête détruit une île
+b. La reine d'une des îles n'a qu'un seul enfant
+c. Les deux rois se disputent
+Qestion 4 : Ce court métrage a été réalisé par :
+a. Des étudiants de l'école Supinfocom
+b. Les studios Pixar
+c. Un réalisateur japonais
+Qestion 5 : Quel thème le film explore-t-il principalement ?
+a. La symétrie et la différence
+b. Le voyage dans le temps
+c. La cuisine</t>
   </si>
 </sst>
 </file>
@@ -1481,11 +1948,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14.83203125" style="3" customWidth="1"/>
     <col min="9" max="9" width="33.5" customWidth="1"/>
+    <col min="11" max="11" width="30.1640625" customWidth="1"/>
     <col min="12" max="12" width="80.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1544,7 +2012,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -1567,7 +2035,7 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -1581,7 +2049,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
@@ -1593,7 +2061,7 @@
         <v>2016</v>
       </c>
       <c r="H4" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1619,7 +2087,7 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -1639,7 +2107,7 @@
         <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="I6" t="s">
         <v>37</v>
@@ -1662,7 +2130,7 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="I7" t="s">
         <v>43</v>
@@ -1682,7 +2150,7 @@
         <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="I8" t="s">
         <v>43</v>
@@ -1705,7 +2173,7 @@
         <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="I9" t="s">
         <v>43</v>
@@ -1734,7 +2202,7 @@
         <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="J10" t="s">
         <v>56</v>
@@ -1757,7 +2225,7 @@
         <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="I11" t="s">
         <v>43</v>
@@ -1783,7 +2251,7 @@
         <v>2019</v>
       </c>
       <c r="H12" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
@@ -1815,7 +2283,7 @@
         <v>2016</v>
       </c>
       <c r="H13" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="I13" t="s">
         <v>73</v>
@@ -1934,7 +2402,7 @@
         <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1954,7 +2422,7 @@
         <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="I18" t="s">
         <v>43</v>
@@ -1977,7 +2445,7 @@
         <v>109</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -2000,7 +2468,7 @@
         <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="I20" t="s">
         <v>114</v>
@@ -2026,7 +2494,7 @@
         <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -2104,13 +2572,13 @@
         <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="H24" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2124,19 +2592,19 @@
         <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H25" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="I25" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -2147,16 +2615,16 @@
         <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="H26" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -2167,16 +2635,16 @@
         <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H27" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="I27" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2187,13 +2655,13 @@
         <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="H28" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2207,28 +2675,28 @@
         <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F29" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G29">
         <v>2018</v>
       </c>
       <c r="H29" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="I29" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J29" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="K29" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2239,19 +2707,19 @@
         <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D30" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H30" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="I30" t="s">
         <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -2266,15 +2734,15 @@
         <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="H31" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <f t="shared" ref="A32:A53" si="0">WORKDAY(A31,1)</f>
+        <f t="shared" ref="A32:A66" si="0">WORKDAY(A31,1)</f>
         <v>46210</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -2284,10 +2752,10 @@
         <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="H32" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -2302,10 +2770,10 @@
         <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="H33" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -2317,13 +2785,13 @@
         <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>326</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="H34" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2338,10 +2806,10 @@
         <v>159</v>
       </c>
       <c r="D35" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="H35" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -2356,28 +2824,28 @@
         <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="E36" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="F36" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="G36">
         <v>2016</v>
       </c>
       <c r="H36" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="I36" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="J36" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2392,10 +2860,10 @@
         <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="H37" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -2410,25 +2878,25 @@
         <v>165</v>
       </c>
       <c r="E38" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="F38" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="G38">
         <v>2016</v>
       </c>
       <c r="H38" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="I38" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="J38" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -2443,10 +2911,10 @@
         <v>167</v>
       </c>
       <c r="D39" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="H39" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -2461,13 +2929,10 @@
         <v>169</v>
       </c>
       <c r="D40" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="H40" t="s">
-        <v>283</v>
-      </c>
-      <c r="K40" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -2482,10 +2947,10 @@
         <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="H41" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -2500,10 +2965,10 @@
         <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="H42" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -2518,10 +2983,10 @@
         <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="H43" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -2536,10 +3001,10 @@
         <v>177</v>
       </c>
       <c r="D44" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="H44" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
@@ -2554,25 +3019,25 @@
         <v>179</v>
       </c>
       <c r="E45" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="F45" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="G45">
         <v>2014</v>
       </c>
       <c r="H45" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="J45" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="K45" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2587,22 +3052,22 @@
         <v>181</v>
       </c>
       <c r="F46" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="G46">
         <v>2010</v>
       </c>
       <c r="H46" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="I46" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="J46" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="K46" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2617,13 +3082,10 @@
         <v>183</v>
       </c>
       <c r="D47" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H47" t="s">
-        <v>302</v>
-      </c>
-      <c r="K47" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2638,10 +3100,10 @@
         <v>185</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="H48" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -2656,10 +3118,10 @@
         <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H49" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -2674,13 +3136,10 @@
         <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="H50" t="s">
-        <v>308</v>
-      </c>
-      <c r="K50" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2695,7 +3154,7 @@
         <v>191</v>
       </c>
       <c r="E51" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="F51" t="s">
         <v>66</v>
@@ -2704,16 +3163,16 @@
         <v>2015</v>
       </c>
       <c r="H51" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I51" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="J51" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="K51" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2728,22 +3187,19 @@
         <v>193</v>
       </c>
       <c r="D52" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="F52" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="G52">
         <v>2015</v>
       </c>
       <c r="H52" t="s">
-        <v>313</v>
-      </c>
-      <c r="K52" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -2758,7 +3214,7 @@
         <v>195</v>
       </c>
       <c r="E53" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="F53" t="s">
         <v>66</v>
@@ -2767,16 +3223,442 @@
         <v>2020</v>
       </c>
       <c r="H53" t="s">
+        <v>301</v>
+      </c>
+      <c r="I53" t="s">
+        <v>302</v>
+      </c>
+      <c r="J53" t="s">
+        <v>303</v>
+      </c>
+      <c r="K53" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
+        <f t="shared" si="0"/>
+        <v>46240</v>
+      </c>
+      <c r="B54" t="s">
+        <v>307</v>
+      </c>
+      <c r="C54" t="s">
+        <v>308</v>
+      </c>
+      <c r="D54" t="s">
+        <v>309</v>
+      </c>
+      <c r="E54" t="s">
+        <v>310</v>
+      </c>
+      <c r="F54" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54">
+        <v>2016</v>
+      </c>
+      <c r="H54" t="s">
+        <v>311</v>
+      </c>
+      <c r="I54" t="s">
+        <v>216</v>
+      </c>
+      <c r="J54" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
+        <f t="shared" si="0"/>
+        <v>46241</v>
+      </c>
+      <c r="B55" t="s">
+        <v>314</v>
+      </c>
+      <c r="C55" t="s">
+        <v>315</v>
+      </c>
+      <c r="D55" t="s">
         <v>316</v>
       </c>
-      <c r="I53" t="s">
+      <c r="E55" t="s">
         <v>317</v>
       </c>
-      <c r="J53" t="s">
+      <c r="F55" t="s">
+        <v>211</v>
+      </c>
+      <c r="G55">
+        <v>2015</v>
+      </c>
+      <c r="H55" t="s">
         <v>318</v>
       </c>
-      <c r="K53" t="s">
+      <c r="I55" t="s">
+        <v>319</v>
+      </c>
+      <c r="J55" t="s">
         <v>320</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="4">
+        <f t="shared" si="0"/>
+        <v>46244</v>
+      </c>
+      <c r="B56" t="s">
+        <v>322</v>
+      </c>
+      <c r="C56" t="s">
+        <v>323</v>
+      </c>
+      <c r="D56" t="s">
+        <v>324</v>
+      </c>
+      <c r="E56" t="s">
+        <v>325</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56">
+        <v>2019</v>
+      </c>
+      <c r="H56" t="s">
+        <v>326</v>
+      </c>
+      <c r="I56" t="s">
+        <v>327</v>
+      </c>
+      <c r="J56" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <f t="shared" si="0"/>
+        <v>46245</v>
+      </c>
+      <c r="B57" t="s">
+        <v>330</v>
+      </c>
+      <c r="C57" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57" t="s">
+        <v>332</v>
+      </c>
+      <c r="E57" t="s">
+        <v>333</v>
+      </c>
+      <c r="F57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57">
+        <v>2010</v>
+      </c>
+      <c r="H57" t="s">
+        <v>311</v>
+      </c>
+      <c r="I57" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <f t="shared" si="0"/>
+        <v>46246</v>
+      </c>
+      <c r="B58" t="s">
+        <v>336</v>
+      </c>
+      <c r="C58" t="s">
+        <v>337</v>
+      </c>
+      <c r="D58" t="s">
+        <v>338</v>
+      </c>
+      <c r="E58" t="s">
+        <v>339</v>
+      </c>
+      <c r="F58" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58">
+        <v>1997</v>
+      </c>
+      <c r="H58" t="s">
+        <v>340</v>
+      </c>
+      <c r="I58" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <f t="shared" si="0"/>
+        <v>46247</v>
+      </c>
+      <c r="B59" t="s">
+        <v>343</v>
+      </c>
+      <c r="C59" t="s">
+        <v>344</v>
+      </c>
+      <c r="D59" t="s">
+        <v>345</v>
+      </c>
+      <c r="E59" t="s">
+        <v>346</v>
+      </c>
+      <c r="F59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59">
+        <v>2012</v>
+      </c>
+      <c r="H59" t="s">
+        <v>347</v>
+      </c>
+      <c r="I59" t="s">
+        <v>348</v>
+      </c>
+      <c r="J59" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <f t="shared" si="0"/>
+        <v>46248</v>
+      </c>
+      <c r="B60" t="s">
+        <v>351</v>
+      </c>
+      <c r="C60" t="s">
+        <v>352</v>
+      </c>
+      <c r="D60" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" t="s">
+        <v>346</v>
+      </c>
+      <c r="F60" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60">
+        <v>2008</v>
+      </c>
+      <c r="H60" t="s">
+        <v>354</v>
+      </c>
+      <c r="I60" t="s">
+        <v>348</v>
+      </c>
+      <c r="J60" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <f t="shared" si="0"/>
+        <v>46251</v>
+      </c>
+      <c r="B61" t="s">
+        <v>357</v>
+      </c>
+      <c r="C61" t="s">
+        <v>358</v>
+      </c>
+      <c r="D61" t="s">
+        <v>359</v>
+      </c>
+      <c r="E61" t="s">
+        <v>360</v>
+      </c>
+      <c r="F61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G61">
+        <v>2019</v>
+      </c>
+      <c r="H61" t="s">
+        <v>361</v>
+      </c>
+      <c r="I61" t="s">
+        <v>362</v>
+      </c>
+      <c r="J61" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <f t="shared" si="0"/>
+        <v>46252</v>
+      </c>
+      <c r="B62" t="s">
+        <v>365</v>
+      </c>
+      <c r="C62" t="s">
+        <v>366</v>
+      </c>
+      <c r="D62" t="s">
+        <v>367</v>
+      </c>
+      <c r="E62" t="s">
+        <v>368</v>
+      </c>
+      <c r="F62" t="s">
+        <v>66</v>
+      </c>
+      <c r="G62">
+        <v>2007</v>
+      </c>
+      <c r="H62" t="s">
+        <v>369</v>
+      </c>
+      <c r="I62" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <f t="shared" si="0"/>
+        <v>46253</v>
+      </c>
+      <c r="B63" t="s">
+        <v>372</v>
+      </c>
+      <c r="C63" t="s">
+        <v>373</v>
+      </c>
+      <c r="D63" t="s">
+        <v>374</v>
+      </c>
+      <c r="E63" t="s">
+        <v>375</v>
+      </c>
+      <c r="F63" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63">
+        <v>2019</v>
+      </c>
+      <c r="H63" t="s">
+        <v>311</v>
+      </c>
+      <c r="I63" t="s">
+        <v>376</v>
+      </c>
+      <c r="J63" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <f t="shared" si="0"/>
+        <v>46254</v>
+      </c>
+      <c r="B64" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s">
+        <v>380</v>
+      </c>
+      <c r="D64" t="s">
+        <v>381</v>
+      </c>
+      <c r="E64" t="s">
+        <v>382</v>
+      </c>
+      <c r="F64" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64">
+        <v>2012</v>
+      </c>
+      <c r="H64" t="s">
+        <v>383</v>
+      </c>
+      <c r="I64" t="s">
+        <v>384</v>
+      </c>
+      <c r="J64" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <f t="shared" si="0"/>
+        <v>46255</v>
+      </c>
+      <c r="B65" t="s">
+        <v>387</v>
+      </c>
+      <c r="C65" t="s">
+        <v>388</v>
+      </c>
+      <c r="E65" t="s">
+        <v>389</v>
+      </c>
+      <c r="F65" t="s">
+        <v>390</v>
+      </c>
+      <c r="G65">
+        <v>2015</v>
+      </c>
+      <c r="H65" t="s">
+        <v>361</v>
+      </c>
+      <c r="I65" t="s">
+        <v>391</v>
+      </c>
+      <c r="J65" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <f t="shared" si="0"/>
+        <v>46258</v>
+      </c>
+      <c r="B66" t="s">
+        <v>394</v>
+      </c>
+      <c r="C66" t="s">
+        <v>395</v>
+      </c>
+      <c r="D66" t="s">
+        <v>396</v>
+      </c>
+      <c r="E66" t="s">
+        <v>397</v>
+      </c>
+      <c r="F66" t="s">
+        <v>66</v>
+      </c>
+      <c r="G66">
+        <v>2017</v>
+      </c>
+      <c r="H66" t="s">
+        <v>398</v>
+      </c>
+      <c r="I66" t="s">
+        <v>399</v>
+      </c>
+      <c r="J66" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -2787,14 +3669,14 @@
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="K10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K16" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K25" r:id="rId6" xr:uid="{66BBCC3E-C4CA-8040-86BD-5AD2C72A2FB3}"/>
-    <hyperlink ref="K36" r:id="rId7" xr:uid="{43E0665D-98BD-8A45-9566-CB982DEB8884}"/>
-    <hyperlink ref="K38" r:id="rId8" xr:uid="{A2A4E428-F265-9E48-917E-4F7835CEDB03}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{84B21FBE-5522-2349-9ED7-1CF7C91EFD61}"/>
+    <hyperlink ref="K10" r:id="rId2" xr:uid="{7DCFB6F7-350B-244A-A4EE-0FEDC3FAD578}"/>
+    <hyperlink ref="K13" r:id="rId3" xr:uid="{F1F97A12-E06B-3042-A44B-81659830FCF3}"/>
+    <hyperlink ref="K14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{4A97EF13-2B9A-5048-90A6-32D3CB3D9118}"/>
+    <hyperlink ref="K16" r:id="rId5" xr:uid="{8F831C98-E96E-C54A-919D-D4130B8003F3}"/>
+    <hyperlink ref="K25" r:id="rId6" xr:uid="{132034D3-17B4-3541-BBC2-3479C0C36EF6}"/>
+    <hyperlink ref="K36" r:id="rId7" xr:uid="{A83A35F1-3AE1-C84D-8BB6-EB29F7D17B61}"/>
+    <hyperlink ref="K38" r:id="rId8" xr:uid="{F1E8F208-0997-6A48-9639-AC5B9CB22618}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2803,14 +3685,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="11" max="11" width="90.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="11" width="64.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -2862,7 +3741,7 @@
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -2885,7 +3764,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -2899,7 +3778,7 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -2911,7 +3790,7 @@
         <v>2016</v>
       </c>
       <c r="G4" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H4" t="s">
         <v>26</v>
@@ -2923,7 +3802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -2934,7 +3813,7 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -2951,7 +3830,7 @@
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="H6" t="s">
         <v>37</v>
@@ -2971,13 +3850,13 @@
         <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="H7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -2988,13 +3867,13 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="H8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -3008,7 +3887,7 @@
         <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H9" t="s">
         <v>43</v>
@@ -3034,7 +3913,7 @@
         <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I10" t="s">
         <v>56</v>
@@ -3054,13 +3933,13 @@
         <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="H11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="119" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>63</v>
       </c>
@@ -3077,7 +3956,7 @@
         <v>2019</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="H12" t="s">
         <v>67</v>
@@ -3106,7 +3985,7 @@
         <v>2016</v>
       </c>
       <c r="G13" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
@@ -3213,7 +4092,7 @@
         <v>101</v>
       </c>
       <c r="G17" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -3230,7 +4109,7 @@
         <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="H18" t="s">
         <v>43</v>
@@ -3250,7 +4129,7 @@
         <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
@@ -3270,7 +4149,7 @@
         <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="H20" t="s">
         <v>114</v>
@@ -3293,13 +4172,13 @@
         <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>122</v>
       </c>
@@ -3362,13 +4241,13 @@
         <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="G24" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
@@ -3379,19 +4258,19 @@
         <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G25" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -3399,16 +4278,16 @@
         <v>145</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="G26" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H26" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -3416,16 +4295,16 @@
         <v>146</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G27" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="H27" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -3433,13 +4312,13 @@
         <v>147</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G28" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -3450,28 +4329,28 @@
         <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="F29">
         <v>2018</v>
       </c>
       <c r="G29" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H29" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="I29" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -3479,19 +4358,19 @@
         <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G30" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H30" t="s">
         <v>43</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -3502,10 +4381,10 @@
         <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="G31" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -3516,10 +4395,10 @@
         <v>153</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G32" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -3530,10 +4409,10 @@
         <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="G33" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -3544,10 +4423,10 @@
         <v>157</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="G34" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -3558,10 +4437,10 @@
         <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G35" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -3572,28 +4451,28 @@
         <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D36" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="E36" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F36">
         <v>2016</v>
       </c>
       <c r="G36" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="H36" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="I36" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -3604,10 +4483,10 @@
         <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="G37" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -3618,25 +4497,25 @@
         <v>165</v>
       </c>
       <c r="D38" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E38" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="F38">
         <v>2016</v>
       </c>
       <c r="G38" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="H38" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="I38" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -3647,10 +4526,10 @@
         <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="G39" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -3661,10 +4540,10 @@
         <v>169</v>
       </c>
       <c r="C40" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="G40" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -3675,10 +4554,10 @@
         <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="G41" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -3689,10 +4568,10 @@
         <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="G42" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -3703,10 +4582,10 @@
         <v>175</v>
       </c>
       <c r="C43" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="G43" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -3717,13 +4596,13 @@
         <v>177</v>
       </c>
       <c r="C44" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="G44" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>178</v>
       </c>
@@ -3731,25 +4610,25 @@
         <v>179</v>
       </c>
       <c r="D45" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F45">
         <v>2014</v>
       </c>
       <c r="G45" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="I45" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J45" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -3760,22 +4639,22 @@
         <v>181</v>
       </c>
       <c r="E46" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="F46">
         <v>2010</v>
       </c>
       <c r="G46" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="H46" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I46" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="J46" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -3786,10 +4665,10 @@
         <v>183</v>
       </c>
       <c r="C47" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="G47" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -3800,13 +4679,13 @@
         <v>185</v>
       </c>
       <c r="C48" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G48" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>186</v>
       </c>
@@ -3814,13 +4693,13 @@
         <v>187</v>
       </c>
       <c r="C49" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G49" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>188</v>
       </c>
@@ -3828,13 +4707,13 @@
         <v>189</v>
       </c>
       <c r="C50" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="G50" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>190</v>
       </c>
@@ -3842,7 +4721,7 @@
         <v>191</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="E51" t="s">
         <v>66</v>
@@ -3851,19 +4730,19 @@
         <v>2015</v>
       </c>
       <c r="G51" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="H51" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="I51" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="J51" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>192</v>
       </c>
@@ -3871,22 +4750,22 @@
         <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="E52" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="F52">
         <v>2015</v>
       </c>
       <c r="G52" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>194</v>
       </c>
@@ -3894,7 +4773,7 @@
         <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="E53" t="s">
         <v>66</v>
@@ -3903,205 +4782,441 @@
         <v>2020</v>
       </c>
       <c r="G53" t="s">
+        <v>301</v>
+      </c>
+      <c r="H53" t="s">
+        <v>302</v>
+      </c>
+      <c r="I53" t="s">
+        <v>303</v>
+      </c>
+      <c r="J53" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>307</v>
+      </c>
+      <c r="B54" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" t="s">
+        <v>309</v>
+      </c>
+      <c r="D54" t="s">
+        <v>310</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54">
+        <v>2016</v>
+      </c>
+      <c r="G54" t="s">
+        <v>311</v>
+      </c>
+      <c r="H54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I54" t="s">
+        <v>312</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>314</v>
+      </c>
+      <c r="B55" t="s">
+        <v>315</v>
+      </c>
+      <c r="C55" t="s">
         <v>316</v>
       </c>
-      <c r="H53" t="s">
+      <c r="D55" t="s">
         <v>317</v>
       </c>
-      <c r="I53" t="s">
+      <c r="E55" t="s">
+        <v>211</v>
+      </c>
+      <c r="F55">
+        <v>2015</v>
+      </c>
+      <c r="G55" t="s">
         <v>318</v>
       </c>
-      <c r="J53" t="s">
+      <c r="H55" t="s">
+        <v>319</v>
+      </c>
+      <c r="I55" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="109" spans="2:11" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" t="s">
-        <v>14</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E109" t="s">
-        <v>16</v>
-      </c>
-      <c r="J109" t="s">
-        <v>18</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B110" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B111" t="s">
-        <v>197</v>
-      </c>
-      <c r="C111" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B112" t="s">
-        <v>197</v>
-      </c>
-      <c r="C112" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B113" t="s">
-        <v>197</v>
-      </c>
-      <c r="C113" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B114" t="s">
-        <v>197</v>
-      </c>
-      <c r="C114" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B115" t="s">
-        <v>197</v>
-      </c>
-      <c r="C115" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B116" t="s">
-        <v>197</v>
-      </c>
-      <c r="C116" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B117" t="s">
-        <v>197</v>
-      </c>
-      <c r="C117" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B118" t="s">
-        <v>197</v>
-      </c>
-      <c r="C118" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B119" t="s">
-        <v>197</v>
-      </c>
-      <c r="C119" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B120" t="s">
-        <v>197</v>
-      </c>
-      <c r="C120" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B121" t="s">
-        <v>197</v>
-      </c>
-      <c r="C121" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B122" t="s">
-        <v>197</v>
-      </c>
-      <c r="C122" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B123" t="s">
-        <v>197</v>
-      </c>
-      <c r="C123" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B124" t="s">
-        <v>197</v>
-      </c>
-      <c r="C124" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B125" t="s">
-        <v>197</v>
-      </c>
-      <c r="C125" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B131" t="s">
-        <v>14</v>
-      </c>
-      <c r="C131" t="s">
-        <v>15</v>
-      </c>
-      <c r="E131" t="s">
-        <v>16</v>
-      </c>
-      <c r="J131" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B132" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B139" s="1"/>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B140" s="1"/>
+      <c r="K55" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>322</v>
+      </c>
+      <c r="B56" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56">
+        <v>2019</v>
+      </c>
+      <c r="G56" t="s">
+        <v>326</v>
+      </c>
+      <c r="H56" t="s">
+        <v>327</v>
+      </c>
+      <c r="I56" t="s">
+        <v>328</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>330</v>
+      </c>
+      <c r="B57" t="s">
+        <v>331</v>
+      </c>
+      <c r="C57" t="s">
+        <v>332</v>
+      </c>
+      <c r="D57" t="s">
+        <v>333</v>
+      </c>
+      <c r="E57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57">
+        <v>2010</v>
+      </c>
+      <c r="G57" t="s">
+        <v>311</v>
+      </c>
+      <c r="H57" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" t="s">
+        <v>334</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>336</v>
+      </c>
+      <c r="B58" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" t="s">
+        <v>339</v>
+      </c>
+      <c r="E58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58">
+        <v>1997</v>
+      </c>
+      <c r="G58" t="s">
+        <v>340</v>
+      </c>
+      <c r="H58" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" t="s">
+        <v>341</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>343</v>
+      </c>
+      <c r="B59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C59" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" t="s">
+        <v>346</v>
+      </c>
+      <c r="E59" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59">
+        <v>2012</v>
+      </c>
+      <c r="G59" t="s">
+        <v>347</v>
+      </c>
+      <c r="H59" t="s">
+        <v>348</v>
+      </c>
+      <c r="I59" t="s">
+        <v>349</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>351</v>
+      </c>
+      <c r="B60" t="s">
+        <v>352</v>
+      </c>
+      <c r="C60" t="s">
+        <v>353</v>
+      </c>
+      <c r="D60" t="s">
+        <v>346</v>
+      </c>
+      <c r="E60" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60">
+        <v>2008</v>
+      </c>
+      <c r="G60" t="s">
+        <v>354</v>
+      </c>
+      <c r="H60" t="s">
+        <v>348</v>
+      </c>
+      <c r="I60" t="s">
+        <v>355</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>357</v>
+      </c>
+      <c r="B61" t="s">
+        <v>358</v>
+      </c>
+      <c r="C61" t="s">
+        <v>359</v>
+      </c>
+      <c r="D61" t="s">
+        <v>360</v>
+      </c>
+      <c r="E61" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61">
+        <v>2019</v>
+      </c>
+      <c r="G61" t="s">
+        <v>361</v>
+      </c>
+      <c r="H61" t="s">
+        <v>362</v>
+      </c>
+      <c r="I61" t="s">
+        <v>363</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>365</v>
+      </c>
+      <c r="B62" t="s">
+        <v>366</v>
+      </c>
+      <c r="C62" t="s">
+        <v>367</v>
+      </c>
+      <c r="D62" t="s">
+        <v>368</v>
+      </c>
+      <c r="E62" t="s">
+        <v>66</v>
+      </c>
+      <c r="F62">
+        <v>2007</v>
+      </c>
+      <c r="G62" t="s">
+        <v>369</v>
+      </c>
+      <c r="H62" t="s">
+        <v>43</v>
+      </c>
+      <c r="I62" t="s">
+        <v>370</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>372</v>
+      </c>
+      <c r="B63" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" t="s">
+        <v>374</v>
+      </c>
+      <c r="D63" t="s">
+        <v>375</v>
+      </c>
+      <c r="E63" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63">
+        <v>2019</v>
+      </c>
+      <c r="G63" t="s">
+        <v>311</v>
+      </c>
+      <c r="H63" t="s">
+        <v>376</v>
+      </c>
+      <c r="I63" t="s">
+        <v>377</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B64" t="s">
+        <v>380</v>
+      </c>
+      <c r="C64" t="s">
+        <v>381</v>
+      </c>
+      <c r="D64" t="s">
+        <v>382</v>
+      </c>
+      <c r="E64" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64">
+        <v>2012</v>
+      </c>
+      <c r="G64" t="s">
+        <v>383</v>
+      </c>
+      <c r="H64" t="s">
+        <v>384</v>
+      </c>
+      <c r="I64" t="s">
+        <v>385</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>387</v>
+      </c>
+      <c r="B65" t="s">
+        <v>388</v>
+      </c>
+      <c r="D65" t="s">
+        <v>389</v>
+      </c>
+      <c r="E65" t="s">
+        <v>390</v>
+      </c>
+      <c r="F65">
+        <v>2015</v>
+      </c>
+      <c r="G65" t="s">
+        <v>361</v>
+      </c>
+      <c r="H65" t="s">
+        <v>391</v>
+      </c>
+      <c r="I65" t="s">
+        <v>392</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" t="s">
+        <v>395</v>
+      </c>
+      <c r="C66" t="s">
+        <v>396</v>
+      </c>
+      <c r="D66" t="s">
+        <v>397</v>
+      </c>
+      <c r="E66" t="s">
+        <v>66</v>
+      </c>
+      <c r="F66">
+        <v>2017</v>
+      </c>
+      <c r="G66" t="s">
+        <v>398</v>
+      </c>
+      <c r="H66" t="s">
+        <v>399</v>
+      </c>
+      <c r="I66" t="s">
+        <v>400</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>401</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C109" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{186B1FBA-DF95-C24D-BFB9-D23FD31DA947}"/>
-    <hyperlink ref="J10" r:id="rId3" xr:uid="{DE481A92-C3EB-1B4F-893B-F8F76042E06E}"/>
-    <hyperlink ref="J13" r:id="rId4" xr:uid="{DA0B6117-DA00-3344-A87C-4E92D413588C}"/>
-    <hyperlink ref="J14" r:id="rId5" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{F665BED2-DA27-0A4D-B108-E2AEFF2279EA}"/>
-    <hyperlink ref="J16" r:id="rId6" xr:uid="{65420500-9579-7443-915D-A91EBE5B0664}"/>
-    <hyperlink ref="J25" r:id="rId7" xr:uid="{CF8BD6DB-94B1-9141-932F-245AD7AC80AB}"/>
-    <hyperlink ref="J36" r:id="rId8" xr:uid="{2811E055-8240-DD4C-8D14-FEA41F368BA5}"/>
-    <hyperlink ref="J38" r:id="rId9" xr:uid="{EAEB4FD9-29D8-AB4C-9E46-753E9EF7FD53}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{C7C0FD43-0AE7-8E4A-8BD5-94D16E8267CE}"/>
+    <hyperlink ref="J10" r:id="rId2" xr:uid="{B77AD5C5-CCF5-A544-956F-90393912BC49}"/>
+    <hyperlink ref="J13" r:id="rId3" xr:uid="{5FA155CA-9C46-A546-B238-40E7291FEC6D}"/>
+    <hyperlink ref="J14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{0233A0CB-1AE5-D046-B836-5554428906B4}"/>
+    <hyperlink ref="J16" r:id="rId5" xr:uid="{E3C0FE21-7AF4-BE40-BB5B-8790DEDB70F5}"/>
+    <hyperlink ref="J25" r:id="rId6" xr:uid="{39C08C03-B790-4F43-8E41-D386913011DA}"/>
+    <hyperlink ref="J36" r:id="rId7" xr:uid="{5B250127-3185-E04F-A929-ED7631A029F4}"/>
+    <hyperlink ref="J38" r:id="rId8" xr:uid="{4142F24F-B116-5844-B438-156E37529825}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D8891A-1B60-824C-AD0B-F681BA7EA3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D23B86-4904-C64A-8FED-9CA2CDB67710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="407">
   <si>
     <t>date</t>
   </si>
@@ -1538,6 +1538,21 @@
 a. La symétrie et la différence
 b. Le voyage dans le temps
 c. La cuisine</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uMVtpCPx8ow</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1Oq4SYcQgQ4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NVN02o8YYlQ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt7510836/</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYTE2MzQyMDMtM2ViZS00ODc4LTg2MWEtZTE4ZGNlOGY3NzgxXkEyXkFqcGc@._V1_FMjpg_UY3508_.jpg</t>
   </si>
 </sst>
 </file>
@@ -3376,7 +3391,7 @@
         <v>336</v>
       </c>
       <c r="C58" t="s">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="D58" t="s">
         <v>338</v>
@@ -3475,7 +3490,7 @@
         <v>357</v>
       </c>
       <c r="C61" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="D61" t="s">
         <v>359</v>
@@ -3598,7 +3613,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <f t="shared" si="0"/>
         <v>46255</v>
@@ -3607,7 +3622,10 @@
         <v>387</v>
       </c>
       <c r="C65" t="s">
-        <v>388</v>
+        <v>404</v>
+      </c>
+      <c r="D65" t="s">
+        <v>405</v>
       </c>
       <c r="E65" t="s">
         <v>389</v>
@@ -3628,7 +3646,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <f t="shared" si="0"/>
         <v>46258</v>
@@ -3659,6 +3677,9 @@
       </c>
       <c r="J66" t="s">
         <v>400</v>
+      </c>
+      <c r="K66" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D23B86-4904-C64A-8FED-9CA2CDB67710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA08ACD5-CAB9-BA47-B106-EA2DE885498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="408">
   <si>
     <t>date</t>
   </si>
@@ -1553,6 +1553,9 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/M/MV5BYTE2MzQyMDMtM2ViZS00ODc4LTg2MWEtZTE4ZGNlOGY3NzgxXkEyXkFqcGc@._V1_FMjpg_UY3508_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BMTFiOTI4YmYtMDczMy00ZjAyLTg1ZTUtYzdkOWI0ZmJlNjBkXkEyXkFqcGc@._V1_FMjpg_UX723_.jpg</t>
   </si>
 </sst>
 </file>
@@ -3216,6 +3219,9 @@
       <c r="H52" t="s">
         <v>298</v>
       </c>
+      <c r="K52" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="4">

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA08ACD5-CAB9-BA47-B106-EA2DE885498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00E8ADA-9A49-E847-BFA2-51517344DD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="412">
   <si>
     <t>date</t>
   </si>
@@ -1556,6 +1556,18 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/M/MV5BMTFiOTI4YmYtMDczMy00ZjAyLTg1ZTUtYzdkOWI0ZmJlNjBkXkEyXkFqcGc@._V1_FMjpg_UX723_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BNTUyM2MwMDMtOGU1Mi00YWMxLTlhYmEtYWM4NmU1YTc0OWFkXkEyXkFqcGc@._V1_FMjpg_UX889_.jpg</t>
+  </si>
+  <si>
+    <t>À une époque où les géants vivaient parmi les gens, un roi égoïste apprendra sa leçon en chassant un géant sympathique qui aidait les habitants de son royaume.</t>
+  </si>
+  <si>
+    <t>https://media.senscritique.com/media/000019184494/0/sans_gravite.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/M/MV5BYTg1NDQ3YzctYzU2OS00YzE4LTg0ZjAtZTZmNmYzMDMzOTUxXkEyXkFqcGc@._V1_FMjpg_UX400_.jpg</t>
   </si>
 </sst>
 </file>
@@ -2952,6 +2964,9 @@
       <c r="H40" t="s">
         <v>268</v>
       </c>
+      <c r="K40" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
@@ -3105,6 +3120,12 @@
       <c r="H47" t="s">
         <v>287</v>
       </c>
+      <c r="J47" t="s">
+        <v>409</v>
+      </c>
+      <c r="K47" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
@@ -3158,6 +3179,9 @@
       </c>
       <c r="H50" t="s">
         <v>293</v>
+      </c>
+      <c r="K50" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00E8ADA-9A49-E847-BFA2-51517344DD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F98421E-3695-BB46-9C86-7447BD90B7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="413">
   <si>
     <t>date</t>
   </si>
@@ -1568,6 +1568,9 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/M/MV5BYTg1NDQ3YzctYzU2OS00YzE4LTg0ZjAtZTZmNmYzMDMzOTUxXkEyXkFqcGc@._V1_FMjpg_UX400_.jpg</t>
+  </si>
+  <si>
+    <t>https://scontent-mrs2-1.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1695x2048&amp;ctp=s1695x2048&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=ScAJXh_MRdEQ7kNvwHpyrNt&amp;_nc_oc=AdrmwBqnIR0R1PidTgo7xQx0yNY39xI3IMs3wndhKdLLydDrvGJH_yucxl1RBCEW_hg&amp;_nc_zt=23&amp;_nc_ht=scontent-mrs2-1.xx&amp;_nc_gid=9FJObORGPt7onE8Y-TDEYA&amp;_nc_ss=7b289&amp;oh=00_AQLkbZicBPQ_7XufU-gjMqSLBh1-_l77WKEoKmYfyIEwOg&amp;oe=6A9BE9EB</t>
   </si>
 </sst>
 </file>
@@ -2351,7 +2354,7 @@
         <v>80</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>81</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -3723,11 +3726,10 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{84B21FBE-5522-2349-9ED7-1CF7C91EFD61}"/>
     <hyperlink ref="K10" r:id="rId2" xr:uid="{7DCFB6F7-350B-244A-A4EE-0FEDC3FAD578}"/>
     <hyperlink ref="K13" r:id="rId3" xr:uid="{F1F97A12-E06B-3042-A44B-81659830FCF3}"/>
-    <hyperlink ref="K14" r:id="rId4" display="https://scontent-cdg4-2.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=io_VDlPOYIUQ7kNvwEWOTOi&amp;_nc_oc=AdrhDDQ18qUlkEcCQ6D83CG4Xfmct2hWSocBZTpFV2CqFSMtwG1K-Y6aHuzmjev-VEg&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-2.xx&amp;_nc_gid=Hg2MxR-PJmj6_LpyJGlgnA&amp;_nc_ss=7b289&amp;oh=00_Af7hKMjz40EcJfB3aAmb6XbQcxXG254aY0DVMlfvDmihBA&amp;oe=6A1A0E2B" xr:uid="{4A97EF13-2B9A-5048-90A6-32D3CB3D9118}"/>
-    <hyperlink ref="K16" r:id="rId5" xr:uid="{8F831C98-E96E-C54A-919D-D4130B8003F3}"/>
-    <hyperlink ref="K25" r:id="rId6" xr:uid="{132034D3-17B4-3541-BBC2-3479C0C36EF6}"/>
-    <hyperlink ref="K36" r:id="rId7" xr:uid="{A83A35F1-3AE1-C84D-8BB6-EB29F7D17B61}"/>
-    <hyperlink ref="K38" r:id="rId8" xr:uid="{F1E8F208-0997-6A48-9639-AC5B9CB22618}"/>
+    <hyperlink ref="K16" r:id="rId4" xr:uid="{8F831C98-E96E-C54A-919D-D4130B8003F3}"/>
+    <hyperlink ref="K25" r:id="rId5" xr:uid="{132034D3-17B4-3541-BBC2-3479C0C36EF6}"/>
+    <hyperlink ref="K36" r:id="rId6" xr:uid="{A83A35F1-3AE1-C84D-8BB6-EB29F7D17B61}"/>
+    <hyperlink ref="K38" r:id="rId7" xr:uid="{F1E8F208-0997-6A48-9639-AC5B9CB22618}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/film.xlsx
+++ b/film.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F98421E-3695-BB46-9C86-7447BD90B7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068D56E8-A16A-7A4C-9C08-36727D20CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="442">
   <si>
     <t>date</t>
   </si>
@@ -1571,6 +1571,169 @@
   </si>
   <si>
     <t>https://scontent-mrs2-1.xx.fbcdn.net/v/t39.30808-6/497729397_4104897759832021_8341241960357943541_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1695x2048&amp;ctp=s1695x2048&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=ScAJXh_MRdEQ7kNvwHpyrNt&amp;_nc_oc=AdrmwBqnIR0R1PidTgo7xQx0yNY39xI3IMs3wndhKdLLydDrvGJH_yucxl1RBCEW_hg&amp;_nc_zt=23&amp;_nc_ht=scontent-mrs2-1.xx&amp;_nc_gid=9FJObORGPt7onE8Y-TDEYA&amp;_nc_ss=7b289&amp;oh=00_AQLkbZicBPQ_7XufU-gjMqSLBh1-_l77WKEoKmYfyIEwOg&amp;oe=6A9BE9EB</t>
+  </si>
+  <si>
+    <t>Coin Operated</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5L4DQfVIcdg</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt6749332/</t>
+  </si>
+  <si>
+    <t>Nicholas Arioli</t>
+  </si>
+  <si>
+    <t>5 min 14</t>
+  </si>
+  <si>
+    <t>Animation, Comédie dramatique</t>
+  </si>
+  <si>
+    <t>Un petit garçon passionné d'espace découvre un manège-fusée qui fonctionne avec des pièces de monnaie. Déçu que le manège ne décolle pas vraiment, il économise toute sa vie pour y remettre le plus de pièces possible, jusqu'à ce que, devenu vieux, le manège finisse enfin par décoller pour de vrai.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : De quoi rêve le petit garçon au début du film ?
+a. De voyager dans l'espace
+b. De devenir pompier
+c. De gagner une course
+Qestion 2 : Que se passe-t-il quand il monte pour la première fois dans le manège-fusée ?
+a. Le manège décolle immédiatement
+b. Le manège ne fait que vibrer, sans décoller
+c. Le manège tombe en panne
+Qestion 3 : Que décide-t-il de faire pour obtenir plus de pièces ?
+a. Il demande de l'argent à ses parents
+b. Il ouvre un stand de citronnade et économise toute sa vie
+c. Il abandonne son rêve
+Qestion 4 : Combien de temps s'écoule dans le film ?
+a. Une seule journée
+b. Une semaine
+c. Toute une vie, jusqu'à la vieillesse
+Qestion 5 : Que se passe-t-il quand, devenu vieux, il remet toutes ses pièces économisées dans le manège ?
+a. Rien ne se passe
+b. Le manège décolle enfin et l'envoie dans l'espace
+c. Le manège se casse</t>
+  </si>
+  <si>
+    <t>Achoo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Iz3J31GY1SQ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt7993166/</t>
+  </si>
+  <si>
+    <t>Lucas Boutrot, Elise Carret, Maoris Creantor, Pierre Hubert, Camille Lacroix, Charlotte Perroux</t>
+  </si>
+  <si>
+    <t>Dans une Chine ancestrale, un petit dragon enrhumé, incapable de cracher du feu comme les autres dragons, doit surmonter son handicap pour participer au grand défilé du Nouvel An. Film de fin d'études des étudiants de l'ESMA.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Où se déroule l'histoire ?
+a. Dans une Chine ancestrale
+b. Au Japon
+c. En France médiévale
+Qestion 2 : Quel est le problème du petit dragon Achoo ?
+a. Il ne sait pas voler
+b. Il est enrhumé et n'arrive pas à cracher du feu
+c. Il a peur des hommes
+Qestion 3 : Que doit-il réussir pour participer au défilé du Nouvel An ?
+a. Voler plus haut que les autres dragons
+b. Cracher du feu devant un jury
+c. Chanter une chanson
+Qestion 4 : Comment Achoo transforme-t-il son handicap en réussite ?
+a. Il abandonne la compétition
+b. Il crée un feu d'artifice coloré grâce à son éternuement
+c. Il demande à un autre dragon de le remplacer
+Qestion 5 : Ce court métrage a été réalisé par des étudiants de quelle école ?
+a. Gobelins
+b. L'ESMA
+c. Supinfocom</t>
+  </si>
+  <si>
+    <t>The Fantastic Flying Books of Mr Morris Lessmore</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ad3CMri3hOs</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt1778342/</t>
+  </si>
+  <si>
+    <t>William Joyce, Brandon Oldenburg</t>
+  </si>
+  <si>
+    <t>15 min 00</t>
+  </si>
+  <si>
+    <t>Animation, Aventure</t>
+  </si>
+  <si>
+    <t>Après qu'une tempête a dévasté sa ville et dispersé les pages de son livre, l'écrivain Morris Lessmore est mené par une femme portée par des livres volants jusqu'à une bibliothèque magique. Il y devient le gardien des livres vivants et passe ses jours à les prêter aux habitants. Un hommage sans parole au pouvoir des histoires. Oscar du meilleur court métrage d'animation en 2012. Note : le film s'ouvre sur une tempête qui détruit la ville (sans scène violente, dans un registre poétique proche du Magicien d'Oz) — à savoir avant diffusion en classe.</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Où vit Morris Lessmore au début de l'histoire ?
+a. Dans le quartier français de La Nouvelle-Orléans
+b. À Paris
+c. Dans une forêt
+Qestion 2 : Que se passe-t-il au début du film et bouleverse sa vie ?
+a. Une tempête dévaste la ville et disperse les pages de son livre
+b. Un incendie détruit sa maison
+c. Il perd son travail
+Qestion 3 : Qui guide Morris vers la bibliothèque magique ?
+a. Une femme portée dans les airs par des livres volants
+b. Un vieux sage
+c. Un chat
+Qestion 4 : Que fait Morris une fois arrivé à la bibliothèque ?
+a. Il devient le gardien des livres et les prête aux habitants
+b. Il repart aussitôt
+c. Il brûle tous les livres
+Qestion 5 : Ce court métrage a reçu quelle récompense ?
+a. La Palme d'or
+b. L'Oscar du meilleur court métrage d'animation
+c. Aucune récompense</t>
+  </si>
+  <si>
+    <t>Taking the Plunge</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vRx64n-ooQQ</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/fr/title/tt5076686/</t>
+  </si>
+  <si>
+    <t>Elizabeth Ku-Herrero, Nicholas Manfredi, Thaddaeus Andreades, Marie Raoult</t>
+  </si>
+  <si>
+    <t>7 min 00</t>
+  </si>
+  <si>
+    <t>Un jeune homme a minutieusement préparé la demande en mariage parfaite pour sa fiancée. Mais quand un imprévu menace de tout gâcher, il doit plonger dans l'inconnu pour sauver son plan et vivre ce moment comme il l'avait rêvé. Film de fin d'études de la School of Visual Arts (New York).</t>
+  </si>
+  <si>
+    <t>Qestion 1 : Que prépare le jeune homme au début du film ?
+a. Un mariage surprise
+b. Une demande en mariage
+c. Un anniversaire
+Qestion 2 : Que se passe-t-il et menace ses plans ?
+a. Il pleut
+b. Un imprévu vient tout compromettre
+c. Il se perd
+Qestion 3 : Que doit-il faire pour sauver la situation ?
+a. Abandonner son projet
+b. Plonger dans l'eau pour récupérer quelque chose
+c. Appeler un ami
+Qestion 4 : Ce film a été réalisé par des étudiants de quelle école ?
+a. La School of Visual Arts (New York)
+b. Les Gobelins
+c. L'ESMA
+Qestion 5 : Comment se termine l'histoire ?
+a. La demande en mariage échoue
+b. La demande en mariage se déroule finalement comme prévu
+c. Le film ne montre pas la fin</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14.83203125" style="3" customWidth="1"/>
@@ -2775,7 +2938,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <f t="shared" ref="A32:A66" si="0">WORKDAY(A31,1)</f>
+        <f t="shared" ref="A32:A70" si="0">WORKDAY(A31,1)</f>
         <v>46210</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -3713,6 +3876,138 @@
       </c>
       <c r="K66" t="s">
         <v>406</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <f t="shared" si="0"/>
+        <v>46259</v>
+      </c>
+      <c r="B67" t="s">
+        <v>413</v>
+      </c>
+      <c r="C67" t="s">
+        <v>414</v>
+      </c>
+      <c r="D67" t="s">
+        <v>415</v>
+      </c>
+      <c r="E67" t="s">
+        <v>416</v>
+      </c>
+      <c r="F67" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67">
+        <v>2017</v>
+      </c>
+      <c r="H67" t="s">
+        <v>417</v>
+      </c>
+      <c r="I67" t="s">
+        <v>418</v>
+      </c>
+      <c r="J67" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <f t="shared" si="0"/>
+        <v>46260</v>
+      </c>
+      <c r="B68" t="s">
+        <v>421</v>
+      </c>
+      <c r="C68" t="s">
+        <v>422</v>
+      </c>
+      <c r="D68" t="s">
+        <v>423</v>
+      </c>
+      <c r="E68" t="s">
+        <v>424</v>
+      </c>
+      <c r="F68" t="s">
+        <v>66</v>
+      </c>
+      <c r="G68">
+        <v>2017</v>
+      </c>
+      <c r="H68" t="s">
+        <v>311</v>
+      </c>
+      <c r="I68" t="s">
+        <v>399</v>
+      </c>
+      <c r="J68" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <f t="shared" si="0"/>
+        <v>46261</v>
+      </c>
+      <c r="B69" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" t="s">
+        <v>428</v>
+      </c>
+      <c r="D69" t="s">
+        <v>429</v>
+      </c>
+      <c r="E69" t="s">
+        <v>430</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69">
+        <v>2011</v>
+      </c>
+      <c r="H69" t="s">
+        <v>431</v>
+      </c>
+      <c r="I69" t="s">
+        <v>432</v>
+      </c>
+      <c r="J69" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <f t="shared" si="0"/>
+        <v>46262</v>
+      </c>
+      <c r="B70" t="s">
+        <v>435</v>
+      </c>
+      <c r="C70" t="s">
+        <v>436</v>
+      </c>
+      <c r="D70" t="s">
+        <v>437</v>
+      </c>
+      <c r="E70" t="s">
+        <v>438</v>
+      </c>
+      <c r="F70" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70">
+        <v>2015</v>
+      </c>
+      <c r="H70" t="s">
+        <v>439</v>
+      </c>
+      <c r="I70" t="s">
+        <v>384</v>
+      </c>
+      <c r="J70" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -3738,7 +4033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="36" customWidth="1"/>
@@ -4911,7 +5206,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>322</v>
       </c>
@@ -4943,7 +5238,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>330</v>
       </c>
@@ -5071,7 +5366,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>357</v>
       </c>
@@ -5103,7 +5398,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>365</v>
       </c>
@@ -5135,7 +5430,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>372</v>
       </c>
@@ -5199,7 +5494,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>387</v>
       </c>
@@ -5228,7 +5523,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>394</v>
       </c>
@@ -5258,6 +5553,134 @@
       </c>
       <c r="K66" s="2" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>413</v>
+      </c>
+      <c r="B67" t="s">
+        <v>414</v>
+      </c>
+      <c r="C67" t="s">
+        <v>415</v>
+      </c>
+      <c r="D67" t="s">
+        <v>416</v>
+      </c>
+      <c r="E67" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67">
+        <v>2017</v>
+      </c>
+      <c r="G67" t="s">
+        <v>417</v>
+      </c>
+      <c r="H67" t="s">
+        <v>418</v>
+      </c>
+      <c r="I67" t="s">
+        <v>419</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>421</v>
+      </c>
+      <c r="B68" t="s">
+        <v>422</v>
+      </c>
+      <c r="C68" t="s">
+        <v>423</v>
+      </c>
+      <c r="D68" t="s">
+        <v>424</v>
+      </c>
+      <c r="E68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F68">
+        <v>2017</v>
+      </c>
+      <c r="G68" t="s">
+        <v>311</v>
+      </c>
+      <c r="H68" t="s">
+        <v>399</v>
+      </c>
+      <c r="I68" t="s">
+        <v>425</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="404" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>427</v>
+      </c>
+      <c r="B69" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" t="s">
+        <v>429</v>
+      </c>
+      <c r="D69" t="s">
+        <v>430</v>
+      </c>
+      <c r="E69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69">
+        <v>2011</v>
+      </c>
+      <c r="G69" t="s">
+        <v>431</v>
+      </c>
+      <c r="H69" t="s">
+        <v>432</v>
+      </c>
+      <c r="I69" t="s">
+        <v>433</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="404" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>435</v>
+      </c>
+      <c r="B70" t="s">
+        <v>436</v>
+      </c>
+      <c r="C70" t="s">
+        <v>437</v>
+      </c>
+      <c r="D70" t="s">
+        <v>438</v>
+      </c>
+      <c r="E70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70">
+        <v>2015</v>
+      </c>
+      <c r="G70" t="s">
+        <v>439</v>
+      </c>
+      <c r="H70" t="s">
+        <v>384</v>
+      </c>
+      <c r="I70" t="s">
+        <v>440</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
